--- a/app/fonlar/haftalik-yatirim-fonlarinin-en-cok-tercih-ettigi-hisseler/data/tercih-edilen-hisseler.xlsx
+++ b/app/fonlar/haftalik-yatirim-fonlarinin-en-cok-tercih-ettigi-hisseler/data/tercih-edilen-hisseler.xlsx
@@ -40,127 +40,139 @@
     <x:t>Maliyet</x:t>
   </x:si>
   <x:si>
+    <x:t>GEDIK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PUSULA YAT.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MIDAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ZIRAAT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>YAPI KREDI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INFO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TACIRLER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OSMANLI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TEB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALNUS</x:t>
+  </x:si>
+  <x:si>
     <x:t>A1 CAPITAL</x:t>
   </x:si>
   <x:si>
-    <x:t>GEDIK</x:t>
+    <x:t>KUVEYT TURK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SEKER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BTCTURK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FIBA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ACAR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TERA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRIVE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UNLU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ANADOLU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BULLS YATIRIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INVEST AZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ICBC TURKEY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DINAMIK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BURGAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIZIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INTEGRAL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALTERNATIF</x:t>
+  </x:si>
+  <x:si>
+    <x:t>YATIRIM FINANSMAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HSBC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AHLATCI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ING</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PHILLIP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GLOBAL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IKON</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HALK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VAKIF</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ATA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MEKSA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>QNB YATIRIM</x:t>
   </x:si>
   <x:si>
     <x:t>AK</x:t>
   </x:si>
   <x:si>
-    <x:t>YAPI KREDI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PUSULA YAT.</x:t>
-  </x:si>
-  <x:si>
     <x:t>OYAK</x:t>
   </x:si>
   <x:si>
-    <x:t>MIDAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UNLU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GLOBAL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ICBC TURKEY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALNUS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FIBA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IKON</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ACAR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TEB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BTCTURK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIZIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SEKER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BULLS YATIRIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HSBC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>YATIRIM FINANSMAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TRIVE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BURGAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INVEST AZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KUVEYT TURK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ING</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OSMANLI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AHLATCI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HALK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ATA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TERA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INFO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TACIRLER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VAKIF</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MEKSA</x:t>
+    <x:t>DENIZ</x:t>
   </x:si>
   <x:si>
     <x:t>GARANTI BBVA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ZIRAAT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PHILLIP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>QNB YATIRIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DENIZ</x:t>
   </x:si>
   <x:si>
     <x:t>MARBAS</x:t>
@@ -514,7 +526,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:I43"/>
+  <x:dimension ref="A1:I47"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:9">
@@ -551,28 +563,28 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B2" s="0">
-        <x:v>237692</x:v>
+        <x:v>207173</x:v>
       </x:c>
       <x:c r="C2" s="0">
-        <x:v>63.935997594565</x:v>
+        <x:v>63.5415233125163</x:v>
       </x:c>
       <x:c r="D2" s="0">
-        <x:v>30652</x:v>
+        <x:v>98426</x:v>
       </x:c>
       <x:c r="E2" s="0">
-        <x:v>63.8280833913999</x:v>
+        <x:v>63.1717836531816</x:v>
       </x:c>
       <x:c r="F2" s="0">
-        <x:v>268344</x:v>
+        <x:v>305599</x:v>
       </x:c>
       <x:c r="G2" s="0">
-        <x:v>12.4732030469972</x:v>
+        <x:v>3.94271637533131</x:v>
       </x:c>
       <x:c r="H2" s="0">
-        <x:v>207040</x:v>
+        <x:v>108747</x:v>
       </x:c>
       <x:c r="I2" s="0">
-        <x:v>63.9519741505707</x:v>
+        <x:v>63.8761715852013</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:9">
@@ -580,28 +592,28 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B3" s="0">
-        <x:v>138402</x:v>
+        <x:v>526033</x:v>
       </x:c>
       <x:c r="C3" s="0">
-        <x:v>63.6828448407952</x:v>
+        <x:v>63.2202920568709</x:v>
       </x:c>
       <x:c r="D3" s="0">
-        <x:v>4790</x:v>
+        <x:v>438161</x:v>
       </x:c>
       <x:c r="E3" s="0">
-        <x:v>63.8160233021778</x:v>
+        <x:v>63.0988508692517</x:v>
       </x:c>
       <x:c r="F3" s="0">
-        <x:v>143192</x:v>
+        <x:v>964194</x:v>
       </x:c>
       <x:c r="G3" s="0">
-        <x:v>6.65587041523424</x:v>
+        <x:v>12.4396463103485</x:v>
       </x:c>
       <x:c r="H3" s="0">
-        <x:v>133612</x:v>
+        <x:v>87872</x:v>
       </x:c>
       <x:c r="I3" s="0">
-        <x:v>63.6780703831864</x:v>
+        <x:v>63.8258409485362</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:9">
@@ -609,28 +621,28 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B4" s="0">
-        <x:v>160144</x:v>
+        <x:v>109797</x:v>
       </x:c>
       <x:c r="C4" s="0">
-        <x:v>63.9920020849034</x:v>
+        <x:v>63.3649725677096</x:v>
       </x:c>
       <x:c r="D4" s="0">
-        <x:v>81190</x:v>
+        <x:v>43732</x:v>
       </x:c>
       <x:c r="E4" s="0">
-        <x:v>63.813543864773</x:v>
+        <x:v>63.6223980803225</x:v>
       </x:c>
       <x:c r="F4" s="0">
-        <x:v>241334</x:v>
+        <x:v>153529</x:v>
       </x:c>
       <x:c r="G4" s="0">
-        <x:v>11.2177204787288</x:v>
+        <x:v>1.98076990562221</x:v>
       </x:c>
       <x:c r="H4" s="0">
-        <x:v>78954</x:v>
+        <x:v>66065</x:v>
       </x:c>
       <x:c r="I4" s="0">
-        <x:v>64.1755142931814</x:v>
+        <x:v>63.1945686849035</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:9">
@@ -638,28 +650,28 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B5" s="0">
-        <x:v>87673</x:v>
+        <x:v>249690</x:v>
       </x:c>
       <x:c r="C5" s="0">
-        <x:v>63.7919662158568</x:v>
+        <x:v>63.2518870349306</x:v>
       </x:c>
       <x:c r="D5" s="0">
-        <x:v>30219</x:v>
+        <x:v>188256</x:v>
       </x:c>
       <x:c r="E5" s="0">
-        <x:v>63.8936509336539</x:v>
+        <x:v>63.1686078629768</x:v>
       </x:c>
       <x:c r="F5" s="0">
-        <x:v>117892</x:v>
+        <x:v>437946</x:v>
       </x:c>
       <x:c r="G5" s="0">
-        <x:v>5.47987230426836</x:v>
+        <x:v>5.65020456778604</x:v>
       </x:c>
       <x:c r="H5" s="0">
-        <x:v>57454</x:v>
+        <x:v>61434</x:v>
       </x:c>
       <x:c r="I5" s="0">
-        <x:v>63.7384832470973</x:v>
+        <x:v>63.5070845443771</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:9">
@@ -667,28 +679,28 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B6" s="0">
-        <x:v>71737</x:v>
+        <x:v>277677</x:v>
       </x:c>
       <x:c r="C6" s="0">
-        <x:v>63.8988150445293</x:v>
+        <x:v>63.4179685011106</x:v>
       </x:c>
       <x:c r="D6" s="0">
-        <x:v>54851</x:v>
+        <x:v>231920</x:v>
       </x:c>
       <x:c r="E6" s="0">
-        <x:v>63.6677961555867</x:v>
+        <x:v>63.1841199488013</x:v>
       </x:c>
       <x:c r="F6" s="0">
-        <x:v>126588</x:v>
+        <x:v>509597</x:v>
       </x:c>
       <x:c r="G6" s="0">
-        <x:v>5.88408098304146</x:v>
+        <x:v>6.57461718369403</x:v>
       </x:c>
       <x:c r="H6" s="0">
-        <x:v>16886</x:v>
+        <x:v>45757</x:v>
       </x:c>
       <x:c r="I6" s="0">
-        <x:v>64.6492365225223</x:v>
+        <x:v>64.6032331874222</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:9">
@@ -696,28 +708,28 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="B7" s="0">
-        <x:v>49151</x:v>
+        <x:v>202039</x:v>
       </x:c>
       <x:c r="C7" s="0">
-        <x:v>63.52132141732</x:v>
+        <x:v>63.418724243242</x:v>
       </x:c>
       <x:c r="D7" s="0">
-        <x:v>33403</x:v>
+        <x:v>165074</x:v>
       </x:c>
       <x:c r="E7" s="0">
-        <x:v>63.646852685203</x:v>
+        <x:v>63.343316386287</x:v>
       </x:c>
       <x:c r="F7" s="0">
-        <x:v>82554</x:v>
+        <x:v>367113</x:v>
       </x:c>
       <x:c r="G7" s="0">
-        <x:v>3.83728648429554</x:v>
+        <x:v>4.73634546152639</x:v>
       </x:c>
       <x:c r="H7" s="0">
-        <x:v>15748</x:v>
+        <x:v>36965</x:v>
       </x:c>
       <x:c r="I7" s="0">
-        <x:v>63.2550577050331</x:v>
+        <x:v>63.7554718850382</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:9">
@@ -725,28 +737,28 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B8" s="0">
-        <x:v>15809</x:v>
+        <x:v>107659</x:v>
       </x:c>
       <x:c r="C8" s="0">
-        <x:v>63.6446316374178</x:v>
+        <x:v>63.1242408176298</x:v>
       </x:c>
       <x:c r="D8" s="0">
-        <x:v>3489</x:v>
+        <x:v>80868</x:v>
       </x:c>
       <x:c r="E8" s="0">
-        <x:v>63.744023964582</x:v>
+        <x:v>63.6446985627409</x:v>
       </x:c>
       <x:c r="F8" s="0">
-        <x:v>19298</x:v>
+        <x:v>188527</x:v>
       </x:c>
       <x:c r="G8" s="0">
-        <x:v>0.897012314048204</x:v>
+        <x:v>2.43230013871801</x:v>
       </x:c>
       <x:c r="H8" s="0">
-        <x:v>12320</x:v>
+        <x:v>26791</x:v>
       </x:c>
       <x:c r="I8" s="0">
-        <x:v>63.6164839239864</x:v>
+        <x:v>61.5532514207561</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:9">
@@ -754,28 +766,28 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="B9" s="0">
-        <x:v>35892</x:v>
+        <x:v>105630</x:v>
       </x:c>
       <x:c r="C9" s="0">
-        <x:v>63.8183911003743</x:v>
+        <x:v>63.3534532095394</x:v>
       </x:c>
       <x:c r="D9" s="0">
-        <x:v>25558</x:v>
+        <x:v>82351</x:v>
       </x:c>
       <x:c r="E9" s="0">
-        <x:v>63.825761738625</x:v>
+        <x:v>63.6116941446259</x:v>
       </x:c>
       <x:c r="F9" s="0">
-        <x:v>61450</x:v>
+        <x:v>187981</x:v>
       </x:c>
       <x:c r="G9" s="0">
-        <x:v>2.85632742762266</x:v>
+        <x:v>2.42525586455177</x:v>
       </x:c>
       <x:c r="H9" s="0">
-        <x:v>10334</x:v>
+        <x:v>23279</x:v>
       </x:c>
       <x:c r="I9" s="0">
-        <x:v>63.8001620726588</x:v>
+        <x:v>62.439908845722</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:9">
@@ -783,28 +795,28 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B10" s="0">
-        <x:v>11034</x:v>
+        <x:v>57483</x:v>
       </x:c>
       <x:c r="C10" s="0">
-        <x:v>63.8359438647432</x:v>
+        <x:v>63.3503271413845</x:v>
       </x:c>
       <x:c r="D10" s="0">
-        <x:v>5171</x:v>
+        <x:v>34294</x:v>
       </x:c>
       <x:c r="E10" s="0">
-        <x:v>64.1132959791134</x:v>
+        <x:v>63.4918703762318</x:v>
       </x:c>
       <x:c r="F10" s="0">
-        <x:v>16205</x:v>
+        <x:v>91777</x:v>
       </x:c>
       <x:c r="G10" s="0">
-        <x:v>0.753243058822217</x:v>
+        <x:v>1.1840702383803</x:v>
       </x:c>
       <x:c r="H10" s="0">
-        <x:v>5863</x:v>
+        <x:v>23189</x:v>
       </x:c>
       <x:c r="I10" s="0">
-        <x:v>63.5913271525808</x:v>
+        <x:v>63.1410001460051</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:9">
@@ -812,28 +824,28 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B11" s="0">
-        <x:v>5410</x:v>
+        <x:v>23060</x:v>
       </x:c>
       <x:c r="C11" s="0">
-        <x:v>63.8156921696971</x:v>
+        <x:v>63.4956591145432</x:v>
       </x:c>
       <x:c r="D11" s="0">
-        <x:v>129</x:v>
+        <x:v>6094</x:v>
       </x:c>
       <x:c r="E11" s="0">
-        <x:v>63.8968994081482</x:v>
+        <x:v>63.1403515655798</x:v>
       </x:c>
       <x:c r="F11" s="0">
-        <x:v>5539</x:v>
+        <x:v>29154</x:v>
       </x:c>
       <x:c r="G11" s="0">
-        <x:v>0.257464566665613</x:v>
+        <x:v>0.376133276635097</x:v>
       </x:c>
       <x:c r="H11" s="0">
-        <x:v>5281</x:v>
+        <x:v>16966</x:v>
       </x:c>
       <x:c r="I11" s="0">
-        <x:v>63.8137085049064</x:v>
+        <x:v>63.6232816657269</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:9">
@@ -841,28 +853,28 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="B12" s="0">
-        <x:v>4000</x:v>
+        <x:v>32211</x:v>
       </x:c>
       <x:c r="C12" s="0">
-        <x:v>63.4500007629394</x:v>
+        <x:v>63.3112678768242</x:v>
       </x:c>
       <x:c r="D12" s="0">
-        <x:v>0</x:v>
+        <x:v>16655</x:v>
       </x:c>
       <x:c r="E12" s="0">
-        <x:v>0</x:v>
+        <x:v>63.2830428566384</x:v>
       </x:c>
       <x:c r="F12" s="0">
-        <x:v>4000</x:v>
+        <x:v>48866</x:v>
       </x:c>
       <x:c r="G12" s="0">
-        <x:v>0.18592855509342</x:v>
+        <x:v>0.630449636278064</x:v>
       </x:c>
       <x:c r="H12" s="0">
-        <x:v>4000</x:v>
+        <x:v>15556</x:v>
       </x:c>
       <x:c r="I12" s="0">
-        <x:v>63.4500007629394</x:v>
+        <x:v>63.3414869377134</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:9">
@@ -870,28 +882,28 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B13" s="0">
-        <x:v>3503</x:v>
+        <x:v>295810</x:v>
       </x:c>
       <x:c r="C13" s="0">
-        <x:v>64.0683999732668</x:v>
+        <x:v>63.7801573385086</x:v>
       </x:c>
       <x:c r="D13" s="0">
-        <x:v>143</x:v>
+        <x:v>283396</x:v>
       </x:c>
       <x:c r="E13" s="0">
-        <x:v>63.3237754715072</x:v>
+        <x:v>63.1751105471905</x:v>
       </x:c>
       <x:c r="F13" s="0">
-        <x:v>3646</x:v>
+        <x:v>579206</x:v>
       </x:c>
       <x:c r="G13" s="0">
-        <x:v>0.169473877967652</x:v>
+        <x:v>7.47268473028429</x:v>
       </x:c>
       <x:c r="H13" s="0">
-        <x:v>3360</x:v>
+        <x:v>12414</x:v>
       </x:c>
       <x:c r="I13" s="0">
-        <x:v>64.1000908374786</x:v>
+        <x:v>77.5926142800578</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:9">
@@ -899,28 +911,28 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="B14" s="0">
-        <x:v>3482</x:v>
+        <x:v>14228</x:v>
       </x:c>
       <x:c r="C14" s="0">
-        <x:v>64.1516655500698</x:v>
+        <x:v>63.4620916684558</x:v>
       </x:c>
       <x:c r="D14" s="0">
-        <x:v>611</x:v>
+        <x:v>5668</x:v>
       </x:c>
       <x:c r="E14" s="0">
-        <x:v>63.6184111375075</x:v>
+        <x:v>63.1116178299898</x:v>
       </x:c>
       <x:c r="F14" s="0">
-        <x:v>4093</x:v>
+        <x:v>19896</x:v>
       </x:c>
       <x:c r="G14" s="0">
-        <x:v>0.190251393999342</x:v>
+        <x:v>0.256690254233789</x:v>
       </x:c>
       <x:c r="H14" s="0">
-        <x:v>2871</x:v>
+        <x:v>8560</x:v>
       </x:c>
       <x:c r="I14" s="0">
-        <x:v>64.2651515988596</x:v>
+        <x:v>63.6941577568232</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:9">
@@ -928,28 +940,28 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B15" s="0">
-        <x:v>9004</x:v>
+        <x:v>7815</x:v>
       </x:c>
       <x:c r="C15" s="0">
-        <x:v>63.5268321975715</x:v>
+        <x:v>63.3483179733071</x:v>
       </x:c>
       <x:c r="D15" s="0">
-        <x:v>6600</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="E15" s="0">
-        <x:v>63.9712110577208</x:v>
+        <x:v>63.5151311974776</x:v>
       </x:c>
       <x:c r="F15" s="0">
-        <x:v>15604</x:v>
+        <x:v>8043</x:v>
       </x:c>
       <x:c r="G15" s="0">
-        <x:v>0.725307293419431</x:v>
+        <x:v>0.103767577141253</x:v>
       </x:c>
       <x:c r="H15" s="0">
-        <x:v>2404</x:v>
+        <x:v>7587</x:v>
       </x:c>
       <x:c r="I15" s="0">
-        <x:v>62.3068236796908</x:v>
+        <x:v>63.3433050017623</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:9">
@@ -957,28 +969,28 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B16" s="0">
-        <x:v>8000</x:v>
+        <x:v>11734</x:v>
       </x:c>
       <x:c r="C16" s="0">
-        <x:v>64.0000009536743</x:v>
+        <x:v>63.2832403035064</x:v>
       </x:c>
       <x:c r="D16" s="0">
-        <x:v>6807</x:v>
+        <x:v>4480</x:v>
       </x:c>
       <x:c r="E16" s="0">
-        <x:v>63.9881447379733</x:v>
+        <x:v>62.9678683613028</x:v>
       </x:c>
       <x:c r="F16" s="0">
-        <x:v>14807</x:v>
+        <x:v>16214</x:v>
       </x:c>
       <x:c r="G16" s="0">
-        <x:v>0.688261028817067</x:v>
+        <x:v>0.209186559215252</x:v>
       </x:c>
       <x:c r="H16" s="0">
-        <x:v>1193</x:v>
+        <x:v>7254</x:v>
       </x:c>
       <x:c r="I16" s="0">
-        <x:v>64.067649956421</x:v>
+        <x:v>63.4780109543297</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:9">
@@ -986,28 +998,28 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B17" s="0">
-        <x:v>2126</x:v>
+        <x:v>8180</x:v>
       </x:c>
       <x:c r="C17" s="0">
-        <x:v>63.781372680377</x:v>
+        <x:v>63.5262406514734</x:v>
       </x:c>
       <x:c r="D17" s="0">
-        <x:v>1011</x:v>
+        <x:v>1338</x:v>
       </x:c>
       <x:c r="E17" s="0">
-        <x:v>63.3420863656215</x:v>
+        <x:v>63.2597522051345</x:v>
       </x:c>
       <x:c r="F17" s="0">
-        <x:v>3137</x:v>
+        <x:v>9518</x:v>
       </x:c>
       <x:c r="G17" s="0">
-        <x:v>0.145814469332014</x:v>
+        <x:v>0.122797438670949</x:v>
       </x:c>
       <x:c r="H17" s="0">
-        <x:v>1115</x:v>
+        <x:v>6842</x:v>
       </x:c>
       <x:c r="I17" s="0">
-        <x:v>64.1796852043391</x:v>
+        <x:v>63.5783542938589</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:9">
@@ -1015,28 +1027,28 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B18" s="0">
-        <x:v>1294</x:v>
+        <x:v>18000</x:v>
       </x:c>
       <x:c r="C18" s="0">
-        <x:v>63.5670002019018</x:v>
+        <x:v>63.5458335876465</x:v>
       </x:c>
       <x:c r="D18" s="0">
-        <x:v>791</x:v>
+        <x:v>13900</x:v>
       </x:c>
       <x:c r="E18" s="0">
-        <x:v>63.2999992370606</x:v>
+        <x:v>63.7091046930217</x:v>
       </x:c>
       <x:c r="F18" s="0">
-        <x:v>2085</x:v>
+        <x:v>31900</x:v>
       </x:c>
       <x:c r="G18" s="0">
-        <x:v>0.0969152593424451</x:v>
+        <x:v>0.411561073082925</x:v>
       </x:c>
       <x:c r="H18" s="0">
-        <x:v>503</x:v>
+        <x:v>4100</x:v>
       </x:c>
       <x:c r="I18" s="0">
-        <x:v>63.9868764706682</x:v>
+        <x:v>62.9923047182037</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:9">
@@ -1044,28 +1056,28 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B19" s="0">
-        <x:v>0</x:v>
+        <x:v>70748</x:v>
       </x:c>
       <x:c r="C19" s="0">
-        <x:v>0</x:v>
+        <x:v>63.0085425625731</x:v>
       </x:c>
       <x:c r="D19" s="0">
-        <x:v>25</x:v>
+        <x:v>67030</x:v>
       </x:c>
       <x:c r="E19" s="0">
-        <x:v>63.9000015258789</x:v>
+        <x:v>63.8711906514487</x:v>
       </x:c>
       <x:c r="F19" s="0">
-        <x:v>25</x:v>
+        <x:v>137778</x:v>
       </x:c>
       <x:c r="G19" s="0">
-        <x:v>0.00116205346933387</x:v>
+        <x:v>1.77755678768712</x:v>
       </x:c>
       <x:c r="H19" s="0">
-        <x:v>-25</x:v>
+        <x:v>3718</x:v>
       </x:c>
       <x:c r="I19" s="0">
-        <x:v>63.9000015258789</x:v>
+        <x:v>47.4562829075609</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:9">
@@ -1073,28 +1085,28 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="B20" s="0">
-        <x:v>2</x:v>
+        <x:v>5524</x:v>
       </x:c>
       <x:c r="C20" s="0">
-        <x:v>63.2999992370606</x:v>
+        <x:v>63.2452845148726</x:v>
       </x:c>
       <x:c r="D20" s="0">
-        <x:v>27</x:v>
+        <x:v>1980</x:v>
       </x:c>
       <x:c r="E20" s="0">
-        <x:v>63.2999992370606</x:v>
+        <x:v>63.3769440005524</x:v>
       </x:c>
       <x:c r="F20" s="0">
-        <x:v>29</x:v>
+        <x:v>7504</x:v>
       </x:c>
       <x:c r="G20" s="0">
-        <x:v>0.00134798202442729</x:v>
+        <x:v>0.0968136141822656</x:v>
       </x:c>
       <x:c r="H20" s="0">
-        <x:v>-25</x:v>
+        <x:v>3544</x:v>
       </x:c>
       <x:c r="I20" s="0">
-        <x:v>63.2999992370606</x:v>
+        <x:v>63.1717275787422</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:9">
@@ -1102,28 +1114,28 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="B21" s="0">
-        <x:v>0</x:v>
+        <x:v>16163</x:v>
       </x:c>
       <x:c r="C21" s="0">
-        <x:v>0</x:v>
+        <x:v>63.4795061852653</x:v>
       </x:c>
       <x:c r="D21" s="0">
-        <x:v>27</x:v>
+        <x:v>15284</x:v>
       </x:c>
       <x:c r="E21" s="0">
-        <x:v>63.2999992370606</x:v>
+        <x:v>63.5477559389915</x:v>
       </x:c>
       <x:c r="F21" s="0">
-        <x:v>27</x:v>
+        <x:v>31447</x:v>
       </x:c>
       <x:c r="G21" s="0">
-        <x:v>0.00125501774688058</x:v>
+        <x:v>0.405716647813127</x:v>
       </x:c>
       <x:c r="H21" s="0">
-        <x:v>-27</x:v>
+        <x:v>879</x:v>
       </x:c>
       <x:c r="I21" s="0">
-        <x:v>63.2999992370606</x:v>
+        <x:v>62.2927835050025</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:9">
@@ -1131,28 +1143,28 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="B22" s="0">
+        <x:v>717</x:v>
+      </x:c>
+      <x:c r="C22" s="0">
+        <x:v>62.5</x:v>
+      </x:c>
+      <x:c r="D22" s="0">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C22" s="0">
+      <x:c r="E22" s="0">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D22" s="0">
-        <x:v>156</x:v>
-      </x:c>
-      <x:c r="E22" s="0">
-        <x:v>64.1500015258789</x:v>
-      </x:c>
       <x:c r="F22" s="0">
-        <x:v>156</x:v>
+        <x:v>717</x:v>
       </x:c>
       <x:c r="G22" s="0">
-        <x:v>0.00725121364864337</x:v>
+        <x:v>0.00925044794358801</x:v>
       </x:c>
       <x:c r="H22" s="0">
-        <x:v>-156</x:v>
+        <x:v>717</x:v>
       </x:c>
       <x:c r="I22" s="0">
-        <x:v>64.1500015258789</x:v>
+        <x:v>62.5</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:9">
@@ -1160,28 +1172,28 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="B23" s="0">
-        <x:v>0</x:v>
+        <x:v>562</x:v>
       </x:c>
       <x:c r="C23" s="0">
-        <x:v>0</x:v>
+        <x:v>62.6010688700286</x:v>
       </x:c>
       <x:c r="D23" s="0">
-        <x:v>184</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="E23" s="0">
-        <x:v>63.3777167900749</x:v>
+        <x:v>63.2314279828753</x:v>
       </x:c>
       <x:c r="F23" s="0">
-        <x:v>184</x:v>
+        <x:v>597</x:v>
       </x:c>
       <x:c r="G23" s="0">
-        <x:v>0.00855271353429731</x:v>
+        <x:v>0.00770225581913813</x:v>
       </x:c>
       <x:c r="H23" s="0">
-        <x:v>-184</x:v>
+        <x:v>527</x:v>
       </x:c>
       <x:c r="I23" s="0">
-        <x:v>63.3777167900749</x:v>
+        <x:v>62.5592044128186</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:9">
@@ -1189,28 +1201,28 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="B24" s="0">
-        <x:v>466</x:v>
+        <x:v>1100</x:v>
       </x:c>
       <x:c r="C24" s="0">
-        <x:v>63.9824045369553</x:v>
+        <x:v>62.6863642605868</x:v>
       </x:c>
       <x:c r="D24" s="0">
-        <x:v>706</x:v>
+        <x:v>836</x:v>
       </x:c>
       <x:c r="E24" s="0">
-        <x:v>63.3715992946463</x:v>
+        <x:v>63.8083738117127</x:v>
       </x:c>
       <x:c r="F24" s="0">
-        <x:v>1172</x:v>
+        <x:v>1936</x:v>
       </x:c>
       <x:c r="G24" s="0">
-        <x:v>0.054477066642372</x:v>
+        <x:v>0.0249774996077913</x:v>
       </x:c>
       <x:c r="H24" s="0">
-        <x:v>-240</x:v>
+        <x:v>264</x:v>
       </x:c>
       <x:c r="I24" s="0">
-        <x:v>62.1856191158295</x:v>
+        <x:v>59.133334015355</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:9">
@@ -1218,28 +1230,28 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="B25" s="0">
-        <x:v>200</x:v>
+        <x:v>4100</x:v>
       </x:c>
       <x:c r="C25" s="0">
-        <x:v>63.2999992370606</x:v>
+        <x:v>63.4554885771216</x:v>
       </x:c>
       <x:c r="D25" s="0">
-        <x:v>586</x:v>
+        <x:v>4027</x:v>
       </x:c>
       <x:c r="E25" s="0">
-        <x:v>64.045306872996</x:v>
+        <x:v>63.6932960199546</x:v>
       </x:c>
       <x:c r="F25" s="0">
-        <x:v>786</x:v>
+        <x:v>8127</x:v>
       </x:c>
       <x:c r="G25" s="0">
-        <x:v>0.036534961075857</x:v>
+        <x:v>0.104851311628368</x:v>
       </x:c>
       <x:c r="H25" s="0">
-        <x:v>-386</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="I25" s="0">
-        <x:v>64.4314766325481</x:v>
+        <x:v>50.3369875868706</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:9">
@@ -1247,28 +1259,28 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="B26" s="0">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="C26" s="0">
+        <x:v>62.8499984741211</x:v>
+      </x:c>
+      <x:c r="D26" s="0">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C26" s="0">
+      <x:c r="E26" s="0">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D26" s="0">
-        <x:v>836</x:v>
-      </x:c>
-      <x:c r="E26" s="0">
-        <x:v>63.8083738117127</x:v>
-      </x:c>
       <x:c r="F26" s="0">
-        <x:v>836</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="G26" s="0">
-        <x:v>0.0388590680145247</x:v>
+        <x:v>0.000387048031112469</x:v>
       </x:c>
       <x:c r="H26" s="0">
-        <x:v>-836</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="I26" s="0">
-        <x:v>63.8083738117127</x:v>
+        <x:v>62.8499984741211</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:9">
@@ -1276,28 +1288,28 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="B27" s="0">
-        <x:v>0</x:v>
+        <x:v>4232</x:v>
       </x:c>
       <x:c r="C27" s="0">
-        <x:v>0</x:v>
+        <x:v>63.1412913902946</x:v>
       </x:c>
       <x:c r="D27" s="0">
-        <x:v>908</x:v>
+        <x:v>4240</x:v>
       </x:c>
       <x:c r="E27" s="0">
-        <x:v>63.3323781857932</x:v>
+        <x:v>63.1327831556212</x:v>
       </x:c>
       <x:c r="F27" s="0">
-        <x:v>908</x:v>
+        <x:v>8472</x:v>
       </x:c>
       <x:c r="G27" s="0">
-        <x:v>0.0422057820062063</x:v>
+        <x:v>0.109302363986161</x:v>
       </x:c>
       <x:c r="H27" s="0">
-        <x:v>-908</x:v>
+        <x:v>-8</x:v>
       </x:c>
       <x:c r="I27" s="0">
-        <x:v>63.3323781857932</x:v>
+        <x:v>58.6319270133972</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:9">
@@ -1305,28 +1317,28 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="B28" s="0">
-        <x:v>1535</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C28" s="0">
-        <x:v>63.7996735339833</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D28" s="0">
-        <x:v>3663</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E28" s="0">
-        <x:v>63.8229324971917</x:v>
+        <x:v>63.9000015258789</x:v>
       </x:c>
       <x:c r="F28" s="0">
-        <x:v>5198</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="G28" s="0">
-        <x:v>0.241614157343899</x:v>
+        <x:v>0.000322540025927057</x:v>
       </x:c>
       <x:c r="H28" s="0">
-        <x:v>-2128</x:v>
+        <x:v>-25</x:v>
       </x:c>
       <x:c r="I28" s="0">
-        <x:v>63.8397099917993</x:v>
+        <x:v>63.9000015258789</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:9">
@@ -1334,28 +1346,28 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B29" s="0">
-        <x:v>7104</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C29" s="0">
-        <x:v>63.3516392455445</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D29" s="0">
-        <x:v>9419</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="E29" s="0">
-        <x:v>64.2567250577492</x:v>
+        <x:v>63.5499992370606</x:v>
       </x:c>
       <x:c r="F29" s="0">
-        <x:v>16523</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G29" s="0">
-        <x:v>0.768024378952144</x:v>
+        <x:v>0.000361244829038304</x:v>
       </x:c>
       <x:c r="H29" s="0">
-        <x:v>-2315</x:v>
+        <x:v>-28</x:v>
       </x:c>
       <x:c r="I29" s="0">
-        <x:v>67.034146055547</x:v>
+        <x:v>63.5499992370606</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:9">
@@ -1363,28 +1375,28 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="B30" s="0">
-        <x:v>52</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C30" s="0">
-        <x:v>63.3384616558368</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D30" s="0">
-        <x:v>2693</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="E30" s="0">
-        <x:v>64.2374145941269</x:v>
+        <x:v>63.4500007629394</x:v>
       </x:c>
       <x:c r="F30" s="0">
-        <x:v>2745</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="G30" s="0">
-        <x:v>0.127593470932859</x:v>
+        <x:v>0.000696686456002444</x:v>
       </x:c>
       <x:c r="H30" s="0">
-        <x:v>-2641</x:v>
+        <x:v>-54</x:v>
       </x:c>
       <x:c r="I30" s="0">
-        <x:v>64.255114538387</x:v>
+        <x:v>63.4500007629394</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:9">
@@ -1392,28 +1404,28 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="B31" s="0">
-        <x:v>9164</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="C31" s="0">
-        <x:v>63.6931568480433</x:v>
+        <x:v>63.0686990691394</x:v>
       </x:c>
       <x:c r="D31" s="0">
-        <x:v>16746</x:v>
+        <x:v>361</x:v>
       </x:c>
       <x:c r="E31" s="0">
-        <x:v>63.7783944519364</x:v>
+        <x:v>63.1497223132865</x:v>
       </x:c>
       <x:c r="F31" s="0">
-        <x:v>25910</x:v>
+        <x:v>484</x:v>
       </x:c>
       <x:c r="G31" s="0">
-        <x:v>1.20435221561763</x:v>
+        <x:v>0.00624437490194783</x:v>
       </x:c>
       <x:c r="H31" s="0">
-        <x:v>-7582</x:v>
+        <x:v>-238</x:v>
       </x:c>
       <x:c r="I31" s="0">
-        <x:v>63.8814170583827</x:v>
+        <x:v>63.1915956705558</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:9">
@@ -1421,28 +1433,28 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="B32" s="0">
-        <x:v>8</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C32" s="0">
-        <x:v>63.2999992370606</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D32" s="0">
-        <x:v>10648</x:v>
+        <x:v>266</x:v>
       </x:c>
       <x:c r="E32" s="0">
-        <x:v>63.3043897469002</x:v>
+        <x:v>63.6218053487907</x:v>
       </x:c>
       <x:c r="F32" s="0">
-        <x:v>10656</x:v>
+        <x:v>266</x:v>
       </x:c>
       <x:c r="G32" s="0">
-        <x:v>0.49531367076887</x:v>
+        <x:v>0.00343182587586389</x:v>
       </x:c>
       <x:c r="H32" s="0">
-        <x:v>-10640</x:v>
+        <x:v>-266</x:v>
       </x:c>
       <x:c r="I32" s="0">
-        <x:v>63.3043930480355</x:v>
+        <x:v>63.6218053487907</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:9">
@@ -1450,28 +1462,28 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="B33" s="0">
-        <x:v>40148</x:v>
+        <x:v>802</x:v>
       </x:c>
       <x:c r="C33" s="0">
-        <x:v>63.2999992370606</x:v>
+        <x:v>63.0458238225923</x:v>
       </x:c>
       <x:c r="D33" s="0">
-        <x:v>52003</x:v>
+        <x:v>3542</x:v>
       </x:c>
       <x:c r="E33" s="0">
-        <x:v>63.973072971511</x:v>
+        <x:v>63.9427887083514</x:v>
       </x:c>
       <x:c r="F33" s="0">
-        <x:v>92151</x:v>
+        <x:v>4344</x:v>
       </x:c>
       <x:c r="G33" s="0">
-        <x:v>4.28337557010343</x:v>
+        <x:v>0.0560445549050855</x:v>
       </x:c>
       <x:c r="H33" s="0">
-        <x:v>-11855</x:v>
+        <x:v>-2740</x:v>
       </x:c>
       <x:c r="I33" s="0">
-        <x:v>66.2524963617023</x:v>
+        <x:v>64.2053309851319</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:9">
@@ -1479,28 +1491,28 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="B34" s="0">
-        <x:v>30627</x:v>
+        <x:v>14003</x:v>
       </x:c>
       <x:c r="C34" s="0">
-        <x:v>63.5960162063107</x:v>
+        <x:v>63.4647075146647</x:v>
       </x:c>
       <x:c r="D34" s="0">
-        <x:v>42580</x:v>
+        <x:v>17749</x:v>
       </x:c>
       <x:c r="E34" s="0">
-        <x:v>64.0517317773255</x:v>
+        <x:v>63.1074472414795</x:v>
       </x:c>
       <x:c r="F34" s="0">
-        <x:v>73207</x:v>
+        <x:v>31752</x:v>
       </x:c>
       <x:c r="G34" s="0">
-        <x:v>3.402817933181</x:v>
+        <x:v>0.409651636129437</x:v>
       </x:c>
       <x:c r="H34" s="0">
-        <x:v>-11953</x:v>
+        <x:v>-3746</x:v>
       </x:c>
       <x:c r="I34" s="0">
-        <x:v>65.2194052311423</x:v>
+        <x:v>61.7719652325599</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:9">
@@ -1508,28 +1520,28 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="B35" s="0">
-        <x:v>31617</x:v>
+        <x:v>38225</x:v>
       </x:c>
       <x:c r="C35" s="0">
-        <x:v>63.9338565797097</x:v>
+        <x:v>62.8486739521513</x:v>
       </x:c>
       <x:c r="D35" s="0">
-        <x:v>48891</x:v>
+        <x:v>46540</x:v>
       </x:c>
       <x:c r="E35" s="0">
-        <x:v>63.8689385114295</x:v>
+        <x:v>63.3151079008187</x:v>
       </x:c>
       <x:c r="F35" s="0">
-        <x:v>80508</x:v>
+        <x:v>84765</x:v>
       </x:c>
       <x:c r="G35" s="0">
-        <x:v>3.74218402836526</x:v>
+        <x:v>1.09360421190828</x:v>
       </x:c>
       <x:c r="H35" s="0">
-        <x:v>-17274</x:v>
+        <x:v>-8315</x:v>
       </x:c>
       <x:c r="I35" s="0">
-        <x:v>63.750117476069</x:v>
+        <x:v>65.4593577730749</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:9">
@@ -1537,28 +1549,28 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="B36" s="0">
-        <x:v>26498</x:v>
+        <x:v>15694</x:v>
       </x:c>
       <x:c r="C36" s="0">
-        <x:v>63.588955031205</x:v>
+        <x:v>63.3300175757352</x:v>
       </x:c>
       <x:c r="D36" s="0">
-        <x:v>45036</x:v>
+        <x:v>24160</x:v>
       </x:c>
       <x:c r="E36" s="0">
-        <x:v>63.3624715390008</x:v>
+        <x:v>62.9825953802526</x:v>
       </x:c>
       <x:c r="F36" s="0">
-        <x:v>71534</x:v>
+        <x:v>39854</x:v>
       </x:c>
       <x:c r="G36" s="0">
-        <x:v>3.32505331501317</x:v>
+        <x:v>0.514180407731878</x:v>
       </x:c>
       <x:c r="H36" s="0">
-        <x:v>-18538</x:v>
+        <x:v>-8466</x:v>
       </x:c>
       <x:c r="I36" s="0">
-        <x:v>63.038738688832</x:v>
+        <x:v>62.338555227181</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:9">
@@ -1566,28 +1578,28 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="B37" s="0">
-        <x:v>1520</x:v>
+        <x:v>23798</x:v>
       </x:c>
       <x:c r="C37" s="0">
-        <x:v>64.3436842014915</x:v>
+        <x:v>63.3218359143726</x:v>
       </x:c>
       <x:c r="D37" s="0">
-        <x:v>21335</x:v>
+        <x:v>33798</x:v>
       </x:c>
       <x:c r="E37" s="0">
-        <x:v>63.3744684665019</x:v>
+        <x:v>63.5754884139371</x:v>
       </x:c>
       <x:c r="F37" s="0">
-        <x:v>22855</x:v>
+        <x:v>57596</x:v>
       </x:c>
       <x:c r="G37" s="0">
-        <x:v>1.06234928166503</x:v>
+        <x:v>0.743080613331792</x:v>
       </x:c>
       <x:c r="H37" s="0">
-        <x:v>-19815</x:v>
+        <x:v>-10000</x:v>
       </x:c>
       <x:c r="I37" s="0">
-        <x:v>63.3001203505704</x:v>
+        <x:v>64.1791306324005</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:9">
@@ -1595,28 +1607,28 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="B38" s="0">
-        <x:v>11966</x:v>
+        <x:v>91666</x:v>
       </x:c>
       <x:c r="C38" s="0">
-        <x:v>63.430585705953</x:v>
+        <x:v>63.2124327734369</x:v>
       </x:c>
       <x:c r="D38" s="0">
-        <x:v>39323</x:v>
+        <x:v>104008</x:v>
       </x:c>
       <x:c r="E38" s="0">
-        <x:v>63.3413134771019</x:v>
+        <x:v>63.1110888212225</x:v>
       </x:c>
       <x:c r="F38" s="0">
-        <x:v>51289</x:v>
+        <x:v>195674</x:v>
       </x:c>
       <x:c r="G38" s="0">
-        <x:v>2.3840224155466</x:v>
+        <x:v>2.52450788133004</x:v>
       </x:c>
       <x:c r="H38" s="0">
-        <x:v>-27357</x:v>
+        <x:v>-12342</x:v>
       </x:c>
       <x:c r="I38" s="0">
-        <x:v>63.3022656469146</x:v>
+        <x:v>62.3583911446964</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:9">
@@ -1624,28 +1636,28 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="B39" s="0">
-        <x:v>42478</x:v>
+        <x:v>175287</x:v>
       </x:c>
       <x:c r="C39" s="0">
-        <x:v>63.9747366585285</x:v>
+        <x:v>63.2614915483222</x:v>
       </x:c>
       <x:c r="D39" s="0">
-        <x:v>70284</x:v>
+        <x:v>188065</x:v>
       </x:c>
       <x:c r="E39" s="0">
-        <x:v>63.5330249109453</x:v>
+        <x:v>63.1191690633942</x:v>
       </x:c>
       <x:c r="F39" s="0">
-        <x:v>112762</x:v>
+        <x:v>363352</x:v>
       </x:c>
       <x:c r="G39" s="0">
-        <x:v>5.24141893236105</x:v>
+        <x:v>4.68782254002593</x:v>
       </x:c>
       <x:c r="H39" s="0">
-        <x:v>-27806</x:v>
+        <x:v>-12778</x:v>
       </x:c>
       <x:c r="I39" s="0">
-        <x:v>62.858241352942</x:v>
+        <x:v>61.1668070806437</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:9">
@@ -1653,28 +1665,28 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="B40" s="0">
-        <x:v>2055</x:v>
+        <x:v>3410</x:v>
       </x:c>
       <x:c r="C40" s="0">
-        <x:v>63.2999992370606</x:v>
+        <x:v>62.7608064612336</x:v>
       </x:c>
       <x:c r="D40" s="0">
-        <x:v>38638</x:v>
+        <x:v>18111</x:v>
       </x:c>
       <x:c r="E40" s="0">
-        <x:v>63.3648641892265</x:v>
+        <x:v>63.3985673206079</x:v>
       </x:c>
       <x:c r="F40" s="0">
-        <x:v>40693</x:v>
+        <x:v>21521</x:v>
       </x:c>
       <x:c r="G40" s="0">
-        <x:v>1.89149767310413</x:v>
+        <x:v>0.277655355919048</x:v>
       </x:c>
       <x:c r="H40" s="0">
-        <x:v>-36583</x:v>
+        <x:v>-14701</x:v>
       </x:c>
       <x:c r="I40" s="0">
-        <x:v>63.3685078892156</x:v>
+        <x:v>63.5465004224695</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:9">
@@ -1682,28 +1694,28 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="B41" s="0">
-        <x:v>14244</x:v>
+        <x:v>27894</x:v>
       </x:c>
       <x:c r="C41" s="0">
-        <x:v>63.7424148427272</x:v>
+        <x:v>62.8231762610961</x:v>
       </x:c>
       <x:c r="D41" s="0">
-        <x:v>85474</x:v>
+        <x:v>46861</x:v>
       </x:c>
       <x:c r="E41" s="0">
-        <x:v>63.9766162568206</x:v>
+        <x:v>63.4029718838917</x:v>
       </x:c>
       <x:c r="F41" s="0">
-        <x:v>99718</x:v>
+        <x:v>74755</x:v>
       </x:c>
       <x:c r="G41" s="0">
-        <x:v>4.63510591420141</x:v>
+        <x:v>0.964459185527087</x:v>
       </x:c>
       <x:c r="H41" s="0">
-        <x:v>-71230</x:v>
+        <x:v>-18967</x:v>
       </x:c>
       <x:c r="I41" s="0">
-        <x:v>64.0234499637187</x:v>
+        <x:v>64.255653863238</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:9">
@@ -1711,28 +1723,28 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="B42" s="0">
-        <x:v>7250</x:v>
+        <x:v>80671</x:v>
       </x:c>
       <x:c r="C42" s="0">
-        <x:v>64.0978062649431</x:v>
+        <x:v>62.825925062796</x:v>
       </x:c>
       <x:c r="D42" s="0">
-        <x:v>95471</x:v>
+        <x:v>104452</x:v>
       </x:c>
       <x:c r="E42" s="0">
-        <x:v>63.8923624957718</x:v>
+        <x:v>63.8066862427928</x:v>
       </x:c>
       <x:c r="F42" s="0">
-        <x:v>102721</x:v>
+        <x:v>185123</x:v>
       </x:c>
       <x:c r="G42" s="0">
-        <x:v>4.77469177693779</x:v>
+        <x:v>2.38838308878779</x:v>
       </x:c>
       <x:c r="H42" s="0">
-        <x:v>-88221</x:v>
+        <x:v>-23781</x:v>
       </x:c>
       <x:c r="I42" s="0">
-        <x:v>63.8754791309665</x:v>
+        <x:v>67.133669344913</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:9">
@@ -1740,28 +1752,144 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="B43" s="0">
-        <x:v>3761</x:v>
+        <x:v>729560</x:v>
       </x:c>
       <x:c r="C43" s="0">
-        <x:v>64.2945467627641</x:v>
+        <x:v>63.1685757629704</x:v>
       </x:c>
       <x:c r="D43" s="0">
-        <x:v>205242</x:v>
+        <x:v>757345</x:v>
       </x:c>
       <x:c r="E43" s="0">
-        <x:v>64.0542472310723</x:v>
+        <x:v>63.1723212645868</x:v>
       </x:c>
       <x:c r="F43" s="0">
-        <x:v>209003</x:v>
+        <x:v>1486905</x:v>
       </x:c>
       <x:c r="G43" s="0">
-        <x:v>9.7149064500475</x:v>
+        <x:v>19.1834550900429</x:v>
       </x:c>
       <x:c r="H43" s="0">
-        <x:v>-201481</x:v>
+        <x:v>-27785</x:v>
       </x:c>
       <x:c r="I43" s="0">
-        <x:v>64.0497616143705</x:v>
+        <x:v>63.2706681481321</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44" spans="1:9">
+      <x:c r="A44" s="0" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="B44" s="0">
+        <x:v>40194</x:v>
+      </x:c>
+      <x:c r="C44" s="0">
+        <x:v>63.330010380384</x:v>
+      </x:c>
+      <x:c r="D44" s="0">
+        <x:v>80369</x:v>
+      </x:c>
+      <x:c r="E44" s="0">
+        <x:v>63.2915514798238</x:v>
+      </x:c>
+      <x:c r="F44" s="0">
+        <x:v>120563</x:v>
+      </x:c>
+      <x:c r="G44" s="0">
+        <x:v>1.55545572583375</x:v>
+      </x:c>
+      <x:c r="H44" s="0">
+        <x:v>-40175</x:v>
+      </x:c>
+      <x:c r="I44" s="0">
+        <x:v>63.25307439086</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45" spans="1:9">
+      <x:c r="A45" s="0" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="B45" s="0">
+        <x:v>120686</x:v>
+      </x:c>
+      <x:c r="C45" s="0">
+        <x:v>63.3018862337085</x:v>
+      </x:c>
+      <x:c r="D45" s="0">
+        <x:v>169834</x:v>
+      </x:c>
+      <x:c r="E45" s="0">
+        <x:v>63.4257738025198</x:v>
+      </x:c>
+      <x:c r="F45" s="0">
+        <x:v>290520</x:v>
+      </x:c>
+      <x:c r="G45" s="0">
+        <x:v>3.74817313329315</x:v>
+      </x:c>
+      <x:c r="H45" s="0">
+        <x:v>-49148</x:v>
+      </x:c>
+      <x:c r="I45" s="0">
+        <x:v>63.729987506629</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46" spans="1:9">
+      <x:c r="A46" s="0" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="B46" s="0">
+        <x:v>101340</x:v>
+      </x:c>
+      <x:c r="C46" s="0">
+        <x:v>63.292554233228</x:v>
+      </x:c>
+      <x:c r="D46" s="0">
+        <x:v>161344</x:v>
+      </x:c>
+      <x:c r="E46" s="0">
+        <x:v>63.1768815527356</x:v>
+      </x:c>
+      <x:c r="F46" s="0">
+        <x:v>262684</x:v>
+      </x:c>
+      <x:c r="G46" s="0">
+        <x:v>3.38904416682493</x:v>
+      </x:c>
+      <x:c r="H46" s="0">
+        <x:v>-60004</x:v>
+      </x:c>
+      <x:c r="I46" s="0">
+        <x:v>62.9815234192593</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47" spans="1:9">
+      <x:c r="A47" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="B47" s="0">
+        <x:v>54740</x:v>
+      </x:c>
+      <x:c r="C47" s="0">
+        <x:v>63.1334518348295</x:v>
+      </x:c>
+      <x:c r="D47" s="0">
+        <x:v>330303</x:v>
+      </x:c>
+      <x:c r="E47" s="0">
+        <x:v>63.7499287921676</x:v>
+      </x:c>
+      <x:c r="F47" s="0">
+        <x:v>385043</x:v>
+      </x:c>
+      <x:c r="G47" s="0">
+        <x:v>4.96767116812128</x:v>
+      </x:c>
+      <x:c r="H47" s="0">
+        <x:v>-275563</x:v>
+      </x:c>
+      <x:c r="I47" s="0">
+        <x:v>63.8723906199336</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/app/fonlar/haftalik-yatirim-fonlarinin-en-cok-tercih-ettigi-hisseler/data/tercih-edilen-hisseler.xlsx
+++ b/app/fonlar/haftalik-yatirim-fonlarinin-en-cok-tercih-ettigi-hisseler/data/tercih-edilen-hisseler.xlsx
@@ -43,139 +43,145 @@
     <x:t>GEDIK</x:t>
   </x:si>
   <x:si>
+    <x:t>BANK OF AMERICA</x:t>
+  </x:si>
+  <x:si>
     <x:t>IS</x:t>
   </x:si>
   <x:si>
+    <x:t>IKON</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MIDAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>YAPI KREDI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ZIRAAT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TACIRLER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TEB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VAKIF</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UNLU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BURGAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DENIZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRIVE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SEKER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BTCTURK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALNUS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ICBC TURKEY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TERA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALTERNATIF</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FIBA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DESTEK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIZIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ACAR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DINAMIK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HSBC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ANADOLU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INVEST AZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HALK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BULLS YATIRIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AHLATCI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ING</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INTEGRAL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PHILLIP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ATA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INFO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GLOBAL</x:t>
+  </x:si>
+  <x:si>
     <x:t>PUSULA YAT.</x:t>
   </x:si>
   <x:si>
-    <x:t>MIDAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ZIRAAT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>YAPI KREDI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INFO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TACIRLER</x:t>
+    <x:t>AK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OYAK</x:t>
   </x:si>
   <x:si>
     <x:t>OSMANLI</x:t>
   </x:si>
   <x:si>
-    <x:t>TEB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALNUS</x:t>
+    <x:t>GARANTI BBVA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MEKSA</x:t>
   </x:si>
   <x:si>
     <x:t>A1 CAPITAL</x:t>
   </x:si>
   <x:si>
+    <x:t>QNB YATIRIM</x:t>
+  </x:si>
+  <x:si>
     <x:t>KUVEYT TURK</x:t>
   </x:si>
   <x:si>
-    <x:t>SEKER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BTCTURK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FIBA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ACAR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TERA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TRIVE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UNLU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ANADOLU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BULLS YATIRIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INVEST AZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ICBC TURKEY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DINAMIK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BURGAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIZIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INTEGRAL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALTERNATIF</x:t>
+    <x:t>MARBAS</x:t>
   </x:si>
   <x:si>
     <x:t>YATIRIM FINANSMAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HSBC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AHLATCI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ING</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PHILLIP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GLOBAL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IKON</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HALK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VAKIF</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ATA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MEKSA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>QNB YATIRIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OYAK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DENIZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GARANTI BBVA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MARBAS</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -526,7 +532,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:I47"/>
+  <x:dimension ref="A1:I49"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:9">
@@ -563,28 +569,28 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B2" s="0">
-        <x:v>207173</x:v>
+        <x:v>595609</x:v>
       </x:c>
       <x:c r="C2" s="0">
-        <x:v>63.5415233125163</x:v>
+        <x:v>64.597</x:v>
       </x:c>
       <x:c r="D2" s="0">
-        <x:v>98426</x:v>
+        <x:v>303573</x:v>
       </x:c>
       <x:c r="E2" s="0">
-        <x:v>63.1717836531816</x:v>
+        <x:v>64.238</x:v>
       </x:c>
       <x:c r="F2" s="0">
-        <x:v>305599</x:v>
+        <x:v>899182</x:v>
       </x:c>
       <x:c r="G2" s="0">
-        <x:v>3.94271637533131</x:v>
+        <x:v>4.38451268618217</x:v>
       </x:c>
       <x:c r="H2" s="0">
-        <x:v>108747</x:v>
+        <x:v>292036</x:v>
       </x:c>
       <x:c r="I2" s="0">
-        <x:v>63.8761715852013</x:v>
+        <x:v>64.97</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:9">
@@ -592,28 +598,28 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B3" s="0">
-        <x:v>526033</x:v>
+        <x:v>215896</x:v>
       </x:c>
       <x:c r="C3" s="0">
-        <x:v>63.2202920568709</x:v>
+        <x:v>65.619</x:v>
       </x:c>
       <x:c r="D3" s="0">
-        <x:v>438161</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E3" s="0">
-        <x:v>63.0988508692517</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F3" s="0">
-        <x:v>964194</x:v>
+        <x:v>215896</x:v>
       </x:c>
       <x:c r="G3" s="0">
-        <x:v>12.4396463103485</x:v>
+        <x:v>1.0527332073996</x:v>
       </x:c>
       <x:c r="H3" s="0">
-        <x:v>87872</x:v>
+        <x:v>215896</x:v>
       </x:c>
       <x:c r="I3" s="0">
-        <x:v>63.8258409485362</x:v>
+        <x:v>65.619</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:9">
@@ -621,28 +627,28 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B4" s="0">
-        <x:v>109797</x:v>
+        <x:v>1077775</x:v>
       </x:c>
       <x:c r="C4" s="0">
-        <x:v>63.3649725677096</x:v>
+        <x:v>64.079</x:v>
       </x:c>
       <x:c r="D4" s="0">
-        <x:v>43732</x:v>
+        <x:v>956750</x:v>
       </x:c>
       <x:c r="E4" s="0">
-        <x:v>63.6223980803225</x:v>
+        <x:v>64.188</x:v>
       </x:c>
       <x:c r="F4" s="0">
-        <x:v>153529</x:v>
+        <x:v>2034525</x:v>
       </x:c>
       <x:c r="G4" s="0">
-        <x:v>1.98076990562221</x:v>
+        <x:v>9.92057300174467</x:v>
       </x:c>
       <x:c r="H4" s="0">
-        <x:v>66065</x:v>
+        <x:v>121025</x:v>
       </x:c>
       <x:c r="I4" s="0">
-        <x:v>63.1945686849035</x:v>
+        <x:v>63.225</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:9">
@@ -650,28 +656,28 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B5" s="0">
-        <x:v>249690</x:v>
+        <x:v>415812</x:v>
       </x:c>
       <x:c r="C5" s="0">
-        <x:v>63.2518870349306</x:v>
+        <x:v>65.308</x:v>
       </x:c>
       <x:c r="D5" s="0">
-        <x:v>188256</x:v>
+        <x:v>310738</x:v>
       </x:c>
       <x:c r="E5" s="0">
-        <x:v>63.1686078629768</x:v>
+        <x:v>65.303</x:v>
       </x:c>
       <x:c r="F5" s="0">
-        <x:v>437946</x:v>
+        <x:v>726550</x:v>
       </x:c>
       <x:c r="G5" s="0">
-        <x:v>5.65020456778604</x:v>
+        <x:v>3.54273961461156</x:v>
       </x:c>
       <x:c r="H5" s="0">
-        <x:v>61434</x:v>
+        <x:v>105074</x:v>
       </x:c>
       <x:c r="I5" s="0">
-        <x:v>63.5070845443771</x:v>
+        <x:v>65.323</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:9">
@@ -679,28 +685,28 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B6" s="0">
-        <x:v>277677</x:v>
+        <x:v>600132</x:v>
       </x:c>
       <x:c r="C6" s="0">
-        <x:v>63.4179685011106</x:v>
+        <x:v>64.262</x:v>
       </x:c>
       <x:c r="D6" s="0">
-        <x:v>231920</x:v>
+        <x:v>495914</x:v>
       </x:c>
       <x:c r="E6" s="0">
-        <x:v>63.1841199488013</x:v>
+        <x:v>64.166</x:v>
       </x:c>
       <x:c r="F6" s="0">
-        <x:v>509597</x:v>
+        <x:v>1096046</x:v>
       </x:c>
       <x:c r="G6" s="0">
-        <x:v>6.57461718369403</x:v>
+        <x:v>5.34444371844546</x:v>
       </x:c>
       <x:c r="H6" s="0">
-        <x:v>45757</x:v>
+        <x:v>104218</x:v>
       </x:c>
       <x:c r="I6" s="0">
-        <x:v>64.6032331874222</x:v>
+        <x:v>64.722</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:9">
@@ -708,28 +714,28 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="B7" s="0">
-        <x:v>202039</x:v>
+        <x:v>870161</x:v>
       </x:c>
       <x:c r="C7" s="0">
-        <x:v>63.418724243242</x:v>
+        <x:v>64.818</x:v>
       </x:c>
       <x:c r="D7" s="0">
-        <x:v>165074</x:v>
+        <x:v>770988</x:v>
       </x:c>
       <x:c r="E7" s="0">
-        <x:v>63.343316386287</x:v>
+        <x:v>64.798</x:v>
       </x:c>
       <x:c r="F7" s="0">
-        <x:v>367113</x:v>
+        <x:v>1641149</x:v>
       </x:c>
       <x:c r="G7" s="0">
-        <x:v>4.73634546152639</x:v>
+        <x:v>8.00242732885576</x:v>
       </x:c>
       <x:c r="H7" s="0">
-        <x:v>36965</x:v>
+        <x:v>99173</x:v>
       </x:c>
       <x:c r="I7" s="0">
-        <x:v>63.7554718850382</x:v>
+        <x:v>64.977</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:9">
@@ -737,28 +743,28 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B8" s="0">
-        <x:v>107659</x:v>
+        <x:v>700517</x:v>
       </x:c>
       <x:c r="C8" s="0">
-        <x:v>63.1242408176298</x:v>
+        <x:v>64.386</x:v>
       </x:c>
       <x:c r="D8" s="0">
-        <x:v>80868</x:v>
+        <x:v>611686</x:v>
       </x:c>
       <x:c r="E8" s="0">
-        <x:v>63.6446985627409</x:v>
+        <x:v>64.45</x:v>
       </x:c>
       <x:c r="F8" s="0">
-        <x:v>188527</x:v>
+        <x:v>1312203</x:v>
       </x:c>
       <x:c r="G8" s="0">
-        <x:v>2.43230013871801</x:v>
+        <x:v>6.39844959123548</x:v>
       </x:c>
       <x:c r="H8" s="0">
-        <x:v>26791</x:v>
+        <x:v>88831</x:v>
       </x:c>
       <x:c r="I8" s="0">
-        <x:v>61.5532514207561</x:v>
+        <x:v>63.943</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:9">
@@ -766,28 +772,28 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="B9" s="0">
-        <x:v>105630</x:v>
+        <x:v>363988</x:v>
       </x:c>
       <x:c r="C9" s="0">
-        <x:v>63.3534532095394</x:v>
+        <x:v>64.629</x:v>
       </x:c>
       <x:c r="D9" s="0">
-        <x:v>82351</x:v>
+        <x:v>279109</x:v>
       </x:c>
       <x:c r="E9" s="0">
-        <x:v>63.6116941446259</x:v>
+        <x:v>64.513</x:v>
       </x:c>
       <x:c r="F9" s="0">
-        <x:v>187981</x:v>
+        <x:v>643097</x:v>
       </x:c>
       <x:c r="G9" s="0">
-        <x:v>2.42525586455177</x:v>
+        <x:v>3.13581338922009</x:v>
       </x:c>
       <x:c r="H9" s="0">
-        <x:v>23279</x:v>
+        <x:v>84879</x:v>
       </x:c>
       <x:c r="I9" s="0">
-        <x:v>62.439908845722</x:v>
+        <x:v>65.009</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:9">
@@ -795,28 +801,28 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B10" s="0">
-        <x:v>57483</x:v>
+        <x:v>67930</x:v>
       </x:c>
       <x:c r="C10" s="0">
-        <x:v>63.3503271413845</x:v>
+        <x:v>64.771</x:v>
       </x:c>
       <x:c r="D10" s="0">
-        <x:v>34294</x:v>
+        <x:v>20607</x:v>
       </x:c>
       <x:c r="E10" s="0">
-        <x:v>63.4918703762318</x:v>
+        <x:v>64.477</x:v>
       </x:c>
       <x:c r="F10" s="0">
-        <x:v>91777</x:v>
+        <x:v>88537</x:v>
       </x:c>
       <x:c r="G10" s="0">
-        <x:v>1.1840702383803</x:v>
+        <x:v>0.431716381885437</x:v>
       </x:c>
       <x:c r="H10" s="0">
-        <x:v>23189</x:v>
+        <x:v>47323</x:v>
       </x:c>
       <x:c r="I10" s="0">
-        <x:v>63.1410001460051</x:v>
+        <x:v>64.899</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:9">
@@ -824,28 +830,28 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B11" s="0">
-        <x:v>23060</x:v>
+        <x:v>422452</x:v>
       </x:c>
       <x:c r="C11" s="0">
-        <x:v>63.4956591145432</x:v>
+        <x:v>64.414</x:v>
       </x:c>
       <x:c r="D11" s="0">
-        <x:v>6094</x:v>
+        <x:v>389937</x:v>
       </x:c>
       <x:c r="E11" s="0">
-        <x:v>63.1403515655798</x:v>
+        <x:v>64.149</x:v>
       </x:c>
       <x:c r="F11" s="0">
-        <x:v>29154</x:v>
+        <x:v>812389</x:v>
       </x:c>
       <x:c r="G11" s="0">
-        <x:v>0.376133276635097</x:v>
+        <x:v>3.96130024468333</x:v>
       </x:c>
       <x:c r="H11" s="0">
-        <x:v>16966</x:v>
+        <x:v>32515</x:v>
       </x:c>
       <x:c r="I11" s="0">
-        <x:v>63.6232816657269</x:v>
+        <x:v>67.591</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:9">
@@ -853,28 +859,28 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="B12" s="0">
-        <x:v>32211</x:v>
+        <x:v>40373</x:v>
       </x:c>
       <x:c r="C12" s="0">
-        <x:v>63.3112678768242</x:v>
+        <x:v>64.421</x:v>
       </x:c>
       <x:c r="D12" s="0">
-        <x:v>16655</x:v>
+        <x:v>15441</x:v>
       </x:c>
       <x:c r="E12" s="0">
-        <x:v>63.2830428566384</x:v>
+        <x:v>63.56</x:v>
       </x:c>
       <x:c r="F12" s="0">
-        <x:v>48866</x:v>
+        <x:v>55814</x:v>
       </x:c>
       <x:c r="G12" s="0">
-        <x:v>0.630449636278064</x:v>
+        <x:v>0.272155349046769</x:v>
       </x:c>
       <x:c r="H12" s="0">
-        <x:v>15556</x:v>
+        <x:v>24932</x:v>
       </x:c>
       <x:c r="I12" s="0">
-        <x:v>63.3414869377134</x:v>
+        <x:v>64.955</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:9">
@@ -882,28 +888,28 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B13" s="0">
-        <x:v>295810</x:v>
+        <x:v>49368</x:v>
       </x:c>
       <x:c r="C13" s="0">
-        <x:v>63.7801573385086</x:v>
+        <x:v>64.451</x:v>
       </x:c>
       <x:c r="D13" s="0">
-        <x:v>283396</x:v>
+        <x:v>28858</x:v>
       </x:c>
       <x:c r="E13" s="0">
-        <x:v>63.1751105471905</x:v>
+        <x:v>65.064</x:v>
       </x:c>
       <x:c r="F13" s="0">
-        <x:v>579206</x:v>
+        <x:v>78226</x:v>
       </x:c>
       <x:c r="G13" s="0">
-        <x:v>7.47268473028429</x:v>
+        <x:v>0.381438784794721</x:v>
       </x:c>
       <x:c r="H13" s="0">
-        <x:v>12414</x:v>
+        <x:v>20510</x:v>
       </x:c>
       <x:c r="I13" s="0">
-        <x:v>77.5926142800578</x:v>
+        <x:v>63.588</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:9">
@@ -911,28 +917,28 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="B14" s="0">
-        <x:v>14228</x:v>
+        <x:v>391419</x:v>
       </x:c>
       <x:c r="C14" s="0">
-        <x:v>63.4620916684558</x:v>
+        <x:v>64.446</x:v>
       </x:c>
       <x:c r="D14" s="0">
-        <x:v>5668</x:v>
+        <x:v>381045</x:v>
       </x:c>
       <x:c r="E14" s="0">
-        <x:v>63.1116178299898</x:v>
+        <x:v>64.403</x:v>
       </x:c>
       <x:c r="F14" s="0">
-        <x:v>19896</x:v>
+        <x:v>772464</x:v>
       </x:c>
       <x:c r="G14" s="0">
-        <x:v>0.256690254233789</x:v>
+        <x:v>3.76662144884909</x:v>
       </x:c>
       <x:c r="H14" s="0">
-        <x:v>8560</x:v>
+        <x:v>10374</x:v>
       </x:c>
       <x:c r="I14" s="0">
-        <x:v>63.6941577568232</x:v>
+        <x:v>66.022</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:9">
@@ -940,28 +946,28 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B15" s="0">
-        <x:v>7815</x:v>
+        <x:v>28686</x:v>
       </x:c>
       <x:c r="C15" s="0">
-        <x:v>63.3483179733071</x:v>
+        <x:v>64.643</x:v>
       </x:c>
       <x:c r="D15" s="0">
-        <x:v>228</x:v>
+        <x:v>21035</x:v>
       </x:c>
       <x:c r="E15" s="0">
-        <x:v>63.5151311974776</x:v>
+        <x:v>64.983</x:v>
       </x:c>
       <x:c r="F15" s="0">
-        <x:v>8043</x:v>
+        <x:v>49721</x:v>
       </x:c>
       <x:c r="G15" s="0">
-        <x:v>0.103767577141253</x:v>
+        <x:v>0.242445194932354</x:v>
       </x:c>
       <x:c r="H15" s="0">
-        <x:v>7587</x:v>
+        <x:v>7651</x:v>
       </x:c>
       <x:c r="I15" s="0">
-        <x:v>63.3433050017623</x:v>
+        <x:v>63.709</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:9">
@@ -969,28 +975,28 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B16" s="0">
-        <x:v>11734</x:v>
+        <x:v>61599</x:v>
       </x:c>
       <x:c r="C16" s="0">
-        <x:v>63.2832403035064</x:v>
+        <x:v>64.115</x:v>
       </x:c>
       <x:c r="D16" s="0">
-        <x:v>4480</x:v>
+        <x:v>56655</x:v>
       </x:c>
       <x:c r="E16" s="0">
-        <x:v>62.9678683613028</x:v>
+        <x:v>64.543</x:v>
       </x:c>
       <x:c r="F16" s="0">
-        <x:v>16214</x:v>
+        <x:v>118254</x:v>
       </x:c>
       <x:c r="G16" s="0">
-        <x:v>0.209186559215252</x:v>
+        <x:v>0.57661982022748</x:v>
       </x:c>
       <x:c r="H16" s="0">
-        <x:v>7254</x:v>
+        <x:v>4944</x:v>
       </x:c>
       <x:c r="I16" s="0">
-        <x:v>63.4780109543297</x:v>
+        <x:v>59.219</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:9">
@@ -998,28 +1004,28 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B17" s="0">
-        <x:v>8180</x:v>
+        <x:v>23596</x:v>
       </x:c>
       <x:c r="C17" s="0">
-        <x:v>63.5262406514734</x:v>
+        <x:v>64.311</x:v>
       </x:c>
       <x:c r="D17" s="0">
-        <x:v>1338</x:v>
+        <x:v>19015</x:v>
       </x:c>
       <x:c r="E17" s="0">
-        <x:v>63.2597522051345</x:v>
+        <x:v>64.246</x:v>
       </x:c>
       <x:c r="F17" s="0">
-        <x:v>9518</x:v>
+        <x:v>42611</x:v>
       </x:c>
       <x:c r="G17" s="0">
-        <x:v>0.122797438670949</x:v>
+        <x:v>0.207776034296626</x:v>
       </x:c>
       <x:c r="H17" s="0">
-        <x:v>6842</x:v>
+        <x:v>4581</x:v>
       </x:c>
       <x:c r="I17" s="0">
-        <x:v>63.5783542938589</x:v>
+        <x:v>64.58</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:9">
@@ -1027,28 +1033,28 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B18" s="0">
-        <x:v>18000</x:v>
+        <x:v>81506</x:v>
       </x:c>
       <x:c r="C18" s="0">
-        <x:v>63.5458335876465</x:v>
+        <x:v>64.422</x:v>
       </x:c>
       <x:c r="D18" s="0">
-        <x:v>13900</x:v>
+        <x:v>77209</x:v>
       </x:c>
       <x:c r="E18" s="0">
-        <x:v>63.7091046930217</x:v>
+        <x:v>64.552</x:v>
       </x:c>
       <x:c r="F18" s="0">
-        <x:v>31900</x:v>
+        <x:v>158715</x:v>
       </x:c>
       <x:c r="G18" s="0">
-        <x:v>0.411561073082925</x:v>
+        <x:v>0.773912212419069</x:v>
       </x:c>
       <x:c r="H18" s="0">
-        <x:v>4100</x:v>
+        <x:v>4297</x:v>
       </x:c>
       <x:c r="I18" s="0">
-        <x:v>62.9923047182037</x:v>
+        <x:v>62.084</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:9">
@@ -1056,28 +1062,28 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B19" s="0">
-        <x:v>70748</x:v>
+        <x:v>8170</x:v>
       </x:c>
       <x:c r="C19" s="0">
-        <x:v>63.0085425625731</x:v>
+        <x:v>64.789</x:v>
       </x:c>
       <x:c r="D19" s="0">
-        <x:v>67030</x:v>
+        <x:v>4742</x:v>
       </x:c>
       <x:c r="E19" s="0">
-        <x:v>63.8711906514487</x:v>
+        <x:v>64.054</x:v>
       </x:c>
       <x:c r="F19" s="0">
-        <x:v>137778</x:v>
+        <x:v>12912</x:v>
       </x:c>
       <x:c r="G19" s="0">
-        <x:v>1.77755678768712</x:v>
+        <x:v>0.0629603659815078</x:v>
       </x:c>
       <x:c r="H19" s="0">
-        <x:v>3718</x:v>
+        <x:v>3428</x:v>
       </x:c>
       <x:c r="I19" s="0">
-        <x:v>47.4562829075609</x:v>
+        <x:v>65.806</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:9">
@@ -1085,28 +1091,28 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="B20" s="0">
-        <x:v>5524</x:v>
+        <x:v>104191</x:v>
       </x:c>
       <x:c r="C20" s="0">
-        <x:v>63.2452845148726</x:v>
+        <x:v>63.938</x:v>
       </x:c>
       <x:c r="D20" s="0">
-        <x:v>1980</x:v>
+        <x:v>101853</x:v>
       </x:c>
       <x:c r="E20" s="0">
-        <x:v>63.3769440005524</x:v>
+        <x:v>64.39</x:v>
       </x:c>
       <x:c r="F20" s="0">
-        <x:v>7504</x:v>
+        <x:v>206044</x:v>
       </x:c>
       <x:c r="G20" s="0">
-        <x:v>0.0968136141822656</x:v>
+        <x:v>1.00469374599549</x:v>
       </x:c>
       <x:c r="H20" s="0">
-        <x:v>3544</x:v>
+        <x:v>2338</x:v>
       </x:c>
       <x:c r="I20" s="0">
-        <x:v>63.1717275787422</x:v>
+        <x:v>44.25</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:9">
@@ -1114,28 +1120,28 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="B21" s="0">
-        <x:v>16163</x:v>
+        <x:v>600</x:v>
       </x:c>
       <x:c r="C21" s="0">
-        <x:v>63.4795061852653</x:v>
+        <x:v>65.3</x:v>
       </x:c>
       <x:c r="D21" s="0">
-        <x:v>15284</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="E21" s="0">
-        <x:v>63.5477559389915</x:v>
+        <x:v>63.444</x:v>
       </x:c>
       <x:c r="F21" s="0">
-        <x:v>31447</x:v>
+        <x:v>654</x:v>
       </x:c>
       <x:c r="G21" s="0">
-        <x:v>0.405716647813127</x:v>
+        <x:v>0.00318897764497414</x:v>
       </x:c>
       <x:c r="H21" s="0">
-        <x:v>879</x:v>
+        <x:v>546</x:v>
       </x:c>
       <x:c r="I21" s="0">
-        <x:v>62.2927835050025</x:v>
+        <x:v>65.484</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:9">
@@ -1143,28 +1149,28 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="B22" s="0">
-        <x:v>717</x:v>
+        <x:v>11722</x:v>
       </x:c>
       <x:c r="C22" s="0">
-        <x:v>62.5</x:v>
+        <x:v>64.031</x:v>
       </x:c>
       <x:c r="D22" s="0">
-        <x:v>0</x:v>
+        <x:v>11290</x:v>
       </x:c>
       <x:c r="E22" s="0">
-        <x:v>0</x:v>
+        <x:v>64.941</x:v>
       </x:c>
       <x:c r="F22" s="0">
-        <x:v>717</x:v>
+        <x:v>23012</x:v>
       </x:c>
       <x:c r="G22" s="0">
-        <x:v>0.00925044794358801</x:v>
+        <x:v>0.112209103312148</x:v>
       </x:c>
       <x:c r="H22" s="0">
-        <x:v>717</x:v>
+        <x:v>432</x:v>
       </x:c>
       <x:c r="I22" s="0">
-        <x:v>62.5</x:v>
+        <x:v>40.269</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:9">
@@ -1172,28 +1178,28 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="B23" s="0">
-        <x:v>562</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C23" s="0">
-        <x:v>62.6010688700286</x:v>
+        <x:v>66.14</x:v>
       </x:c>
       <x:c r="D23" s="0">
-        <x:v>35</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E23" s="0">
-        <x:v>63.2314279828753</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F23" s="0">
-        <x:v>597</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="G23" s="0">
-        <x:v>0.00770225581913813</x:v>
+        <x:v>0.000243805630349705</x:v>
       </x:c>
       <x:c r="H23" s="0">
-        <x:v>527</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="I23" s="0">
-        <x:v>62.5592044128186</x:v>
+        <x:v>66.14</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:9">
@@ -1201,28 +1207,28 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="B24" s="0">
-        <x:v>1100</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C24" s="0">
-        <x:v>62.6863642605868</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D24" s="0">
-        <x:v>836</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E24" s="0">
-        <x:v>63.8083738117127</x:v>
+        <x:v>63.92</x:v>
       </x:c>
       <x:c r="F24" s="0">
-        <x:v>1936</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="G24" s="0">
-        <x:v>0.0249774996077913</x:v>
+        <x:v>0.000121902815174853</x:v>
       </x:c>
       <x:c r="H24" s="0">
-        <x:v>264</x:v>
+        <x:v>-25</x:v>
       </x:c>
       <x:c r="I24" s="0">
-        <x:v>59.133334015355</x:v>
+        <x:v>63.92</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:9">
@@ -1230,28 +1236,28 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="B25" s="0">
-        <x:v>4100</x:v>
+        <x:v>47129</x:v>
       </x:c>
       <x:c r="C25" s="0">
-        <x:v>63.4554885771216</x:v>
+        <x:v>64.593</x:v>
       </x:c>
       <x:c r="D25" s="0">
-        <x:v>4027</x:v>
+        <x:v>47162</x:v>
       </x:c>
       <x:c r="E25" s="0">
-        <x:v>63.6932960199546</x:v>
+        <x:v>64.721</x:v>
       </x:c>
       <x:c r="F25" s="0">
-        <x:v>8127</x:v>
+        <x:v>94291</x:v>
       </x:c>
       <x:c r="G25" s="0">
-        <x:v>0.104851311628368</x:v>
+        <x:v>0.459773533826081</x:v>
       </x:c>
       <x:c r="H25" s="0">
-        <x:v>73</x:v>
+        <x:v>-33</x:v>
       </x:c>
       <x:c r="I25" s="0">
-        <x:v>50.3369875868706</x:v>
+        <x:v>247.697</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:9">
@@ -1262,25 +1268,25 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="C26" s="0">
-        <x:v>62.8499984741211</x:v>
+        <x:v>62.833</x:v>
       </x:c>
       <x:c r="D26" s="0">
-        <x:v>0</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="E26" s="0">
-        <x:v>0</x:v>
+        <x:v>64.667</x:v>
       </x:c>
       <x:c r="F26" s="0">
-        <x:v>30</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="G26" s="0">
-        <x:v>0.000387048031112469</x:v>
+        <x:v>0.000731416891049115</x:v>
       </x:c>
       <x:c r="H26" s="0">
-        <x:v>30</x:v>
+        <x:v>-90</x:v>
       </x:c>
       <x:c r="I26" s="0">
-        <x:v>62.8499984741211</x:v>
+        <x:v>65.278</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:9">
@@ -1288,28 +1294,28 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="B27" s="0">
-        <x:v>4232</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C27" s="0">
-        <x:v>63.1412913902946</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D27" s="0">
-        <x:v>4240</x:v>
+        <x:v>1245</x:v>
       </x:c>
       <x:c r="E27" s="0">
-        <x:v>63.1327831556212</x:v>
+        <x:v>64.957</x:v>
       </x:c>
       <x:c r="F27" s="0">
-        <x:v>8472</x:v>
+        <x:v>1245</x:v>
       </x:c>
       <x:c r="G27" s="0">
-        <x:v>0.109302363986161</x:v>
+        <x:v>0.00607076019570766</x:v>
       </x:c>
       <x:c r="H27" s="0">
-        <x:v>-8</x:v>
+        <x:v>-1245</x:v>
       </x:c>
       <x:c r="I27" s="0">
-        <x:v>58.6319270133972</x:v>
+        <x:v>64.957</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:9">
@@ -1317,28 +1323,28 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="B28" s="0">
-        <x:v>0</x:v>
+        <x:v>717</x:v>
       </x:c>
       <x:c r="C28" s="0">
-        <x:v>0</x:v>
+        <x:v>62.499</x:v>
       </x:c>
       <x:c r="D28" s="0">
-        <x:v>25</x:v>
+        <x:v>2127</x:v>
       </x:c>
       <x:c r="E28" s="0">
-        <x:v>63.9000015258789</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="F28" s="0">
-        <x:v>25</x:v>
+        <x:v>2844</x:v>
       </x:c>
       <x:c r="G28" s="0">
-        <x:v>0.000322540025927057</x:v>
+        <x:v>0.0138676642542912</x:v>
       </x:c>
       <x:c r="H28" s="0">
-        <x:v>-25</x:v>
+        <x:v>-1410</x:v>
       </x:c>
       <x:c r="I28" s="0">
-        <x:v>63.9000015258789</x:v>
+        <x:v>64.763</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:9">
@@ -1346,28 +1352,28 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B29" s="0">
-        <x:v>0</x:v>
+        <x:v>9619</x:v>
       </x:c>
       <x:c r="C29" s="0">
-        <x:v>0</x:v>
+        <x:v>64.872</x:v>
       </x:c>
       <x:c r="D29" s="0">
-        <x:v>28</x:v>
+        <x:v>11055</x:v>
       </x:c>
       <x:c r="E29" s="0">
-        <x:v>63.5499992370606</x:v>
+        <x:v>65.283</x:v>
       </x:c>
       <x:c r="F29" s="0">
-        <x:v>28</x:v>
+        <x:v>20674</x:v>
       </x:c>
       <x:c r="G29" s="0">
-        <x:v>0.000361244829038304</x:v>
+        <x:v>0.100808752036996</x:v>
       </x:c>
       <x:c r="H29" s="0">
-        <x:v>-28</x:v>
+        <x:v>-1436</x:v>
       </x:c>
       <x:c r="I29" s="0">
-        <x:v>63.5499992370606</x:v>
+        <x:v>68.036</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:9">
@@ -1375,28 +1381,28 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="B30" s="0">
-        <x:v>0</x:v>
+        <x:v>229104</x:v>
       </x:c>
       <x:c r="C30" s="0">
-        <x:v>0</x:v>
+        <x:v>64.219</x:v>
       </x:c>
       <x:c r="D30" s="0">
-        <x:v>54</x:v>
+        <x:v>231330</x:v>
       </x:c>
       <x:c r="E30" s="0">
-        <x:v>63.4500007629394</x:v>
+        <x:v>64.295</x:v>
       </x:c>
       <x:c r="F30" s="0">
-        <x:v>54</x:v>
+        <x:v>460434</x:v>
       </x:c>
       <x:c r="G30" s="0">
-        <x:v>0.000696686456002444</x:v>
+        <x:v>2.24512803208872</x:v>
       </x:c>
       <x:c r="H30" s="0">
-        <x:v>-54</x:v>
+        <x:v>-2226</x:v>
       </x:c>
       <x:c r="I30" s="0">
-        <x:v>63.4500007629394</x:v>
+        <x:v>72.155</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:9">
@@ -1404,28 +1410,28 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="B31" s="0">
-        <x:v>123</x:v>
+        <x:v>1046</x:v>
       </x:c>
       <x:c r="C31" s="0">
-        <x:v>63.0686990691394</x:v>
+        <x:v>64.011</x:v>
       </x:c>
       <x:c r="D31" s="0">
-        <x:v>361</x:v>
+        <x:v>3980</x:v>
       </x:c>
       <x:c r="E31" s="0">
-        <x:v>63.1497223132865</x:v>
+        <x:v>64.587</x:v>
       </x:c>
       <x:c r="F31" s="0">
-        <x:v>484</x:v>
+        <x:v>5026</x:v>
       </x:c>
       <x:c r="G31" s="0">
-        <x:v>0.00624437490194783</x:v>
+        <x:v>0.0245073419627524</x:v>
       </x:c>
       <x:c r="H31" s="0">
-        <x:v>-238</x:v>
+        <x:v>-2934</x:v>
       </x:c>
       <x:c r="I31" s="0">
-        <x:v>63.1915956705558</x:v>
+        <x:v>64.793</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:9">
@@ -1433,28 +1439,28 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="B32" s="0">
-        <x:v>0</x:v>
+        <x:v>13752</x:v>
       </x:c>
       <x:c r="C32" s="0">
-        <x:v>0</x:v>
+        <x:v>64.925</x:v>
       </x:c>
       <x:c r="D32" s="0">
-        <x:v>266</x:v>
+        <x:v>21506</x:v>
       </x:c>
       <x:c r="E32" s="0">
-        <x:v>63.6218053487907</x:v>
+        <x:v>64.85</x:v>
       </x:c>
       <x:c r="F32" s="0">
-        <x:v>266</x:v>
+        <x:v>35258</x:v>
       </x:c>
       <x:c r="G32" s="0">
-        <x:v>0.00343182587586389</x:v>
+        <x:v>0.171921978297398</x:v>
       </x:c>
       <x:c r="H32" s="0">
-        <x:v>-266</x:v>
+        <x:v>-7754</x:v>
       </x:c>
       <x:c r="I32" s="0">
-        <x:v>63.6218053487907</x:v>
+        <x:v>64.718</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:9">
@@ -1462,28 +1468,28 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="B33" s="0">
-        <x:v>802</x:v>
+        <x:v>19375</x:v>
       </x:c>
       <x:c r="C33" s="0">
-        <x:v>63.0458238225923</x:v>
+        <x:v>63.697</x:v>
       </x:c>
       <x:c r="D33" s="0">
-        <x:v>3542</x:v>
+        <x:v>27706</x:v>
       </x:c>
       <x:c r="E33" s="0">
-        <x:v>63.9427887083514</x:v>
+        <x:v>63.836</x:v>
       </x:c>
       <x:c r="F33" s="0">
-        <x:v>4344</x:v>
+        <x:v>47081</x:v>
       </x:c>
       <x:c r="G33" s="0">
-        <x:v>0.0560445549050855</x:v>
+        <x:v>0.229572257649889</x:v>
       </x:c>
       <x:c r="H33" s="0">
-        <x:v>-2740</x:v>
+        <x:v>-8331</x:v>
       </x:c>
       <x:c r="I33" s="0">
-        <x:v>64.2053309851319</x:v>
+        <x:v>64.159</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:9">
@@ -1491,28 +1497,28 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="B34" s="0">
-        <x:v>14003</x:v>
+        <x:v>998</x:v>
       </x:c>
       <x:c r="C34" s="0">
-        <x:v>63.4647075146647</x:v>
+        <x:v>65.214</x:v>
       </x:c>
       <x:c r="D34" s="0">
-        <x:v>17749</x:v>
+        <x:v>11831</x:v>
       </x:c>
       <x:c r="E34" s="0">
-        <x:v>63.1074472414795</x:v>
+        <x:v>64.755</x:v>
       </x:c>
       <x:c r="F34" s="0">
-        <x:v>31752</x:v>
+        <x:v>12829</x:v>
       </x:c>
       <x:c r="G34" s="0">
-        <x:v>0.409651636129437</x:v>
+        <x:v>0.0625556486351273</x:v>
       </x:c>
       <x:c r="H34" s="0">
-        <x:v>-3746</x:v>
+        <x:v>-10833</x:v>
       </x:c>
       <x:c r="I34" s="0">
-        <x:v>61.7719652325599</x:v>
+        <x:v>64.712</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:9">
@@ -1520,28 +1526,28 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="B35" s="0">
-        <x:v>38225</x:v>
+        <x:v>83518</x:v>
       </x:c>
       <x:c r="C35" s="0">
-        <x:v>62.8486739521513</x:v>
+        <x:v>64.385</x:v>
       </x:c>
       <x:c r="D35" s="0">
-        <x:v>46540</x:v>
+        <x:v>103722</x:v>
       </x:c>
       <x:c r="E35" s="0">
-        <x:v>63.3151079008187</x:v>
+        <x:v>64.081</x:v>
       </x:c>
       <x:c r="F35" s="0">
-        <x:v>84765</x:v>
+        <x:v>187240</x:v>
       </x:c>
       <x:c r="G35" s="0">
-        <x:v>1.09360421190828</x:v>
+        <x:v>0.913003324533575</x:v>
       </x:c>
       <x:c r="H35" s="0">
-        <x:v>-8315</x:v>
+        <x:v>-20204</x:v>
       </x:c>
       <x:c r="I35" s="0">
-        <x:v>65.4593577730749</x:v>
+        <x:v>62.826</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:9">
@@ -1549,28 +1555,28 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="B36" s="0">
-        <x:v>15694</x:v>
+        <x:v>9688</x:v>
       </x:c>
       <x:c r="C36" s="0">
-        <x:v>63.3300175757352</x:v>
+        <x:v>64.192</x:v>
       </x:c>
       <x:c r="D36" s="0">
-        <x:v>24160</x:v>
+        <x:v>30384</x:v>
       </x:c>
       <x:c r="E36" s="0">
-        <x:v>62.9825953802526</x:v>
+        <x:v>64.014</x:v>
       </x:c>
       <x:c r="F36" s="0">
-        <x:v>39854</x:v>
+        <x:v>40072</x:v>
       </x:c>
       <x:c r="G36" s="0">
-        <x:v>0.514180407731878</x:v>
+        <x:v>0.195395584387468</x:v>
       </x:c>
       <x:c r="H36" s="0">
-        <x:v>-8466</x:v>
+        <x:v>-20696</x:v>
       </x:c>
       <x:c r="I36" s="0">
-        <x:v>62.338555227181</x:v>
+        <x:v>63.931</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:9">
@@ -1578,28 +1584,28 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="B37" s="0">
-        <x:v>23798</x:v>
+        <x:v>167539</x:v>
       </x:c>
       <x:c r="C37" s="0">
-        <x:v>63.3218359143726</x:v>
+        <x:v>63.862</x:v>
       </x:c>
       <x:c r="D37" s="0">
-        <x:v>33798</x:v>
+        <x:v>188818</x:v>
       </x:c>
       <x:c r="E37" s="0">
-        <x:v>63.5754884139371</x:v>
+        <x:v>64.267</x:v>
       </x:c>
       <x:c r="F37" s="0">
-        <x:v>57596</x:v>
+        <x:v>356357</x:v>
       </x:c>
       <x:c r="G37" s="0">
-        <x:v>0.743080613331792</x:v>
+        <x:v>1.7376368602906</x:v>
       </x:c>
       <x:c r="H37" s="0">
-        <x:v>-10000</x:v>
+        <x:v>-21279</x:v>
       </x:c>
       <x:c r="I37" s="0">
-        <x:v>64.1791306324005</x:v>
+        <x:v>67.462</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:9">
@@ -1607,28 +1613,28 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="B38" s="0">
-        <x:v>91666</x:v>
+        <x:v>67765</x:v>
       </x:c>
       <x:c r="C38" s="0">
-        <x:v>63.2124327734369</x:v>
+        <x:v>64.752</x:v>
       </x:c>
       <x:c r="D38" s="0">
-        <x:v>104008</x:v>
+        <x:v>90448</x:v>
       </x:c>
       <x:c r="E38" s="0">
-        <x:v>63.1110888212225</x:v>
+        <x:v>64.826</x:v>
       </x:c>
       <x:c r="F38" s="0">
-        <x:v>195674</x:v>
+        <x:v>158213</x:v>
       </x:c>
       <x:c r="G38" s="0">
-        <x:v>2.52450788133004</x:v>
+        <x:v>0.771464403890358</x:v>
       </x:c>
       <x:c r="H38" s="0">
-        <x:v>-12342</x:v>
+        <x:v>-22683</x:v>
       </x:c>
       <x:c r="I38" s="0">
-        <x:v>62.3583911446964</x:v>
+        <x:v>65.047</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:9">
@@ -1636,28 +1642,28 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="B39" s="0">
-        <x:v>175287</x:v>
+        <x:v>110571</x:v>
       </x:c>
       <x:c r="C39" s="0">
-        <x:v>63.2614915483222</x:v>
+        <x:v>63.375</x:v>
       </x:c>
       <x:c r="D39" s="0">
-        <x:v>188065</x:v>
+        <x:v>135377</x:v>
       </x:c>
       <x:c r="E39" s="0">
-        <x:v>63.1191690633942</x:v>
+        <x:v>64.195</x:v>
       </x:c>
       <x:c r="F39" s="0">
-        <x:v>363352</x:v>
+        <x:v>245948</x:v>
       </x:c>
       <x:c r="G39" s="0">
-        <x:v>4.68782254002593</x:v>
+        <x:v>1.19927014346499</x:v>
       </x:c>
       <x:c r="H39" s="0">
-        <x:v>-12778</x:v>
+        <x:v>-24806</x:v>
       </x:c>
       <x:c r="I39" s="0">
-        <x:v>61.1668070806437</x:v>
+        <x:v>67.848</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:9">
@@ -1665,28 +1671,28 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="B40" s="0">
-        <x:v>3410</x:v>
+        <x:v>1731919</x:v>
       </x:c>
       <x:c r="C40" s="0">
-        <x:v>62.7608064612336</x:v>
+        <x:v>64.224</x:v>
       </x:c>
       <x:c r="D40" s="0">
-        <x:v>18111</x:v>
+        <x:v>1771755</x:v>
       </x:c>
       <x:c r="E40" s="0">
-        <x:v>63.3985673206079</x:v>
+        <x:v>64.28</x:v>
       </x:c>
       <x:c r="F40" s="0">
-        <x:v>21521</x:v>
+        <x:v>3503674</x:v>
       </x:c>
       <x:c r="G40" s="0">
-        <x:v>0.277655355919048</x:v>
+        <x:v>17.0843089621974</x:v>
       </x:c>
       <x:c r="H40" s="0">
-        <x:v>-14701</x:v>
+        <x:v>-39836</x:v>
       </x:c>
       <x:c r="I40" s="0">
-        <x:v>63.5465004224695</x:v>
+        <x:v>66.709</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:9">
@@ -1694,28 +1700,28 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="B41" s="0">
-        <x:v>27894</x:v>
+        <x:v>114720</x:v>
       </x:c>
       <x:c r="C41" s="0">
-        <x:v>62.8231762610961</x:v>
+        <x:v>64.399</x:v>
       </x:c>
       <x:c r="D41" s="0">
-        <x:v>46861</x:v>
+        <x:v>161032</x:v>
       </x:c>
       <x:c r="E41" s="0">
-        <x:v>63.4029718838917</x:v>
+        <x:v>64.107</x:v>
       </x:c>
       <x:c r="F41" s="0">
-        <x:v>74755</x:v>
+        <x:v>275752</x:v>
       </x:c>
       <x:c r="G41" s="0">
-        <x:v>0.964459185527087</x:v>
+        <x:v>1.34459780360384</x:v>
       </x:c>
       <x:c r="H41" s="0">
-        <x:v>-18967</x:v>
+        <x:v>-46312</x:v>
       </x:c>
       <x:c r="I41" s="0">
-        <x:v>64.255653863238</x:v>
+        <x:v>63.385</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:9">
@@ -1723,28 +1729,28 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="B42" s="0">
-        <x:v>80671</x:v>
+        <x:v>143038</x:v>
       </x:c>
       <x:c r="C42" s="0">
-        <x:v>62.825925062796</x:v>
+        <x:v>64.457</x:v>
       </x:c>
       <x:c r="D42" s="0">
-        <x:v>104452</x:v>
+        <x:v>189941</x:v>
       </x:c>
       <x:c r="E42" s="0">
-        <x:v>63.8066862427928</x:v>
+        <x:v>64.691</x:v>
       </x:c>
       <x:c r="F42" s="0">
-        <x:v>185123</x:v>
+        <x:v>332979</x:v>
       </x:c>
       <x:c r="G42" s="0">
-        <x:v>2.38838308878779</x:v>
+        <x:v>1.62364309976429</x:v>
       </x:c>
       <x:c r="H42" s="0">
-        <x:v>-23781</x:v>
+        <x:v>-46903</x:v>
       </x:c>
       <x:c r="I42" s="0">
-        <x:v>67.133669344913</x:v>
+        <x:v>65.403</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:9">
@@ -1752,28 +1758,28 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="B43" s="0">
-        <x:v>729560</x:v>
+        <x:v>236336</x:v>
       </x:c>
       <x:c r="C43" s="0">
-        <x:v>63.1685757629704</x:v>
+        <x:v>64.153</x:v>
       </x:c>
       <x:c r="D43" s="0">
-        <x:v>757345</x:v>
+        <x:v>294445</x:v>
       </x:c>
       <x:c r="E43" s="0">
-        <x:v>63.1723212645868</x:v>
+        <x:v>64.116</x:v>
       </x:c>
       <x:c r="F43" s="0">
-        <x:v>1486905</x:v>
+        <x:v>530781</x:v>
       </x:c>
       <x:c r="G43" s="0">
-        <x:v>19.1834550900429</x:v>
+        <x:v>2.58814792565294</x:v>
       </x:c>
       <x:c r="H43" s="0">
-        <x:v>-27785</x:v>
+        <x:v>-58109</x:v>
       </x:c>
       <x:c r="I43" s="0">
-        <x:v>63.2706681481321</x:v>
+        <x:v>63.966</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:9">
@@ -1781,28 +1787,28 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="B44" s="0">
-        <x:v>40194</x:v>
+        <x:v>58735</x:v>
       </x:c>
       <x:c r="C44" s="0">
-        <x:v>63.330010380384</x:v>
+        <x:v>64.067</x:v>
       </x:c>
       <x:c r="D44" s="0">
-        <x:v>80369</x:v>
+        <x:v>120493</x:v>
       </x:c>
       <x:c r="E44" s="0">
-        <x:v>63.2915514798238</x:v>
+        <x:v>64.397</x:v>
       </x:c>
       <x:c r="F44" s="0">
-        <x:v>120563</x:v>
+        <x:v>179228</x:v>
       </x:c>
       <x:c r="G44" s="0">
-        <x:v>1.55545572583375</x:v>
+        <x:v>0.873935910326339</x:v>
       </x:c>
       <x:c r="H44" s="0">
-        <x:v>-40175</x:v>
+        <x:v>-61758</x:v>
       </x:c>
       <x:c r="I44" s="0">
-        <x:v>63.25307439086</x:v>
+        <x:v>64.71</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:9">
@@ -1810,28 +1816,28 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="B45" s="0">
-        <x:v>120686</x:v>
+        <x:v>514837</x:v>
       </x:c>
       <x:c r="C45" s="0">
-        <x:v>63.3018862337085</x:v>
+        <x:v>64.448</x:v>
       </x:c>
       <x:c r="D45" s="0">
-        <x:v>169834</x:v>
+        <x:v>588557</x:v>
       </x:c>
       <x:c r="E45" s="0">
-        <x:v>63.4257738025198</x:v>
+        <x:v>64.298</x:v>
       </x:c>
       <x:c r="F45" s="0">
-        <x:v>290520</x:v>
+        <x:v>1103394</x:v>
       </x:c>
       <x:c r="G45" s="0">
-        <x:v>3.74817313329315</x:v>
+        <x:v>5.38027339388165</x:v>
       </x:c>
       <x:c r="H45" s="0">
-        <x:v>-49148</x:v>
+        <x:v>-73720</x:v>
       </x:c>
       <x:c r="I45" s="0">
-        <x:v>63.729987506629</x:v>
+        <x:v>63.252</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:9">
@@ -1839,28 +1845,28 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="B46" s="0">
-        <x:v>101340</x:v>
+        <x:v>131579</x:v>
       </x:c>
       <x:c r="C46" s="0">
-        <x:v>63.292554233228</x:v>
+        <x:v>63.838</x:v>
       </x:c>
       <x:c r="D46" s="0">
-        <x:v>161344</x:v>
+        <x:v>211213</x:v>
       </x:c>
       <x:c r="E46" s="0">
-        <x:v>63.1768815527356</x:v>
+        <x:v>64.408</x:v>
       </x:c>
       <x:c r="F46" s="0">
-        <x:v>262684</x:v>
+        <x:v>342792</x:v>
       </x:c>
       <x:c r="G46" s="0">
-        <x:v>3.38904416682493</x:v>
+        <x:v>1.67149239277672</x:v>
       </x:c>
       <x:c r="H46" s="0">
-        <x:v>-60004</x:v>
+        <x:v>-79634</x:v>
       </x:c>
       <x:c r="I46" s="0">
-        <x:v>62.9815234192593</x:v>
+        <x:v>65.349</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:9">
@@ -1868,28 +1874,86 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="B47" s="0">
-        <x:v>54740</x:v>
+        <x:v>23024</x:v>
       </x:c>
       <x:c r="C47" s="0">
-        <x:v>63.1334518348295</x:v>
+        <x:v>64.34</x:v>
       </x:c>
       <x:c r="D47" s="0">
-        <x:v>330303</x:v>
+        <x:v>129444</x:v>
       </x:c>
       <x:c r="E47" s="0">
-        <x:v>63.7499287921676</x:v>
+        <x:v>65.829</x:v>
       </x:c>
       <x:c r="F47" s="0">
-        <x:v>385043</x:v>
+        <x:v>152468</x:v>
       </x:c>
       <x:c r="G47" s="0">
-        <x:v>4.96767116812128</x:v>
+        <x:v>0.743451136963177</x:v>
       </x:c>
       <x:c r="H47" s="0">
-        <x:v>-275563</x:v>
+        <x:v>-106420</x:v>
       </x:c>
       <x:c r="I47" s="0">
-        <x:v>63.8723906199336</x:v>
+        <x:v>66.151</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48" spans="1:9">
+      <x:c r="A48" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="B48" s="0">
+        <x:v>346164</x:v>
+      </x:c>
+      <x:c r="C48" s="0">
+        <x:v>65.297</x:v>
+      </x:c>
+      <x:c r="D48" s="0">
+        <x:v>600918</x:v>
+      </x:c>
+      <x:c r="E48" s="0">
+        <x:v>64.589</x:v>
+      </x:c>
+      <x:c r="F48" s="0">
+        <x:v>947082</x:v>
+      </x:c>
+      <x:c r="G48" s="0">
+        <x:v>4.61807848005719</x:v>
+      </x:c>
+      <x:c r="H48" s="0">
+        <x:v>-254754</x:v>
+      </x:c>
+      <x:c r="I48" s="0">
+        <x:v>63.627</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49" spans="1:9">
+      <x:c r="A49" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="B49" s="0">
+        <x:v>61315</x:v>
+      </x:c>
+      <x:c r="C49" s="0">
+        <x:v>65.347</x:v>
+      </x:c>
+      <x:c r="D49" s="0">
+        <x:v>422937</x:v>
+      </x:c>
+      <x:c r="E49" s="0">
+        <x:v>65.272</x:v>
+      </x:c>
+      <x:c r="F49" s="0">
+        <x:v>484252</x:v>
+      </x:c>
+      <x:c r="G49" s="0">
+        <x:v>2.36126728216211</x:v>
+      </x:c>
+      <x:c r="H49" s="0">
+        <x:v>-361622</x:v>
+      </x:c>
+      <x:c r="I49" s="0">
+        <x:v>65.259</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/app/fonlar/haftalik-yatirim-fonlarinin-en-cok-tercih-ettigi-hisseler/data/tercih-edilen-hisseler.xlsx
+++ b/app/fonlar/haftalik-yatirim-fonlarinin-en-cok-tercih-ettigi-hisseler/data/tercih-edilen-hisseler.xlsx
@@ -40,142 +40,142 @@
     <x:t>Maliyet</x:t>
   </x:si>
   <x:si>
+    <x:t>YAPI KREDI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BANK OF AMERICA</x:t>
+  </x:si>
+  <x:si>
     <x:t>GEDIK</x:t>
   </x:si>
   <x:si>
-    <x:t>BANK OF AMERICA</x:t>
+    <x:t>VAKIF</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DENIZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ZIRAAT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SEKER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IKON</x:t>
   </x:si>
   <x:si>
     <x:t>IS</x:t>
   </x:si>
   <x:si>
-    <x:t>IKON</x:t>
+    <x:t>TEB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALNUS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FIBA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BURGAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRIVE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ICBC TURKEY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ACAR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DESTEK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIZIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DINAMIK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALTERNATIF</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BTCTURK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ANADOLU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HSBC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UNLU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AHLATCI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INVEST AZ</x:t>
   </x:si>
   <x:si>
     <x:t>MIDAS</x:t>
   </x:si>
   <x:si>
-    <x:t>YAPI KREDI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ZIRAAT</x:t>
+    <x:t>INTEGRAL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TERA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ING</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PUSULA YAT.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BULLS YATIRIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HALK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GLOBAL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ATA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PHILLIP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OSMANLI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INFO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MEKSA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OYAK</x:t>
   </x:si>
   <x:si>
     <x:t>TACIRLER</x:t>
   </x:si>
   <x:si>
-    <x:t>TEB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VAKIF</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UNLU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BURGAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DENIZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TRIVE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SEKER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BTCTURK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALNUS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ICBC TURKEY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TERA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALTERNATIF</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FIBA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DESTEK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIZIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ACAR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DINAMIK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HSBC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ANADOLU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INVEST AZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HALK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BULLS YATIRIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AHLATCI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ING</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INTEGRAL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PHILLIP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ATA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INFO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GLOBAL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PUSULA YAT.</x:t>
-  </x:si>
-  <x:si>
     <x:t>AK</x:t>
   </x:si>
   <x:si>
-    <x:t>OYAK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OSMANLI</x:t>
+    <x:t>QNB YATIRIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KUVEYT TURK</x:t>
   </x:si>
   <x:si>
     <x:t>GARANTI BBVA</x:t>
   </x:si>
   <x:si>
-    <x:t>MEKSA</x:t>
-  </x:si>
-  <x:si>
     <x:t>A1 CAPITAL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>QNB YATIRIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KUVEYT TURK</x:t>
   </x:si>
   <x:si>
     <x:t>MARBAS</x:t>
@@ -569,28 +569,28 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B2" s="0">
-        <x:v>595609</x:v>
+        <x:v>1531348</x:v>
       </x:c>
       <x:c r="C2" s="0">
-        <x:v>64.597</x:v>
+        <x:v>65.555</x:v>
       </x:c>
       <x:c r="D2" s="0">
-        <x:v>303573</x:v>
+        <x:v>993199</x:v>
       </x:c>
       <x:c r="E2" s="0">
-        <x:v>64.238</x:v>
+        <x:v>65.179</x:v>
       </x:c>
       <x:c r="F2" s="0">
-        <x:v>899182</x:v>
+        <x:v>2524547</x:v>
       </x:c>
       <x:c r="G2" s="0">
-        <x:v>4.38451268618217</x:v>
+        <x:v>8.16579717397841</x:v>
       </x:c>
       <x:c r="H2" s="0">
-        <x:v>292036</x:v>
+        <x:v>538149</x:v>
       </x:c>
       <x:c r="I2" s="0">
-        <x:v>64.97</x:v>
+        <x:v>66.249</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:9">
@@ -598,28 +598,28 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B3" s="0">
-        <x:v>215896</x:v>
+        <x:v>351531</x:v>
       </x:c>
       <x:c r="C3" s="0">
-        <x:v>65.619</x:v>
+        <x:v>65.91</x:v>
       </x:c>
       <x:c r="D3" s="0">
-        <x:v>0</x:v>
+        <x:v>3923</x:v>
       </x:c>
       <x:c r="E3" s="0">
-        <x:v>0</x:v>
+        <x:v>66.656</x:v>
       </x:c>
       <x:c r="F3" s="0">
-        <x:v>215896</x:v>
+        <x:v>355454</x:v>
       </x:c>
       <x:c r="G3" s="0">
-        <x:v>1.0527332073996</x:v>
+        <x:v>1.14973706913728</x:v>
       </x:c>
       <x:c r="H3" s="0">
-        <x:v>215896</x:v>
+        <x:v>347608</x:v>
       </x:c>
       <x:c r="I3" s="0">
-        <x:v>65.619</x:v>
+        <x:v>65.901</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:9">
@@ -627,28 +627,28 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B4" s="0">
-        <x:v>1077775</x:v>
+        <x:v>915912</x:v>
       </x:c>
       <x:c r="C4" s="0">
-        <x:v>64.079</x:v>
+        <x:v>65.288</x:v>
       </x:c>
       <x:c r="D4" s="0">
-        <x:v>956750</x:v>
+        <x:v>591565</x:v>
       </x:c>
       <x:c r="E4" s="0">
-        <x:v>64.188</x:v>
+        <x:v>65.457</x:v>
       </x:c>
       <x:c r="F4" s="0">
-        <x:v>2034525</x:v>
+        <x:v>1507477</x:v>
       </x:c>
       <x:c r="G4" s="0">
-        <x:v>9.92057300174467</x:v>
+        <x:v>4.8760238674255</x:v>
       </x:c>
       <x:c r="H4" s="0">
-        <x:v>121025</x:v>
+        <x:v>324347</x:v>
       </x:c>
       <x:c r="I4" s="0">
-        <x:v>63.225</x:v>
+        <x:v>64.978</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:9">
@@ -656,28 +656,28 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B5" s="0">
-        <x:v>415812</x:v>
+        <x:v>915951</x:v>
       </x:c>
       <x:c r="C5" s="0">
-        <x:v>65.308</x:v>
+        <x:v>65.479</x:v>
       </x:c>
       <x:c r="D5" s="0">
-        <x:v>310738</x:v>
+        <x:v>610268</x:v>
       </x:c>
       <x:c r="E5" s="0">
-        <x:v>65.303</x:v>
+        <x:v>65.007</x:v>
       </x:c>
       <x:c r="F5" s="0">
-        <x:v>726550</x:v>
+        <x:v>1526219</x:v>
       </x:c>
       <x:c r="G5" s="0">
-        <x:v>3.54273961461156</x:v>
+        <x:v>4.93664597928743</x:v>
       </x:c>
       <x:c r="H5" s="0">
-        <x:v>105074</x:v>
+        <x:v>305683</x:v>
       </x:c>
       <x:c r="I5" s="0">
-        <x:v>65.323</x:v>
+        <x:v>66.421</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:9">
@@ -685,28 +685,28 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B6" s="0">
-        <x:v>600132</x:v>
+        <x:v>701280</x:v>
       </x:c>
       <x:c r="C6" s="0">
-        <x:v>64.262</x:v>
+        <x:v>65.345</x:v>
       </x:c>
       <x:c r="D6" s="0">
-        <x:v>495914</x:v>
+        <x:v>616837</x:v>
       </x:c>
       <x:c r="E6" s="0">
-        <x:v>64.166</x:v>
+        <x:v>65.213</x:v>
       </x:c>
       <x:c r="F6" s="0">
-        <x:v>1096046</x:v>
+        <x:v>1318117</x:v>
       </x:c>
       <x:c r="G6" s="0">
-        <x:v>5.34444371844546</x:v>
+        <x:v>4.26352770361293</x:v>
       </x:c>
       <x:c r="H6" s="0">
-        <x:v>104218</x:v>
+        <x:v>84443</x:v>
       </x:c>
       <x:c r="I6" s="0">
-        <x:v>64.722</x:v>
+        <x:v>66.309</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:9">
@@ -714,28 +714,28 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="B7" s="0">
-        <x:v>870161</x:v>
+        <x:v>937601</x:v>
       </x:c>
       <x:c r="C7" s="0">
-        <x:v>64.818</x:v>
+        <x:v>64.931</x:v>
       </x:c>
       <x:c r="D7" s="0">
-        <x:v>770988</x:v>
+        <x:v>860887</x:v>
       </x:c>
       <x:c r="E7" s="0">
-        <x:v>64.798</x:v>
+        <x:v>64.997</x:v>
       </x:c>
       <x:c r="F7" s="0">
-        <x:v>1641149</x:v>
+        <x:v>1798488</x:v>
       </x:c>
       <x:c r="G7" s="0">
-        <x:v>8.00242732885576</x:v>
+        <x:v>5.81731622656821</x:v>
       </x:c>
       <x:c r="H7" s="0">
-        <x:v>99173</x:v>
+        <x:v>76714</x:v>
       </x:c>
       <x:c r="I7" s="0">
-        <x:v>64.977</x:v>
+        <x:v>64.198</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:9">
@@ -743,28 +743,28 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B8" s="0">
-        <x:v>700517</x:v>
+        <x:v>127784</x:v>
       </x:c>
       <x:c r="C8" s="0">
-        <x:v>64.386</x:v>
+        <x:v>65.558</x:v>
       </x:c>
       <x:c r="D8" s="0">
-        <x:v>611686</x:v>
+        <x:v>59530</x:v>
       </x:c>
       <x:c r="E8" s="0">
-        <x:v>64.45</x:v>
+        <x:v>64.646</x:v>
       </x:c>
       <x:c r="F8" s="0">
-        <x:v>1312203</x:v>
+        <x:v>187314</x:v>
       </x:c>
       <x:c r="G8" s="0">
-        <x:v>6.39844959123548</x:v>
+        <x:v>0.605878255325249</x:v>
       </x:c>
       <x:c r="H8" s="0">
-        <x:v>88831</x:v>
+        <x:v>68254</x:v>
       </x:c>
       <x:c r="I8" s="0">
-        <x:v>63.943</x:v>
+        <x:v>66.354</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:9">
@@ -772,28 +772,28 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="B9" s="0">
-        <x:v>363988</x:v>
+        <x:v>796960</x:v>
       </x:c>
       <x:c r="C9" s="0">
-        <x:v>64.629</x:v>
+        <x:v>65.879</x:v>
       </x:c>
       <x:c r="D9" s="0">
-        <x:v>279109</x:v>
+        <x:v>742874</x:v>
       </x:c>
       <x:c r="E9" s="0">
-        <x:v>64.513</x:v>
+        <x:v>65.985</x:v>
       </x:c>
       <x:c r="F9" s="0">
-        <x:v>643097</x:v>
+        <x:v>1539834</x:v>
       </x:c>
       <x:c r="G9" s="0">
-        <x:v>3.13581338922009</x:v>
+        <x:v>4.98068450521851</x:v>
       </x:c>
       <x:c r="H9" s="0">
-        <x:v>84879</x:v>
+        <x:v>54086</x:v>
       </x:c>
       <x:c r="I9" s="0">
-        <x:v>65.009</x:v>
+        <x:v>64.424</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:9">
@@ -801,28 +801,28 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B10" s="0">
-        <x:v>67930</x:v>
+        <x:v>1372871</x:v>
       </x:c>
       <x:c r="C10" s="0">
-        <x:v>64.771</x:v>
+        <x:v>64.605</x:v>
       </x:c>
       <x:c r="D10" s="0">
-        <x:v>20607</x:v>
+        <x:v>1320291</x:v>
       </x:c>
       <x:c r="E10" s="0">
-        <x:v>64.477</x:v>
+        <x:v>64.823</x:v>
       </x:c>
       <x:c r="F10" s="0">
-        <x:v>88537</x:v>
+        <x:v>2693162</x:v>
       </x:c>
       <x:c r="G10" s="0">
-        <x:v>0.431716381885437</x:v>
+        <x:v>8.71119240349498</x:v>
       </x:c>
       <x:c r="H10" s="0">
-        <x:v>47323</x:v>
+        <x:v>52580</x:v>
       </x:c>
       <x:c r="I10" s="0">
-        <x:v>64.899</x:v>
+        <x:v>59.112</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:9">
@@ -830,28 +830,28 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B11" s="0">
-        <x:v>422452</x:v>
+        <x:v>98178</x:v>
       </x:c>
       <x:c r="C11" s="0">
-        <x:v>64.414</x:v>
+        <x:v>65.4</x:v>
       </x:c>
       <x:c r="D11" s="0">
-        <x:v>389937</x:v>
+        <x:v>58984</x:v>
       </x:c>
       <x:c r="E11" s="0">
-        <x:v>64.149</x:v>
+        <x:v>65.773</x:v>
       </x:c>
       <x:c r="F11" s="0">
-        <x:v>812389</x:v>
+        <x:v>157162</x:v>
       </x:c>
       <x:c r="G11" s="0">
-        <x:v>3.96130024468333</x:v>
+        <x:v>0.508349820960669</x:v>
       </x:c>
       <x:c r="H11" s="0">
-        <x:v>32515</x:v>
+        <x:v>39194</x:v>
       </x:c>
       <x:c r="I11" s="0">
-        <x:v>67.591</x:v>
+        <x:v>64.838</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:9">
@@ -859,28 +859,28 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="B12" s="0">
-        <x:v>40373</x:v>
+        <x:v>147402</x:v>
       </x:c>
       <x:c r="C12" s="0">
-        <x:v>64.421</x:v>
+        <x:v>65.344</x:v>
       </x:c>
       <x:c r="D12" s="0">
-        <x:v>15441</x:v>
+        <x:v>119393</x:v>
       </x:c>
       <x:c r="E12" s="0">
-        <x:v>63.56</x:v>
+        <x:v>65.209</x:v>
       </x:c>
       <x:c r="F12" s="0">
-        <x:v>55814</x:v>
+        <x:v>266795</x:v>
       </x:c>
       <x:c r="G12" s="0">
-        <x:v>0.272155349046769</x:v>
+        <x:v>0.862964269245758</x:v>
       </x:c>
       <x:c r="H12" s="0">
-        <x:v>24932</x:v>
+        <x:v>28009</x:v>
       </x:c>
       <x:c r="I12" s="0">
-        <x:v>64.955</x:v>
+        <x:v>65.917</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:9">
@@ -888,28 +888,28 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B13" s="0">
-        <x:v>49368</x:v>
+        <x:v>42502</x:v>
       </x:c>
       <x:c r="C13" s="0">
-        <x:v>64.451</x:v>
+        <x:v>65.564</x:v>
       </x:c>
       <x:c r="D13" s="0">
-        <x:v>28858</x:v>
+        <x:v>15105</x:v>
       </x:c>
       <x:c r="E13" s="0">
-        <x:v>65.064</x:v>
+        <x:v>65.393</x:v>
       </x:c>
       <x:c r="F13" s="0">
-        <x:v>78226</x:v>
+        <x:v>57607</x:v>
       </x:c>
       <x:c r="G13" s="0">
-        <x:v>0.381438784794721</x:v>
+        <x:v>0.186333262086772</x:v>
       </x:c>
       <x:c r="H13" s="0">
-        <x:v>20510</x:v>
+        <x:v>27397</x:v>
       </x:c>
       <x:c r="I13" s="0">
-        <x:v>63.588</x:v>
+        <x:v>65.659</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:9">
@@ -917,28 +917,28 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="B14" s="0">
-        <x:v>391419</x:v>
+        <x:v>55493</x:v>
       </x:c>
       <x:c r="C14" s="0">
-        <x:v>64.446</x:v>
+        <x:v>64.722</x:v>
       </x:c>
       <x:c r="D14" s="0">
-        <x:v>381045</x:v>
+        <x:v>38371</x:v>
       </x:c>
       <x:c r="E14" s="0">
-        <x:v>64.403</x:v>
+        <x:v>65.377</x:v>
       </x:c>
       <x:c r="F14" s="0">
-        <x:v>772464</x:v>
+        <x:v>93864</x:v>
       </x:c>
       <x:c r="G14" s="0">
-        <x:v>3.76662144884909</x:v>
+        <x:v>0.303608681453865</x:v>
       </x:c>
       <x:c r="H14" s="0">
-        <x:v>10374</x:v>
+        <x:v>17122</x:v>
       </x:c>
       <x:c r="I14" s="0">
-        <x:v>66.022</x:v>
+        <x:v>63.253</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:9">
@@ -946,28 +946,28 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B15" s="0">
-        <x:v>28686</x:v>
+        <x:v>50744</x:v>
       </x:c>
       <x:c r="C15" s="0">
-        <x:v>64.643</x:v>
+        <x:v>65.477</x:v>
       </x:c>
       <x:c r="D15" s="0">
-        <x:v>21035</x:v>
+        <x:v>46368</x:v>
       </x:c>
       <x:c r="E15" s="0">
-        <x:v>64.983</x:v>
+        <x:v>65.847</x:v>
       </x:c>
       <x:c r="F15" s="0">
-        <x:v>49721</x:v>
+        <x:v>97112</x:v>
       </x:c>
       <x:c r="G15" s="0">
-        <x:v>0.242445194932354</x:v>
+        <x:v>0.314114530313514</x:v>
       </x:c>
       <x:c r="H15" s="0">
-        <x:v>7651</x:v>
+        <x:v>4376</x:v>
       </x:c>
       <x:c r="I15" s="0">
-        <x:v>63.709</x:v>
+        <x:v>61.559</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:9">
@@ -975,28 +975,28 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B16" s="0">
-        <x:v>61599</x:v>
+        <x:v>15170</x:v>
       </x:c>
       <x:c r="C16" s="0">
-        <x:v>64.115</x:v>
+        <x:v>65.608</x:v>
       </x:c>
       <x:c r="D16" s="0">
-        <x:v>56655</x:v>
+        <x:v>13632</x:v>
       </x:c>
       <x:c r="E16" s="0">
-        <x:v>64.543</x:v>
+        <x:v>65.837</x:v>
       </x:c>
       <x:c r="F16" s="0">
-        <x:v>118254</x:v>
+        <x:v>28802</x:v>
       </x:c>
       <x:c r="G16" s="0">
-        <x:v>0.57661982022748</x:v>
+        <x:v>0.0931617792043191</x:v>
       </x:c>
       <x:c r="H16" s="0">
-        <x:v>4944</x:v>
+        <x:v>1538</x:v>
       </x:c>
       <x:c r="I16" s="0">
-        <x:v>59.219</x:v>
+        <x:v>63.573</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:9">
@@ -1004,28 +1004,28 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B17" s="0">
-        <x:v>23596</x:v>
+        <x:v>81554</x:v>
       </x:c>
       <x:c r="C17" s="0">
-        <x:v>64.311</x:v>
+        <x:v>65.37</x:v>
       </x:c>
       <x:c r="D17" s="0">
-        <x:v>19015</x:v>
+        <x:v>80675</x:v>
       </x:c>
       <x:c r="E17" s="0">
-        <x:v>64.246</x:v>
+        <x:v>65.452</x:v>
       </x:c>
       <x:c r="F17" s="0">
-        <x:v>42611</x:v>
+        <x:v>162229</x:v>
       </x:c>
       <x:c r="G17" s="0">
-        <x:v>0.207776034296626</x:v>
+        <x:v>0.524739333328848</x:v>
       </x:c>
       <x:c r="H17" s="0">
-        <x:v>4581</x:v>
+        <x:v>879</x:v>
       </x:c>
       <x:c r="I17" s="0">
-        <x:v>64.58</x:v>
+        <x:v>57.783</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:9">
@@ -1033,28 +1033,28 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B18" s="0">
-        <x:v>81506</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C18" s="0">
-        <x:v>64.422</x:v>
+        <x:v>66.14</x:v>
       </x:c>
       <x:c r="D18" s="0">
-        <x:v>77209</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E18" s="0">
-        <x:v>64.552</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F18" s="0">
-        <x:v>158715</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="G18" s="0">
-        <x:v>0.773912212419069</x:v>
+        <x:v>0.000161727968898547</x:v>
       </x:c>
       <x:c r="H18" s="0">
-        <x:v>4297</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="I18" s="0">
-        <x:v>62.084</x:v>
+        <x:v>66.14</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:9">
@@ -1062,28 +1062,28 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B19" s="0">
-        <x:v>8170</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C19" s="0">
-        <x:v>64.789</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D19" s="0">
-        <x:v>4742</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E19" s="0">
-        <x:v>64.054</x:v>
+        <x:v>63.92</x:v>
       </x:c>
       <x:c r="F19" s="0">
-        <x:v>12912</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="G19" s="0">
-        <x:v>0.0629603659815078</x:v>
+        <x:v>8.08639844492736E-05</x:v>
       </x:c>
       <x:c r="H19" s="0">
-        <x:v>3428</x:v>
+        <x:v>-25</x:v>
       </x:c>
       <x:c r="I19" s="0">
-        <x:v>65.806</x:v>
+        <x:v>63.92</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:9">
@@ -1091,28 +1091,28 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="B20" s="0">
-        <x:v>104191</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C20" s="0">
-        <x:v>63.938</x:v>
+        <x:v>62.833</x:v>
       </x:c>
       <x:c r="D20" s="0">
-        <x:v>101853</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="E20" s="0">
-        <x:v>64.39</x:v>
+        <x:v>65.322</x:v>
       </x:c>
       <x:c r="F20" s="0">
-        <x:v>206044</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="G20" s="0">
-        <x:v>1.00469374599549</x:v>
+        <x:v>0.000679257469373898</x:v>
       </x:c>
       <x:c r="H20" s="0">
-        <x:v>2338</x:v>
+        <x:v>-150</x:v>
       </x:c>
       <x:c r="I20" s="0">
-        <x:v>44.25</x:v>
+        <x:v>65.82</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:9">
@@ -1126,22 +1126,22 @@
         <x:v>65.3</x:v>
       </x:c>
       <x:c r="D21" s="0">
-        <x:v>54</x:v>
+        <x:v>1542</x:v>
       </x:c>
       <x:c r="E21" s="0">
-        <x:v>63.444</x:v>
+        <x:v>66.307</x:v>
       </x:c>
       <x:c r="F21" s="0">
-        <x:v>654</x:v>
+        <x:v>2142</x:v>
       </x:c>
       <x:c r="G21" s="0">
-        <x:v>0.00318897764497414</x:v>
+        <x:v>0.00692842618761376</x:v>
       </x:c>
       <x:c r="H21" s="0">
-        <x:v>546</x:v>
+        <x:v>-942</x:v>
       </x:c>
       <x:c r="I21" s="0">
-        <x:v>65.484</x:v>
+        <x:v>66.948</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:9">
@@ -1149,28 +1149,28 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="B22" s="0">
-        <x:v>11722</x:v>
+        <x:v>27877</x:v>
       </x:c>
       <x:c r="C22" s="0">
-        <x:v>64.031</x:v>
+        <x:v>64.661</x:v>
       </x:c>
       <x:c r="D22" s="0">
-        <x:v>11290</x:v>
+        <x:v>29052</x:v>
       </x:c>
       <x:c r="E22" s="0">
-        <x:v>64.941</x:v>
+        <x:v>64.996</x:v>
       </x:c>
       <x:c r="F22" s="0">
-        <x:v>23012</x:v>
+        <x:v>56929</x:v>
       </x:c>
       <x:c r="G22" s="0">
-        <x:v>0.112209103312148</x:v>
+        <x:v>0.184140230828508</x:v>
       </x:c>
       <x:c r="H22" s="0">
-        <x:v>432</x:v>
+        <x:v>-1175</x:v>
       </x:c>
       <x:c r="I22" s="0">
-        <x:v>40.269</x:v>
+        <x:v>72.94</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:9">
@@ -1178,28 +1178,28 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="B23" s="0">
-        <x:v>50</x:v>
+        <x:v>717</x:v>
       </x:c>
       <x:c r="C23" s="0">
-        <x:v>66.14</x:v>
+        <x:v>62.499</x:v>
       </x:c>
       <x:c r="D23" s="0">
-        <x:v>0</x:v>
+        <x:v>2127</x:v>
       </x:c>
       <x:c r="E23" s="0">
-        <x:v>0</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="F23" s="0">
-        <x:v>50</x:v>
+        <x:v>2844</x:v>
       </x:c>
       <x:c r="G23" s="0">
-        <x:v>0.000243805630349705</x:v>
+        <x:v>0.00919908687094936</x:v>
       </x:c>
       <x:c r="H23" s="0">
-        <x:v>50</x:v>
+        <x:v>-1410</x:v>
       </x:c>
       <x:c r="I23" s="0">
-        <x:v>66.14</x:v>
+        <x:v>64.763</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:9">
@@ -1207,28 +1207,28 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="B24" s="0">
-        <x:v>0</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="C24" s="0">
-        <x:v>0</x:v>
+        <x:v>66.7</x:v>
       </x:c>
       <x:c r="D24" s="0">
-        <x:v>25</x:v>
+        <x:v>2577</x:v>
       </x:c>
       <x:c r="E24" s="0">
-        <x:v>63.92</x:v>
+        <x:v>65.956</x:v>
       </x:c>
       <x:c r="F24" s="0">
-        <x:v>25</x:v>
+        <x:v>3577</x:v>
       </x:c>
       <x:c r="G24" s="0">
-        <x:v>0.000121902815174853</x:v>
+        <x:v>0.0115700188950021</x:v>
       </x:c>
       <x:c r="H24" s="0">
-        <x:v>-25</x:v>
+        <x:v>-1577</x:v>
       </x:c>
       <x:c r="I24" s="0">
-        <x:v>63.92</x:v>
+        <x:v>65.484</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:9">
@@ -1236,28 +1236,28 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="B25" s="0">
-        <x:v>47129</x:v>
+        <x:v>40393</x:v>
       </x:c>
       <x:c r="C25" s="0">
-        <x:v>64.593</x:v>
+        <x:v>64.422</x:v>
       </x:c>
       <x:c r="D25" s="0">
-        <x:v>47162</x:v>
+        <x:v>42511</x:v>
       </x:c>
       <x:c r="E25" s="0">
-        <x:v>64.721</x:v>
+        <x:v>65.06</x:v>
       </x:c>
       <x:c r="F25" s="0">
-        <x:v>94291</x:v>
+        <x:v>82904</x:v>
       </x:c>
       <x:c r="G25" s="0">
-        <x:v>0.459773533826081</x:v>
+        <x:v>0.268157910671303</x:v>
       </x:c>
       <x:c r="H25" s="0">
-        <x:v>-33</x:v>
+        <x:v>-2118</x:v>
       </x:c>
       <x:c r="I25" s="0">
-        <x:v>247.697</x:v>
+        <x:v>77.229</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:9">
@@ -1265,28 +1265,28 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="B26" s="0">
-        <x:v>30</x:v>
+        <x:v>26136</x:v>
       </x:c>
       <x:c r="C26" s="0">
-        <x:v>62.833</x:v>
+        <x:v>65.722</x:v>
       </x:c>
       <x:c r="D26" s="0">
-        <x:v>120</x:v>
+        <x:v>29543</x:v>
       </x:c>
       <x:c r="E26" s="0">
-        <x:v>64.667</x:v>
+        <x:v>65.333</x:v>
       </x:c>
       <x:c r="F26" s="0">
-        <x:v>150</x:v>
+        <x:v>55679</x:v>
       </x:c>
       <x:c r="G26" s="0">
-        <x:v>0.000731416891049115</x:v>
+        <x:v>0.180097031606044</x:v>
       </x:c>
       <x:c r="H26" s="0">
-        <x:v>-90</x:v>
+        <x:v>-3407</x:v>
       </x:c>
       <x:c r="I26" s="0">
-        <x:v>65.278</x:v>
+        <x:v>62.343</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:9">
@@ -1294,28 +1294,28 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="B27" s="0">
-        <x:v>0</x:v>
+        <x:v>9968</x:v>
       </x:c>
       <x:c r="C27" s="0">
-        <x:v>0</x:v>
+        <x:v>64.907</x:v>
       </x:c>
       <x:c r="D27" s="0">
-        <x:v>1245</x:v>
+        <x:v>18680</x:v>
       </x:c>
       <x:c r="E27" s="0">
-        <x:v>64.957</x:v>
+        <x:v>65.557</x:v>
       </x:c>
       <x:c r="F27" s="0">
-        <x:v>1245</x:v>
+        <x:v>28648</x:v>
       </x:c>
       <x:c r="G27" s="0">
-        <x:v>0.00607076019570766</x:v>
+        <x:v>0.0926636570601116</x:v>
       </x:c>
       <x:c r="H27" s="0">
-        <x:v>-1245</x:v>
+        <x:v>-8712</x:v>
       </x:c>
       <x:c r="I27" s="0">
-        <x:v>64.957</x:v>
+        <x:v>66.3</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:9">
@@ -1323,28 +1323,28 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="B28" s="0">
-        <x:v>717</x:v>
+        <x:v>814340</x:v>
       </x:c>
       <x:c r="C28" s="0">
-        <x:v>62.499</x:v>
+        <x:v>64.874</x:v>
       </x:c>
       <x:c r="D28" s="0">
-        <x:v>2127</x:v>
+        <x:v>824864</x:v>
       </x:c>
       <x:c r="E28" s="0">
-        <x:v>64</x:v>
+        <x:v>65.068</x:v>
       </x:c>
       <x:c r="F28" s="0">
-        <x:v>2844</x:v>
+        <x:v>1639204</x:v>
       </x:c>
       <x:c r="G28" s="0">
-        <x:v>0.0138676642542912</x:v>
+        <x:v>5.30210267060748</x:v>
       </x:c>
       <x:c r="H28" s="0">
-        <x:v>-1410</x:v>
+        <x:v>-10524</x:v>
       </x:c>
       <x:c r="I28" s="0">
-        <x:v>64.763</x:v>
+        <x:v>80.034</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:9">
@@ -1352,28 +1352,28 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B29" s="0">
-        <x:v>9619</x:v>
+        <x:v>1379</x:v>
       </x:c>
       <x:c r="C29" s="0">
-        <x:v>64.872</x:v>
+        <x:v>65.576</x:v>
       </x:c>
       <x:c r="D29" s="0">
-        <x:v>11055</x:v>
+        <x:v>11931</x:v>
       </x:c>
       <x:c r="E29" s="0">
-        <x:v>65.283</x:v>
+        <x:v>64.77</x:v>
       </x:c>
       <x:c r="F29" s="0">
-        <x:v>20674</x:v>
+        <x:v>13310</x:v>
       </x:c>
       <x:c r="G29" s="0">
-        <x:v>0.100808752036996</x:v>
+        <x:v>0.0430519853207932</x:v>
       </x:c>
       <x:c r="H29" s="0">
-        <x:v>-1436</x:v>
+        <x:v>-10552</x:v>
       </x:c>
       <x:c r="I29" s="0">
-        <x:v>68.036</x:v>
+        <x:v>64.664</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:9">
@@ -1381,28 +1381,28 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="B30" s="0">
-        <x:v>229104</x:v>
+        <x:v>214505</x:v>
       </x:c>
       <x:c r="C30" s="0">
-        <x:v>64.219</x:v>
+        <x:v>65.172</x:v>
       </x:c>
       <x:c r="D30" s="0">
-        <x:v>231330</x:v>
+        <x:v>226009</x:v>
       </x:c>
       <x:c r="E30" s="0">
-        <x:v>64.295</x:v>
+        <x:v>65.485</x:v>
       </x:c>
       <x:c r="F30" s="0">
-        <x:v>460434</x:v>
+        <x:v>440514</x:v>
       </x:c>
       <x:c r="G30" s="0">
-        <x:v>2.24512803208872</x:v>
+        <x:v>1.42486868982749</x:v>
       </x:c>
       <x:c r="H30" s="0">
-        <x:v>-2226</x:v>
+        <x:v>-11504</x:v>
       </x:c>
       <x:c r="I30" s="0">
-        <x:v>72.155</x:v>
+        <x:v>71.322</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:9">
@@ -1410,28 +1410,28 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="B31" s="0">
-        <x:v>1046</x:v>
+        <x:v>25432</x:v>
       </x:c>
       <x:c r="C31" s="0">
-        <x:v>64.011</x:v>
+        <x:v>64.334</x:v>
       </x:c>
       <x:c r="D31" s="0">
-        <x:v>3980</x:v>
+        <x:v>37526</x:v>
       </x:c>
       <x:c r="E31" s="0">
-        <x:v>64.587</x:v>
+        <x:v>64.584</x:v>
       </x:c>
       <x:c r="F31" s="0">
-        <x:v>5026</x:v>
+        <x:v>62958</x:v>
       </x:c>
       <x:c r="G31" s="0">
-        <x:v>0.0245073419627524</x:v>
+        <x:v>0.203641389318295</x:v>
       </x:c>
       <x:c r="H31" s="0">
-        <x:v>-2934</x:v>
+        <x:v>-12094</x:v>
       </x:c>
       <x:c r="I31" s="0">
-        <x:v>64.793</x:v>
+        <x:v>65.109</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:9">
@@ -1439,28 +1439,28 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="B32" s="0">
-        <x:v>13752</x:v>
+        <x:v>146091</x:v>
       </x:c>
       <x:c r="C32" s="0">
-        <x:v>64.925</x:v>
+        <x:v>64.206</x:v>
       </x:c>
       <x:c r="D32" s="0">
-        <x:v>21506</x:v>
+        <x:v>158304</x:v>
       </x:c>
       <x:c r="E32" s="0">
-        <x:v>64.85</x:v>
+        <x:v>64.537</x:v>
       </x:c>
       <x:c r="F32" s="0">
-        <x:v>35258</x:v>
+        <x:v>304395</x:v>
       </x:c>
       <x:c r="G32" s="0">
-        <x:v>0.171921978297398</x:v>
+        <x:v>0.984583701857465</x:v>
       </x:c>
       <x:c r="H32" s="0">
-        <x:v>-7754</x:v>
+        <x:v>-12213</x:v>
       </x:c>
       <x:c r="I32" s="0">
-        <x:v>64.718</x:v>
+        <x:v>68.496</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:9">
@@ -1468,28 +1468,28 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="B33" s="0">
-        <x:v>19375</x:v>
+        <x:v>1593</x:v>
       </x:c>
       <x:c r="C33" s="0">
-        <x:v>63.697</x:v>
+        <x:v>65.022</x:v>
       </x:c>
       <x:c r="D33" s="0">
-        <x:v>27706</x:v>
+        <x:v>19950</x:v>
       </x:c>
       <x:c r="E33" s="0">
-        <x:v>63.836</x:v>
+        <x:v>65.551</x:v>
       </x:c>
       <x:c r="F33" s="0">
-        <x:v>47081</x:v>
+        <x:v>21543</x:v>
       </x:c>
       <x:c r="G33" s="0">
-        <x:v>0.229572257649889</x:v>
+        <x:v>0.069682112679628</x:v>
       </x:c>
       <x:c r="H33" s="0">
-        <x:v>-8331</x:v>
+        <x:v>-18357</x:v>
       </x:c>
       <x:c r="I33" s="0">
-        <x:v>64.159</x:v>
+        <x:v>65.597</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:9">
@@ -1497,28 +1497,28 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="B34" s="0">
-        <x:v>998</x:v>
+        <x:v>379554</x:v>
       </x:c>
       <x:c r="C34" s="0">
-        <x:v>65.214</x:v>
+        <x:v>65.066</x:v>
       </x:c>
       <x:c r="D34" s="0">
-        <x:v>11831</x:v>
+        <x:v>411932</x:v>
       </x:c>
       <x:c r="E34" s="0">
-        <x:v>64.755</x:v>
+        <x:v>65.314</x:v>
       </x:c>
       <x:c r="F34" s="0">
-        <x:v>12829</x:v>
+        <x:v>791486</x:v>
       </x:c>
       <x:c r="G34" s="0">
-        <x:v>0.0625556486351273</x:v>
+        <x:v>2.56010846383271</x:v>
       </x:c>
       <x:c r="H34" s="0">
-        <x:v>-10833</x:v>
+        <x:v>-32378</x:v>
       </x:c>
       <x:c r="I34" s="0">
-        <x:v>64.712</x:v>
+        <x:v>68.225</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:9">
@@ -1526,28 +1526,28 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="B35" s="0">
-        <x:v>83518</x:v>
+        <x:v>93170</x:v>
       </x:c>
       <x:c r="C35" s="0">
-        <x:v>64.385</x:v>
+        <x:v>65.298</x:v>
       </x:c>
       <x:c r="D35" s="0">
-        <x:v>103722</x:v>
+        <x:v>129481</x:v>
       </x:c>
       <x:c r="E35" s="0">
-        <x:v>64.081</x:v>
+        <x:v>65.294</x:v>
       </x:c>
       <x:c r="F35" s="0">
-        <x:v>187240</x:v>
+        <x:v>222651</x:v>
       </x:c>
       <x:c r="G35" s="0">
-        <x:v>0.913003324533575</x:v>
+        <x:v>0.720177880064608</x:v>
       </x:c>
       <x:c r="H35" s="0">
-        <x:v>-20204</x:v>
+        <x:v>-36311</x:v>
       </x:c>
       <x:c r="I35" s="0">
-        <x:v>62.826</x:v>
+        <x:v>65.282</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:9">
@@ -1555,28 +1555,28 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="B36" s="0">
-        <x:v>9688</x:v>
+        <x:v>15839</x:v>
       </x:c>
       <x:c r="C36" s="0">
-        <x:v>64.192</x:v>
+        <x:v>65.023</x:v>
       </x:c>
       <x:c r="D36" s="0">
-        <x:v>30384</x:v>
+        <x:v>56154</x:v>
       </x:c>
       <x:c r="E36" s="0">
-        <x:v>64.014</x:v>
+        <x:v>65.359</x:v>
       </x:c>
       <x:c r="F36" s="0">
-        <x:v>40072</x:v>
+        <x:v>71993</x:v>
       </x:c>
       <x:c r="G36" s="0">
-        <x:v>0.195395584387468</x:v>
+        <x:v>0.232865633298262</x:v>
       </x:c>
       <x:c r="H36" s="0">
-        <x:v>-20696</x:v>
+        <x:v>-40315</x:v>
       </x:c>
       <x:c r="I36" s="0">
-        <x:v>63.931</x:v>
+        <x:v>65.491</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:9">
@@ -1584,28 +1584,28 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="B37" s="0">
-        <x:v>167539</x:v>
+        <x:v>134249</x:v>
       </x:c>
       <x:c r="C37" s="0">
-        <x:v>63.862</x:v>
+        <x:v>65.109</x:v>
       </x:c>
       <x:c r="D37" s="0">
-        <x:v>188818</x:v>
+        <x:v>175709</x:v>
       </x:c>
       <x:c r="E37" s="0">
-        <x:v>64.267</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="F37" s="0">
-        <x:v>356357</x:v>
+        <x:v>309958</x:v>
       </x:c>
       <x:c r="G37" s="0">
-        <x:v>1.7376368602906</x:v>
+        <x:v>1.00257755567712</x:v>
       </x:c>
       <x:c r="H37" s="0">
-        <x:v>-21279</x:v>
+        <x:v>-41460</x:v>
       </x:c>
       <x:c r="I37" s="0">
-        <x:v>67.462</x:v>
+        <x:v>64.647</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:9">
@@ -1613,28 +1613,28 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="B38" s="0">
-        <x:v>67765</x:v>
+        <x:v>190971</x:v>
       </x:c>
       <x:c r="C38" s="0">
-        <x:v>64.752</x:v>
+        <x:v>65.015</x:v>
       </x:c>
       <x:c r="D38" s="0">
-        <x:v>90448</x:v>
+        <x:v>238505</x:v>
       </x:c>
       <x:c r="E38" s="0">
-        <x:v>64.826</x:v>
+        <x:v>65.052</x:v>
       </x:c>
       <x:c r="F38" s="0">
-        <x:v>158213</x:v>
+        <x:v>429476</x:v>
       </x:c>
       <x:c r="G38" s="0">
-        <x:v>0.771464403890358</x:v>
+        <x:v>1.38916562341345</x:v>
       </x:c>
       <x:c r="H38" s="0">
-        <x:v>-22683</x:v>
+        <x:v>-47534</x:v>
       </x:c>
       <x:c r="I38" s="0">
-        <x:v>65.047</x:v>
+        <x:v>65.203</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:9">
@@ -1642,28 +1642,28 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="B39" s="0">
-        <x:v>110571</x:v>
+        <x:v>212563</x:v>
       </x:c>
       <x:c r="C39" s="0">
-        <x:v>63.375</x:v>
+        <x:v>64.431</x:v>
       </x:c>
       <x:c r="D39" s="0">
-        <x:v>135377</x:v>
+        <x:v>273883</x:v>
       </x:c>
       <x:c r="E39" s="0">
-        <x:v>64.195</x:v>
+        <x:v>64.951</x:v>
       </x:c>
       <x:c r="F39" s="0">
-        <x:v>245948</x:v>
+        <x:v>486446</x:v>
       </x:c>
       <x:c r="G39" s="0">
-        <x:v>1.19927014346499</x:v>
+        <x:v>1.57343847117645</x:v>
       </x:c>
       <x:c r="H39" s="0">
-        <x:v>-24806</x:v>
+        <x:v>-61320</x:v>
       </x:c>
       <x:c r="I39" s="0">
-        <x:v>67.848</x:v>
+        <x:v>66.756</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:9">
@@ -1671,28 +1671,28 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="B40" s="0">
-        <x:v>1731919</x:v>
+        <x:v>78779</x:v>
       </x:c>
       <x:c r="C40" s="0">
-        <x:v>64.224</x:v>
+        <x:v>64.673</x:v>
       </x:c>
       <x:c r="D40" s="0">
-        <x:v>1771755</x:v>
+        <x:v>140100</x:v>
       </x:c>
       <x:c r="E40" s="0">
-        <x:v>64.28</x:v>
+        <x:v>64.66</x:v>
       </x:c>
       <x:c r="F40" s="0">
-        <x:v>3503674</x:v>
+        <x:v>218879</x:v>
       </x:c>
       <x:c r="G40" s="0">
-        <x:v>17.0843089621974</x:v>
+        <x:v>0.707977122090902</x:v>
       </x:c>
       <x:c r="H40" s="0">
-        <x:v>-39836</x:v>
+        <x:v>-61321</x:v>
       </x:c>
       <x:c r="I40" s="0">
-        <x:v>66.709</x:v>
+        <x:v>64.643</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:9">
@@ -1700,28 +1700,28 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="B41" s="0">
-        <x:v>114720</x:v>
+        <x:v>159672</x:v>
       </x:c>
       <x:c r="C41" s="0">
-        <x:v>64.399</x:v>
+        <x:v>65.018</x:v>
       </x:c>
       <x:c r="D41" s="0">
-        <x:v>161032</x:v>
+        <x:v>221670</x:v>
       </x:c>
       <x:c r="E41" s="0">
-        <x:v>64.107</x:v>
+        <x:v>64.784</x:v>
       </x:c>
       <x:c r="F41" s="0">
-        <x:v>275752</x:v>
+        <x:v>381342</x:v>
       </x:c>
       <x:c r="G41" s="0">
-        <x:v>1.34459780360384</x:v>
+        <x:v>1.2334733423142</x:v>
       </x:c>
       <x:c r="H41" s="0">
-        <x:v>-46312</x:v>
+        <x:v>-61998</x:v>
       </x:c>
       <x:c r="I41" s="0">
-        <x:v>63.385</x:v>
+        <x:v>64.179</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:9">
@@ -1729,28 +1729,28 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="B42" s="0">
-        <x:v>143038</x:v>
+        <x:v>539021</x:v>
       </x:c>
       <x:c r="C42" s="0">
-        <x:v>64.457</x:v>
+        <x:v>65.186</x:v>
       </x:c>
       <x:c r="D42" s="0">
-        <x:v>189941</x:v>
+        <x:v>610215</x:v>
       </x:c>
       <x:c r="E42" s="0">
-        <x:v>64.691</x:v>
+        <x:v>65.537</x:v>
       </x:c>
       <x:c r="F42" s="0">
-        <x:v>332979</x:v>
+        <x:v>1149236</x:v>
       </x:c>
       <x:c r="G42" s="0">
-        <x:v>1.62364309976429</x:v>
+        <x:v>3.71727208130181</x:v>
       </x:c>
       <x:c r="H42" s="0">
-        <x:v>-46903</x:v>
+        <x:v>-71194</x:v>
       </x:c>
       <x:c r="I42" s="0">
-        <x:v>65.403</x:v>
+        <x:v>68.193</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:9">
@@ -1758,28 +1758,28 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="B43" s="0">
-        <x:v>236336</x:v>
+        <x:v>2465796</x:v>
       </x:c>
       <x:c r="C43" s="0">
-        <x:v>64.153</x:v>
+        <x:v>64.897</x:v>
       </x:c>
       <x:c r="D43" s="0">
-        <x:v>294445</x:v>
+        <x:v>2562900</x:v>
       </x:c>
       <x:c r="E43" s="0">
-        <x:v>64.116</x:v>
+        <x:v>64.968</x:v>
       </x:c>
       <x:c r="F43" s="0">
-        <x:v>530781</x:v>
+        <x:v>5028696</x:v>
       </x:c>
       <x:c r="G43" s="0">
-        <x:v>2.58814792565294</x:v>
+        <x:v>16.265615805765</x:v>
       </x:c>
       <x:c r="H43" s="0">
-        <x:v>-58109</x:v>
+        <x:v>-97104</x:v>
       </x:c>
       <x:c r="I43" s="0">
-        <x:v>63.966</x:v>
+        <x:v>66.785</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:9">
@@ -1787,28 +1787,28 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="B44" s="0">
-        <x:v>58735</x:v>
+        <x:v>168376</x:v>
       </x:c>
       <x:c r="C44" s="0">
-        <x:v>64.067</x:v>
+        <x:v>64.395</x:v>
       </x:c>
       <x:c r="D44" s="0">
-        <x:v>120493</x:v>
+        <x:v>270449</x:v>
       </x:c>
       <x:c r="E44" s="0">
-        <x:v>64.397</x:v>
+        <x:v>64.893</x:v>
       </x:c>
       <x:c r="F44" s="0">
-        <x:v>179228</x:v>
+        <x:v>438825</x:v>
       </x:c>
       <x:c r="G44" s="0">
-        <x:v>0.873935910326339</x:v>
+        <x:v>1.4194055190381</x:v>
       </x:c>
       <x:c r="H44" s="0">
-        <x:v>-61758</x:v>
+        <x:v>-102073</x:v>
       </x:c>
       <x:c r="I44" s="0">
-        <x:v>64.71</x:v>
+        <x:v>65.715</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:9">
@@ -1816,28 +1816,28 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="B45" s="0">
-        <x:v>514837</x:v>
+        <x:v>34834</x:v>
       </x:c>
       <x:c r="C45" s="0">
-        <x:v>64.448</x:v>
+        <x:v>65.062</x:v>
       </x:c>
       <x:c r="D45" s="0">
-        <x:v>588557</x:v>
+        <x:v>150489</x:v>
       </x:c>
       <x:c r="E45" s="0">
-        <x:v>64.298</x:v>
+        <x:v>65.936</x:v>
       </x:c>
       <x:c r="F45" s="0">
-        <x:v>1103394</x:v>
+        <x:v>185323</x:v>
       </x:c>
       <x:c r="G45" s="0">
-        <x:v>5.38027339388165</x:v>
+        <x:v>0.599438247603709</x:v>
       </x:c>
       <x:c r="H45" s="0">
-        <x:v>-73720</x:v>
+        <x:v>-115655</x:v>
       </x:c>
       <x:c r="I45" s="0">
-        <x:v>63.252</x:v>
+        <x:v>66.199</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:9">
@@ -1845,28 +1845,28 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="B46" s="0">
-        <x:v>131579</x:v>
+        <x:v>332897</x:v>
       </x:c>
       <x:c r="C46" s="0">
-        <x:v>63.838</x:v>
+        <x:v>64.799</x:v>
       </x:c>
       <x:c r="D46" s="0">
-        <x:v>211213</x:v>
+        <x:v>499516</x:v>
       </x:c>
       <x:c r="E46" s="0">
-        <x:v>64.408</x:v>
+        <x:v>65.083</x:v>
       </x:c>
       <x:c r="F46" s="0">
-        <x:v>342792</x:v>
+        <x:v>832413</x:v>
       </x:c>
       <x:c r="G46" s="0">
-        <x:v>1.67149239277672</x:v>
+        <x:v>2.69248927549493</x:v>
       </x:c>
       <x:c r="H46" s="0">
-        <x:v>-79634</x:v>
+        <x:v>-166619</x:v>
       </x:c>
       <x:c r="I46" s="0">
-        <x:v>65.349</x:v>
+        <x:v>65.65</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:9">
@@ -1874,28 +1874,28 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="B47" s="0">
-        <x:v>23024</x:v>
+        <x:v>734989</x:v>
       </x:c>
       <x:c r="C47" s="0">
-        <x:v>64.34</x:v>
+        <x:v>65.056</x:v>
       </x:c>
       <x:c r="D47" s="0">
-        <x:v>129444</x:v>
+        <x:v>1011127</x:v>
       </x:c>
       <x:c r="E47" s="0">
-        <x:v>65.829</x:v>
+        <x:v>65.243</x:v>
       </x:c>
       <x:c r="F47" s="0">
-        <x:v>152468</x:v>
+        <x:v>1746116</x:v>
       </x:c>
       <x:c r="G47" s="0">
-        <x:v>0.743451136963177</x:v>
+        <x:v>5.64791588282511</x:v>
       </x:c>
       <x:c r="H47" s="0">
-        <x:v>-106420</x:v>
+        <x:v>-276138</x:v>
       </x:c>
       <x:c r="I47" s="0">
-        <x:v>66.151</x:v>
+        <x:v>65.74</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:9">
@@ -1903,28 +1903,28 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="B48" s="0">
-        <x:v>346164</x:v>
+        <x:v>400181</x:v>
       </x:c>
       <x:c r="C48" s="0">
-        <x:v>65.297</x:v>
+        <x:v>65.485</x:v>
       </x:c>
       <x:c r="D48" s="0">
-        <x:v>600918</x:v>
+        <x:v>697650</x:v>
       </x:c>
       <x:c r="E48" s="0">
-        <x:v>64.589</x:v>
+        <x:v>64.829</x:v>
       </x:c>
       <x:c r="F48" s="0">
-        <x:v>947082</x:v>
+        <x:v>1097831</x:v>
       </x:c>
       <x:c r="G48" s="0">
-        <x:v>4.61807848005719</x:v>
+        <x:v>3.55099955647722</x:v>
       </x:c>
       <x:c r="H48" s="0">
-        <x:v>-254754</x:v>
+        <x:v>-297469</x:v>
       </x:c>
       <x:c r="I48" s="0">
-        <x:v>63.627</x:v>
+        <x:v>63.945</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:9">
@@ -1932,28 +1932,28 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="B49" s="0">
-        <x:v>61315</x:v>
+        <x:v>64773</x:v>
       </x:c>
       <x:c r="C49" s="0">
-        <x:v>65.347</x:v>
+        <x:v>65.424</x:v>
       </x:c>
       <x:c r="D49" s="0">
-        <x:v>422937</x:v>
+        <x:v>431553</x:v>
       </x:c>
       <x:c r="E49" s="0">
+        <x:v>65.295</x:v>
+      </x:c>
+      <x:c r="F49" s="0">
+        <x:v>496326</x:v>
+      </x:c>
+      <x:c r="G49" s="0">
+        <x:v>1.60539591783081</x:v>
+      </x:c>
+      <x:c r="H49" s="0">
+        <x:v>-366780</x:v>
+      </x:c>
+      <x:c r="I49" s="0">
         <x:v>65.272</x:v>
-      </x:c>
-      <x:c r="F49" s="0">
-        <x:v>484252</x:v>
-      </x:c>
-      <x:c r="G49" s="0">
-        <x:v>2.36126728216211</x:v>
-      </x:c>
-      <x:c r="H49" s="0">
-        <x:v>-361622</x:v>
-      </x:c>
-      <x:c r="I49" s="0">
-        <x:v>65.259</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/app/fonlar/haftalik-yatirim-fonlarinin-en-cok-tercih-ettigi-hisseler/data/tercih-edilen-hisseler.xlsx
+++ b/app/fonlar/haftalik-yatirim-fonlarinin-en-cok-tercih-ettigi-hisseler/data/tercih-edilen-hisseler.xlsx
@@ -46,139 +46,145 @@
     <x:t>BANK OF AMERICA</x:t>
   </x:si>
   <x:si>
+    <x:t>VAKIF</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DENIZ</x:t>
+  </x:si>
+  <x:si>
     <x:t>GEDIK</x:t>
   </x:si>
   <x:si>
-    <x:t>VAKIF</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DENIZ</x:t>
+    <x:t>IKON</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SEKER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TEB</x:t>
   </x:si>
   <x:si>
     <x:t>ZIRAAT</x:t>
   </x:si>
   <x:si>
-    <x:t>SEKER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IKON</x:t>
+    <x:t>FIBA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALNUS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRIVE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BURGAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ACAR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GLOBAL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DESTEK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PIRAMIT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIZIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NCM INVESTMENT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DINAMIK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AHLATCI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ANADOLU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALTERNATIF</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HSBC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UNLU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PUSULA YAT.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ICBC TURKEY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INTEGRAL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INVEST AZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TERA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BULLS YATIRIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BTCTURK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ING</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PHILLIP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ATA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OSMANLI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INFO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HALK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MIDAS</x:t>
   </x:si>
   <x:si>
     <x:t>IS</x:t>
   </x:si>
   <x:si>
-    <x:t>TEB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALNUS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FIBA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BURGAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TRIVE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ICBC TURKEY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ACAR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DESTEK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIZIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DINAMIK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALTERNATIF</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BTCTURK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ANADOLU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HSBC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UNLU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AHLATCI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INVEST AZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MIDAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INTEGRAL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TERA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ING</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PUSULA YAT.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BULLS YATIRIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HALK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GLOBAL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ATA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PHILLIP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OSMANLI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INFO</x:t>
-  </x:si>
-  <x:si>
     <x:t>MEKSA</x:t>
   </x:si>
   <x:si>
+    <x:t>QNB YATIRIM</x:t>
+  </x:si>
+  <x:si>
     <x:t>OYAK</x:t>
   </x:si>
   <x:si>
     <x:t>TACIRLER</x:t>
   </x:si>
   <x:si>
+    <x:t>KUVEYT TURK</x:t>
+  </x:si>
+  <x:si>
     <x:t>AK</x:t>
   </x:si>
   <x:si>
-    <x:t>QNB YATIRIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KUVEYT TURK</x:t>
-  </x:si>
-  <x:si>
     <x:t>GARANTI BBVA</x:t>
   </x:si>
   <x:si>
+    <x:t>MARBAS</x:t>
+  </x:si>
+  <x:si>
     <x:t>A1 CAPITAL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MARBAS</x:t>
   </x:si>
   <x:si>
     <x:t>YATIRIM FINANSMAN</x:t>
@@ -532,7 +538,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:I49"/>
+  <x:dimension ref="A1:I51"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:9">
@@ -569,28 +575,28 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B2" s="0">
-        <x:v>1531348</x:v>
+        <x:v>1958979</x:v>
       </x:c>
       <x:c r="C2" s="0">
-        <x:v>65.555</x:v>
+        <x:v>65.939</x:v>
       </x:c>
       <x:c r="D2" s="0">
-        <x:v>993199</x:v>
+        <x:v>1152729</x:v>
       </x:c>
       <x:c r="E2" s="0">
-        <x:v>65.179</x:v>
+        <x:v>65.502</x:v>
       </x:c>
       <x:c r="F2" s="0">
-        <x:v>2524547</x:v>
+        <x:v>3111708</x:v>
       </x:c>
       <x:c r="G2" s="0">
-        <x:v>8.16579717397841</x:v>
+        <x:v>7.71055278254667</x:v>
       </x:c>
       <x:c r="H2" s="0">
-        <x:v>538149</x:v>
+        <x:v>806250</x:v>
       </x:c>
       <x:c r="I2" s="0">
-        <x:v>66.249</x:v>
+        <x:v>66.564</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:9">
@@ -598,10 +604,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B3" s="0">
-        <x:v>351531</x:v>
+        <x:v>655932</x:v>
       </x:c>
       <x:c r="C3" s="0">
-        <x:v>65.91</x:v>
+        <x:v>66.662</x:v>
       </x:c>
       <x:c r="D3" s="0">
         <x:v>3923</x:v>
@@ -610,16 +616,16 @@
         <x:v>66.656</x:v>
       </x:c>
       <x:c r="F3" s="0">
-        <x:v>355454</x:v>
+        <x:v>659855</x:v>
       </x:c>
       <x:c r="G3" s="0">
-        <x:v>1.14973706913728</x:v>
+        <x:v>1.63506563158475</x:v>
       </x:c>
       <x:c r="H3" s="0">
-        <x:v>347608</x:v>
+        <x:v>652009</x:v>
       </x:c>
       <x:c r="I3" s="0">
-        <x:v>65.901</x:v>
+        <x:v>66.662</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:9">
@@ -627,28 +633,28 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B4" s="0">
-        <x:v>915912</x:v>
+        <x:v>1065343</x:v>
       </x:c>
       <x:c r="C4" s="0">
-        <x:v>65.288</x:v>
+        <x:v>65.768</x:v>
       </x:c>
       <x:c r="D4" s="0">
-        <x:v>591565</x:v>
+        <x:v>788310</x:v>
       </x:c>
       <x:c r="E4" s="0">
-        <x:v>65.457</x:v>
+        <x:v>65.545</x:v>
       </x:c>
       <x:c r="F4" s="0">
-        <x:v>1507477</x:v>
+        <x:v>1853653</x:v>
       </x:c>
       <x:c r="G4" s="0">
-        <x:v>4.8760238674255</x:v>
+        <x:v>4.5931974648733</x:v>
       </x:c>
       <x:c r="H4" s="0">
-        <x:v>324347</x:v>
+        <x:v>277033</x:v>
       </x:c>
       <x:c r="I4" s="0">
-        <x:v>64.978</x:v>
+        <x:v>66.402</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:9">
@@ -656,28 +662,28 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B5" s="0">
-        <x:v>915951</x:v>
+        <x:v>1209662</x:v>
       </x:c>
       <x:c r="C5" s="0">
-        <x:v>65.479</x:v>
+        <x:v>66.232</x:v>
       </x:c>
       <x:c r="D5" s="0">
-        <x:v>610268</x:v>
+        <x:v>972743</x:v>
       </x:c>
       <x:c r="E5" s="0">
-        <x:v>65.007</x:v>
+        <x:v>66.136</x:v>
       </x:c>
       <x:c r="F5" s="0">
-        <x:v>1526219</x:v>
+        <x:v>2182405</x:v>
       </x:c>
       <x:c r="G5" s="0">
-        <x:v>4.93664597928743</x:v>
+        <x:v>5.4078174897496</x:v>
       </x:c>
       <x:c r="H5" s="0">
-        <x:v>305683</x:v>
+        <x:v>236919</x:v>
       </x:c>
       <x:c r="I5" s="0">
-        <x:v>66.421</x:v>
+        <x:v>66.626</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:9">
@@ -685,28 +691,28 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B6" s="0">
-        <x:v>701280</x:v>
+        <x:v>1193523</x:v>
       </x:c>
       <x:c r="C6" s="0">
-        <x:v>65.345</x:v>
+        <x:v>65.711</x:v>
       </x:c>
       <x:c r="D6" s="0">
-        <x:v>616837</x:v>
+        <x:v>1000460</x:v>
       </x:c>
       <x:c r="E6" s="0">
-        <x:v>65.213</x:v>
+        <x:v>66.237</x:v>
       </x:c>
       <x:c r="F6" s="0">
-        <x:v>1318117</x:v>
+        <x:v>2193983</x:v>
       </x:c>
       <x:c r="G6" s="0">
-        <x:v>4.26352770361293</x:v>
+        <x:v>5.43650680767928</x:v>
       </x:c>
       <x:c r="H6" s="0">
-        <x:v>84443</x:v>
+        <x:v>193063</x:v>
       </x:c>
       <x:c r="I6" s="0">
-        <x:v>66.309</x:v>
+        <x:v>62.986</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:9">
@@ -714,28 +720,28 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="B7" s="0">
-        <x:v>937601</x:v>
+        <x:v>1206893</x:v>
       </x:c>
       <x:c r="C7" s="0">
-        <x:v>64.931</x:v>
+        <x:v>66.394</x:v>
       </x:c>
       <x:c r="D7" s="0">
-        <x:v>860887</x:v>
+        <x:v>1087998</x:v>
       </x:c>
       <x:c r="E7" s="0">
-        <x:v>64.997</x:v>
+        <x:v>66.437</x:v>
       </x:c>
       <x:c r="F7" s="0">
-        <x:v>1798488</x:v>
+        <x:v>2294891</x:v>
       </x:c>
       <x:c r="G7" s="0">
-        <x:v>5.81731622656821</x:v>
+        <x:v>5.68654841189832</x:v>
       </x:c>
       <x:c r="H7" s="0">
-        <x:v>76714</x:v>
+        <x:v>118895</x:v>
       </x:c>
       <x:c r="I7" s="0">
-        <x:v>64.198</x:v>
+        <x:v>66.005</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:9">
@@ -743,28 +749,28 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B8" s="0">
-        <x:v>127784</x:v>
+        <x:v>157567</x:v>
       </x:c>
       <x:c r="C8" s="0">
-        <x:v>65.558</x:v>
+        <x:v>65.844</x:v>
       </x:c>
       <x:c r="D8" s="0">
-        <x:v>59530</x:v>
+        <x:v>76910</x:v>
       </x:c>
       <x:c r="E8" s="0">
-        <x:v>64.646</x:v>
+        <x:v>65.26</x:v>
       </x:c>
       <x:c r="F8" s="0">
-        <x:v>187314</x:v>
+        <x:v>234477</x:v>
       </x:c>
       <x:c r="G8" s="0">
-        <x:v>0.605878255325249</x:v>
+        <x:v>0.581014441198594</x:v>
       </x:c>
       <x:c r="H8" s="0">
-        <x:v>68254</x:v>
+        <x:v>80657</x:v>
       </x:c>
       <x:c r="I8" s="0">
-        <x:v>66.354</x:v>
+        <x:v>66.401</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:9">
@@ -772,28 +778,28 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="B9" s="0">
-        <x:v>796960</x:v>
+        <x:v>115573</x:v>
       </x:c>
       <x:c r="C9" s="0">
-        <x:v>65.879</x:v>
+        <x:v>65.729</x:v>
       </x:c>
       <x:c r="D9" s="0">
-        <x:v>742874</x:v>
+        <x:v>84996</x:v>
       </x:c>
       <x:c r="E9" s="0">
-        <x:v>65.985</x:v>
+        <x:v>66.27</x:v>
       </x:c>
       <x:c r="F9" s="0">
-        <x:v>1539834</x:v>
+        <x:v>200569</x:v>
       </x:c>
       <x:c r="G9" s="0">
-        <x:v>4.98068450521851</x:v>
+        <x:v>0.496993246487975</x:v>
       </x:c>
       <x:c r="H9" s="0">
-        <x:v>54086</x:v>
+        <x:v>30577</x:v>
       </x:c>
       <x:c r="I9" s="0">
-        <x:v>64.424</x:v>
+        <x:v>64.228</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:9">
@@ -801,28 +807,28 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B10" s="0">
-        <x:v>1372871</x:v>
+        <x:v>1131460</x:v>
       </x:c>
       <x:c r="C10" s="0">
-        <x:v>64.605</x:v>
+        <x:v>65.36</x:v>
       </x:c>
       <x:c r="D10" s="0">
-        <x:v>1320291</x:v>
+        <x:v>1108806</x:v>
       </x:c>
       <x:c r="E10" s="0">
-        <x:v>64.823</x:v>
+        <x:v>65.524</x:v>
       </x:c>
       <x:c r="F10" s="0">
-        <x:v>2693162</x:v>
+        <x:v>2240266</x:v>
       </x:c>
       <x:c r="G10" s="0">
-        <x:v>8.71119240349498</x:v>
+        <x:v>5.55119221981776</x:v>
       </x:c>
       <x:c r="H10" s="0">
-        <x:v>52580</x:v>
+        <x:v>22654</x:v>
       </x:c>
       <x:c r="I10" s="0">
-        <x:v>59.112</x:v>
+        <x:v>57.328</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:9">
@@ -830,28 +836,28 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B11" s="0">
-        <x:v>98178</x:v>
+        <x:v>43037</x:v>
       </x:c>
       <x:c r="C11" s="0">
-        <x:v>65.4</x:v>
+        <x:v>65.589</x:v>
       </x:c>
       <x:c r="D11" s="0">
-        <x:v>58984</x:v>
+        <x:v>20483</x:v>
       </x:c>
       <x:c r="E11" s="0">
-        <x:v>65.773</x:v>
+        <x:v>65.937</x:v>
       </x:c>
       <x:c r="F11" s="0">
-        <x:v>157162</x:v>
+        <x:v>63520</x:v>
       </x:c>
       <x:c r="G11" s="0">
-        <x:v>0.508349820960669</x:v>
+        <x:v>0.157397259880221</x:v>
       </x:c>
       <x:c r="H11" s="0">
-        <x:v>39194</x:v>
+        <x:v>22554</x:v>
       </x:c>
       <x:c r="I11" s="0">
-        <x:v>64.838</x:v>
+        <x:v>65.273</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:9">
@@ -859,28 +865,28 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="B12" s="0">
-        <x:v>147402</x:v>
+        <x:v>198721</x:v>
       </x:c>
       <x:c r="C12" s="0">
-        <x:v>65.344</x:v>
+        <x:v>65.9</x:v>
       </x:c>
       <x:c r="D12" s="0">
-        <x:v>119393</x:v>
+        <x:v>177871</x:v>
       </x:c>
       <x:c r="E12" s="0">
-        <x:v>65.209</x:v>
+        <x:v>65.893</x:v>
       </x:c>
       <x:c r="F12" s="0">
-        <x:v>266795</x:v>
+        <x:v>376592</x:v>
       </x:c>
       <x:c r="G12" s="0">
-        <x:v>0.862964269245758</x:v>
+        <x:v>0.933163553098431</x:v>
       </x:c>
       <x:c r="H12" s="0">
-        <x:v>28009</x:v>
+        <x:v>20850</x:v>
       </x:c>
       <x:c r="I12" s="0">
-        <x:v>65.917</x:v>
+        <x:v>65.959</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:9">
@@ -888,28 +894,28 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B13" s="0">
-        <x:v>42502</x:v>
+        <x:v>71720</x:v>
       </x:c>
       <x:c r="C13" s="0">
-        <x:v>65.564</x:v>
+        <x:v>66.06</x:v>
       </x:c>
       <x:c r="D13" s="0">
-        <x:v>15105</x:v>
+        <x:v>61846</x:v>
       </x:c>
       <x:c r="E13" s="0">
-        <x:v>65.393</x:v>
+        <x:v>66.271</x:v>
       </x:c>
       <x:c r="F13" s="0">
-        <x:v>57607</x:v>
+        <x:v>133566</x:v>
       </x:c>
       <x:c r="G13" s="0">
-        <x:v>0.186333262086772</x:v>
+        <x:v>0.330965403229875</x:v>
       </x:c>
       <x:c r="H13" s="0">
-        <x:v>27397</x:v>
+        <x:v>9874</x:v>
       </x:c>
       <x:c r="I13" s="0">
-        <x:v>65.659</x:v>
+        <x:v>64.738</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:9">
@@ -917,28 +923,28 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="B14" s="0">
-        <x:v>55493</x:v>
+        <x:v>61503</x:v>
       </x:c>
       <x:c r="C14" s="0">
-        <x:v>64.722</x:v>
+        <x:v>64.953</x:v>
       </x:c>
       <x:c r="D14" s="0">
-        <x:v>38371</x:v>
+        <x:v>52106</x:v>
       </x:c>
       <x:c r="E14" s="0">
-        <x:v>65.377</x:v>
+        <x:v>65.902</x:v>
       </x:c>
       <x:c r="F14" s="0">
-        <x:v>93864</x:v>
+        <x:v>113609</x:v>
       </x:c>
       <x:c r="G14" s="0">
-        <x:v>0.303608681453865</x:v>
+        <x:v>0.281513622445404</x:v>
       </x:c>
       <x:c r="H14" s="0">
-        <x:v>17122</x:v>
+        <x:v>9397</x:v>
       </x:c>
       <x:c r="I14" s="0">
-        <x:v>63.253</x:v>
+        <x:v>59.691</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:9">
@@ -946,28 +952,28 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B15" s="0">
-        <x:v>50744</x:v>
+        <x:v>104554</x:v>
       </x:c>
       <x:c r="C15" s="0">
-        <x:v>65.477</x:v>
+        <x:v>65.827</x:v>
       </x:c>
       <x:c r="D15" s="0">
-        <x:v>46368</x:v>
+        <x:v>103185</x:v>
       </x:c>
       <x:c r="E15" s="0">
-        <x:v>65.847</x:v>
+        <x:v>65.877</x:v>
       </x:c>
       <x:c r="F15" s="0">
-        <x:v>97112</x:v>
+        <x:v>207739</x:v>
       </x:c>
       <x:c r="G15" s="0">
-        <x:v>0.314114530313514</x:v>
+        <x:v>0.514759908221935</x:v>
       </x:c>
       <x:c r="H15" s="0">
-        <x:v>4376</x:v>
+        <x:v>1369</x:v>
       </x:c>
       <x:c r="I15" s="0">
-        <x:v>61.559</x:v>
+        <x:v>62.042</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:9">
@@ -975,28 +981,28 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B16" s="0">
-        <x:v>15170</x:v>
+        <x:v>141251</x:v>
       </x:c>
       <x:c r="C16" s="0">
-        <x:v>65.608</x:v>
+        <x:v>66.052</x:v>
       </x:c>
       <x:c r="D16" s="0">
-        <x:v>13632</x:v>
+        <x:v>141093</x:v>
       </x:c>
       <x:c r="E16" s="0">
-        <x:v>65.837</x:v>
+        <x:v>65.502</x:v>
       </x:c>
       <x:c r="F16" s="0">
-        <x:v>28802</x:v>
+        <x:v>282344</x:v>
       </x:c>
       <x:c r="G16" s="0">
-        <x:v>0.0931617792043191</x:v>
+        <x:v>0.699624873167841</x:v>
       </x:c>
       <x:c r="H16" s="0">
-        <x:v>1538</x:v>
+        <x:v>158</x:v>
       </x:c>
       <x:c r="I16" s="0">
-        <x:v>63.573</x:v>
+        <x:v>557.728</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:9">
@@ -1004,28 +1010,28 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B17" s="0">
-        <x:v>81554</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C17" s="0">
-        <x:v>65.37</x:v>
+        <x:v>66.14</x:v>
       </x:c>
       <x:c r="D17" s="0">
-        <x:v>80675</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E17" s="0">
-        <x:v>65.452</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F17" s="0">
-        <x:v>162229</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="G17" s="0">
-        <x:v>0.524739333328848</x:v>
+        <x:v>0.000123895827991358</x:v>
       </x:c>
       <x:c r="H17" s="0">
-        <x:v>879</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="I17" s="0">
-        <x:v>57.783</x:v>
+        <x:v>66.14</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:9">
@@ -1033,10 +1039,10 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B18" s="0">
-        <x:v>50</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C18" s="0">
-        <x:v>66.14</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="D18" s="0">
         <x:v>0</x:v>
@@ -1045,16 +1051,16 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F18" s="0">
-        <x:v>50</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="G18" s="0">
-        <x:v>0.000161727968898547</x:v>
+        <x:v>2.47791655982716E-06</x:v>
       </x:c>
       <x:c r="H18" s="0">
-        <x:v>50</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="I18" s="0">
-        <x:v>66.14</x:v>
+        <x:v>67</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:9">
@@ -1068,22 +1074,22 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D19" s="0">
-        <x:v>25</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="E19" s="0">
-        <x:v>63.92</x:v>
+        <x:v>65.981</x:v>
       </x:c>
       <x:c r="F19" s="0">
-        <x:v>25</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="G19" s="0">
-        <x:v>8.08639844492736E-05</x:v>
+        <x:v>0.000128851661111013</x:v>
       </x:c>
       <x:c r="H19" s="0">
-        <x:v>-25</x:v>
+        <x:v>-52</x:v>
       </x:c>
       <x:c r="I19" s="0">
-        <x:v>63.92</x:v>
+        <x:v>65.981</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:9">
@@ -1091,28 +1097,28 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="B20" s="0">
-        <x:v>30</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C20" s="0">
-        <x:v>62.833</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D20" s="0">
-        <x:v>180</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="E20" s="0">
-        <x:v>65.322</x:v>
+        <x:v>67.428</x:v>
       </x:c>
       <x:c r="F20" s="0">
-        <x:v>210</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="G20" s="0">
-        <x:v>0.000679257469373898</x:v>
+        <x:v>0.000359297901174939</x:v>
       </x:c>
       <x:c r="H20" s="0">
-        <x:v>-150</x:v>
+        <x:v>-145</x:v>
       </x:c>
       <x:c r="I20" s="0">
-        <x:v>65.82</x:v>
+        <x:v>67.428</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:9">
@@ -1120,28 +1126,28 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="B21" s="0">
-        <x:v>600</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C21" s="0">
-        <x:v>65.3</x:v>
+        <x:v>62.833</x:v>
       </x:c>
       <x:c r="D21" s="0">
-        <x:v>1542</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="E21" s="0">
-        <x:v>66.307</x:v>
+        <x:v>65.322</x:v>
       </x:c>
       <x:c r="F21" s="0">
-        <x:v>2142</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="G21" s="0">
-        <x:v>0.00692842618761376</x:v>
+        <x:v>0.000520362477563705</x:v>
       </x:c>
       <x:c r="H21" s="0">
-        <x:v>-942</x:v>
+        <x:v>-150</x:v>
       </x:c>
       <x:c r="I21" s="0">
-        <x:v>66.948</x:v>
+        <x:v>65.82</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:9">
@@ -1149,28 +1155,28 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="B22" s="0">
-        <x:v>27877</x:v>
+        <x:v>42302</x:v>
       </x:c>
       <x:c r="C22" s="0">
-        <x:v>64.661</x:v>
+        <x:v>66.392</x:v>
       </x:c>
       <x:c r="D22" s="0">
-        <x:v>29052</x:v>
+        <x:v>43414</x:v>
       </x:c>
       <x:c r="E22" s="0">
-        <x:v>64.996</x:v>
+        <x:v>65.991</x:v>
       </x:c>
       <x:c r="F22" s="0">
-        <x:v>56929</x:v>
+        <x:v>85716</x:v>
       </x:c>
       <x:c r="G22" s="0">
-        <x:v>0.184140230828508</x:v>
+        <x:v>0.212397095842145</x:v>
       </x:c>
       <x:c r="H22" s="0">
-        <x:v>-1175</x:v>
+        <x:v>-1112</x:v>
       </x:c>
       <x:c r="I22" s="0">
-        <x:v>72.94</x:v>
+        <x:v>50.748</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:9">
@@ -1193,7 +1199,7 @@
         <x:v>2844</x:v>
       </x:c>
       <x:c r="G23" s="0">
-        <x:v>0.00919908687094936</x:v>
+        <x:v>0.00704719469614846</x:v>
       </x:c>
       <x:c r="H23" s="0">
         <x:v>-1410</x:v>
@@ -1207,28 +1213,28 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="B24" s="0">
-        <x:v>1000</x:v>
+        <x:v>600</x:v>
       </x:c>
       <x:c r="C24" s="0">
-        <x:v>66.7</x:v>
+        <x:v>65.3</x:v>
       </x:c>
       <x:c r="D24" s="0">
-        <x:v>2577</x:v>
+        <x:v>2225</x:v>
       </x:c>
       <x:c r="E24" s="0">
-        <x:v>65.956</x:v>
+        <x:v>66.546</x:v>
       </x:c>
       <x:c r="F24" s="0">
-        <x:v>3577</x:v>
+        <x:v>2825</x:v>
       </x:c>
       <x:c r="G24" s="0">
-        <x:v>0.0115700188950021</x:v>
+        <x:v>0.00700011428151174</x:v>
       </x:c>
       <x:c r="H24" s="0">
-        <x:v>-1577</x:v>
+        <x:v>-1625</x:v>
       </x:c>
       <x:c r="I24" s="0">
-        <x:v>65.484</x:v>
+        <x:v>67.006</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:9">
@@ -1236,28 +1242,28 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="B25" s="0">
-        <x:v>40393</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="C25" s="0">
-        <x:v>64.422</x:v>
+        <x:v>66.7</x:v>
       </x:c>
       <x:c r="D25" s="0">
-        <x:v>42511</x:v>
+        <x:v>2872</x:v>
       </x:c>
       <x:c r="E25" s="0">
-        <x:v>65.06</x:v>
+        <x:v>66.15</x:v>
       </x:c>
       <x:c r="F25" s="0">
-        <x:v>82904</x:v>
+        <x:v>3872</x:v>
       </x:c>
       <x:c r="G25" s="0">
-        <x:v>0.268157910671303</x:v>
+        <x:v>0.00959449291965078</x:v>
       </x:c>
       <x:c r="H25" s="0">
-        <x:v>-2118</x:v>
+        <x:v>-1872</x:v>
       </x:c>
       <x:c r="I25" s="0">
-        <x:v>77.229</x:v>
+        <x:v>65.856</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:9">
@@ -1265,28 +1271,28 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="B26" s="0">
-        <x:v>26136</x:v>
+        <x:v>40543</x:v>
       </x:c>
       <x:c r="C26" s="0">
-        <x:v>65.722</x:v>
+        <x:v>64.435</x:v>
       </x:c>
       <x:c r="D26" s="0">
-        <x:v>29543</x:v>
+        <x:v>43295</x:v>
       </x:c>
       <x:c r="E26" s="0">
-        <x:v>65.333</x:v>
+        <x:v>65.1</x:v>
       </x:c>
       <x:c r="F26" s="0">
-        <x:v>55679</x:v>
+        <x:v>83838</x:v>
       </x:c>
       <x:c r="G26" s="0">
-        <x:v>0.180097031606044</x:v>
+        <x:v>0.20774356854279</x:v>
       </x:c>
       <x:c r="H26" s="0">
-        <x:v>-3407</x:v>
+        <x:v>-2752</x:v>
       </x:c>
       <x:c r="I26" s="0">
-        <x:v>62.343</x:v>
+        <x:v>74.901</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:9">
@@ -1294,28 +1300,28 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="B27" s="0">
-        <x:v>9968</x:v>
+        <x:v>182602</x:v>
       </x:c>
       <x:c r="C27" s="0">
-        <x:v>64.907</x:v>
+        <x:v>64.917</x:v>
       </x:c>
       <x:c r="D27" s="0">
-        <x:v>18680</x:v>
+        <x:v>185840</x:v>
       </x:c>
       <x:c r="E27" s="0">
-        <x:v>65.557</x:v>
+        <x:v>64.932</x:v>
       </x:c>
       <x:c r="F27" s="0">
-        <x:v>28648</x:v>
+        <x:v>368442</x:v>
       </x:c>
       <x:c r="G27" s="0">
-        <x:v>0.0926636570601116</x:v>
+        <x:v>0.91296853313584</x:v>
       </x:c>
       <x:c r="H27" s="0">
-        <x:v>-8712</x:v>
+        <x:v>-3238</x:v>
       </x:c>
       <x:c r="I27" s="0">
-        <x:v>66.3</x:v>
+        <x:v>65.75</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:9">
@@ -1323,28 +1329,28 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="B28" s="0">
-        <x:v>814340</x:v>
+        <x:v>18070</x:v>
       </x:c>
       <x:c r="C28" s="0">
-        <x:v>64.874</x:v>
+        <x:v>65.992</x:v>
       </x:c>
       <x:c r="D28" s="0">
-        <x:v>824864</x:v>
+        <x:v>24322</x:v>
       </x:c>
       <x:c r="E28" s="0">
-        <x:v>65.068</x:v>
+        <x:v>66.7</x:v>
       </x:c>
       <x:c r="F28" s="0">
-        <x:v>1639204</x:v>
+        <x:v>42392</x:v>
       </x:c>
       <x:c r="G28" s="0">
-        <x:v>5.30210267060748</x:v>
+        <x:v>0.105043838804193</x:v>
       </x:c>
       <x:c r="H28" s="0">
-        <x:v>-10524</x:v>
+        <x:v>-6252</x:v>
       </x:c>
       <x:c r="I28" s="0">
-        <x:v>80.034</x:v>
+        <x:v>68.747</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:9">
@@ -1352,28 +1358,28 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B29" s="0">
-        <x:v>1379</x:v>
+        <x:v>1479</x:v>
       </x:c>
       <x:c r="C29" s="0">
-        <x:v>65.576</x:v>
+        <x:v>65.719</x:v>
       </x:c>
       <x:c r="D29" s="0">
-        <x:v>11931</x:v>
+        <x:v>12148</x:v>
       </x:c>
       <x:c r="E29" s="0">
-        <x:v>64.77</x:v>
+        <x:v>64.81</x:v>
       </x:c>
       <x:c r="F29" s="0">
-        <x:v>13310</x:v>
+        <x:v>13627</x:v>
       </x:c>
       <x:c r="G29" s="0">
-        <x:v>0.0430519853207932</x:v>
+        <x:v>0.0337665689607648</x:v>
       </x:c>
       <x:c r="H29" s="0">
-        <x:v>-10552</x:v>
+        <x:v>-10669</x:v>
       </x:c>
       <x:c r="I29" s="0">
-        <x:v>64.664</x:v>
+        <x:v>64.683</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:9">
@@ -1381,28 +1387,28 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="B30" s="0">
-        <x:v>214505</x:v>
+        <x:v>10478</x:v>
       </x:c>
       <x:c r="C30" s="0">
-        <x:v>65.172</x:v>
+        <x:v>65.007</x:v>
       </x:c>
       <x:c r="D30" s="0">
-        <x:v>226009</x:v>
+        <x:v>23180</x:v>
       </x:c>
       <x:c r="E30" s="0">
-        <x:v>65.485</x:v>
+        <x:v>65.955</x:v>
       </x:c>
       <x:c r="F30" s="0">
-        <x:v>440514</x:v>
+        <x:v>33658</x:v>
       </x:c>
       <x:c r="G30" s="0">
-        <x:v>1.42486868982749</x:v>
+        <x:v>0.0834017155706627</x:v>
       </x:c>
       <x:c r="H30" s="0">
-        <x:v>-11504</x:v>
+        <x:v>-12702</x:v>
       </x:c>
       <x:c r="I30" s="0">
-        <x:v>71.322</x:v>
+        <x:v>66.736</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:9">
@@ -1410,28 +1416,28 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="B31" s="0">
-        <x:v>25432</x:v>
+        <x:v>295551</x:v>
       </x:c>
       <x:c r="C31" s="0">
-        <x:v>64.334</x:v>
+        <x:v>65.705</x:v>
       </x:c>
       <x:c r="D31" s="0">
-        <x:v>37526</x:v>
+        <x:v>309394</x:v>
       </x:c>
       <x:c r="E31" s="0">
-        <x:v>64.584</x:v>
+        <x:v>65.993</x:v>
       </x:c>
       <x:c r="F31" s="0">
-        <x:v>62958</x:v>
+        <x:v>604945</x:v>
       </x:c>
       <x:c r="G31" s="0">
-        <x:v>0.203641389318295</x:v>
+        <x:v>1.49900323328464</x:v>
       </x:c>
       <x:c r="H31" s="0">
-        <x:v>-12094</x:v>
+        <x:v>-13843</x:v>
       </x:c>
       <x:c r="I31" s="0">
-        <x:v>65.109</x:v>
+        <x:v>72.143</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:9">
@@ -1439,28 +1445,28 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="B32" s="0">
-        <x:v>146091</x:v>
+        <x:v>2893</x:v>
       </x:c>
       <x:c r="C32" s="0">
-        <x:v>64.206</x:v>
+        <x:v>66.16</x:v>
       </x:c>
       <x:c r="D32" s="0">
-        <x:v>158304</x:v>
+        <x:v>21375</x:v>
       </x:c>
       <x:c r="E32" s="0">
-        <x:v>64.537</x:v>
+        <x:v>65.672</x:v>
       </x:c>
       <x:c r="F32" s="0">
-        <x:v>304395</x:v>
+        <x:v>24268</x:v>
       </x:c>
       <x:c r="G32" s="0">
-        <x:v>0.984583701857465</x:v>
+        <x:v>0.0601340790738856</x:v>
       </x:c>
       <x:c r="H32" s="0">
-        <x:v>-12213</x:v>
+        <x:v>-18482</x:v>
       </x:c>
       <x:c r="I32" s="0">
-        <x:v>68.496</x:v>
+        <x:v>65.595</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:9">
@@ -1468,28 +1474,28 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="B33" s="0">
-        <x:v>1593</x:v>
+        <x:v>30522</x:v>
       </x:c>
       <x:c r="C33" s="0">
-        <x:v>65.022</x:v>
+        <x:v>64.925</x:v>
       </x:c>
       <x:c r="D33" s="0">
-        <x:v>19950</x:v>
+        <x:v>52193</x:v>
       </x:c>
       <x:c r="E33" s="0">
-        <x:v>65.551</x:v>
+        <x:v>65.996</x:v>
       </x:c>
       <x:c r="F33" s="0">
-        <x:v>21543</x:v>
+        <x:v>82715</x:v>
       </x:c>
       <x:c r="G33" s="0">
-        <x:v>0.069682112679628</x:v>
+        <x:v>0.204960868246104</x:v>
       </x:c>
       <x:c r="H33" s="0">
-        <x:v>-18357</x:v>
+        <x:v>-21671</x:v>
       </x:c>
       <x:c r="I33" s="0">
-        <x:v>65.597</x:v>
+        <x:v>67.503</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:9">
@@ -1497,28 +1503,28 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="B34" s="0">
-        <x:v>379554</x:v>
+        <x:v>29396</x:v>
       </x:c>
       <x:c r="C34" s="0">
-        <x:v>65.066</x:v>
+        <x:v>64.744</x:v>
       </x:c>
       <x:c r="D34" s="0">
-        <x:v>411932</x:v>
+        <x:v>51420</x:v>
       </x:c>
       <x:c r="E34" s="0">
-        <x:v>65.314</x:v>
+        <x:v>65.349</x:v>
       </x:c>
       <x:c r="F34" s="0">
-        <x:v>791486</x:v>
+        <x:v>80816</x:v>
       </x:c>
       <x:c r="G34" s="0">
-        <x:v>2.56010846383271</x:v>
+        <x:v>0.200255304698992</x:v>
       </x:c>
       <x:c r="H34" s="0">
-        <x:v>-32378</x:v>
+        <x:v>-22024</x:v>
       </x:c>
       <x:c r="I34" s="0">
-        <x:v>68.225</x:v>
+        <x:v>66.155</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:9">
@@ -1526,28 +1532,28 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="B35" s="0">
-        <x:v>93170</x:v>
+        <x:v>194685</x:v>
       </x:c>
       <x:c r="C35" s="0">
-        <x:v>65.298</x:v>
+        <x:v>65.866</x:v>
       </x:c>
       <x:c r="D35" s="0">
-        <x:v>129481</x:v>
+        <x:v>216768</x:v>
       </x:c>
       <x:c r="E35" s="0">
-        <x:v>65.294</x:v>
+        <x:v>65.501</x:v>
       </x:c>
       <x:c r="F35" s="0">
-        <x:v>222651</x:v>
+        <x:v>411453</x:v>
       </x:c>
       <x:c r="G35" s="0">
-        <x:v>0.720177880064608</x:v>
+        <x:v>1.01954620229057</x:v>
       </x:c>
       <x:c r="H35" s="0">
-        <x:v>-36311</x:v>
+        <x:v>-22083</x:v>
       </x:c>
       <x:c r="I35" s="0">
-        <x:v>65.282</x:v>
+        <x:v>62.281</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:9">
@@ -1555,28 +1561,28 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="B36" s="0">
-        <x:v>15839</x:v>
+        <x:v>26278</x:v>
       </x:c>
       <x:c r="C36" s="0">
-        <x:v>65.023</x:v>
+        <x:v>65.982</x:v>
       </x:c>
       <x:c r="D36" s="0">
-        <x:v>56154</x:v>
+        <x:v>68219</x:v>
       </x:c>
       <x:c r="E36" s="0">
-        <x:v>65.359</x:v>
+        <x:v>65.716</x:v>
       </x:c>
       <x:c r="F36" s="0">
-        <x:v>71993</x:v>
+        <x:v>94497</x:v>
       </x:c>
       <x:c r="G36" s="0">
-        <x:v>0.232865633298262</x:v>
+        <x:v>0.234155681153988</x:v>
       </x:c>
       <x:c r="H36" s="0">
-        <x:v>-40315</x:v>
+        <x:v>-41941</x:v>
       </x:c>
       <x:c r="I36" s="0">
-        <x:v>65.491</x:v>
+        <x:v>65.549</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:9">
@@ -1584,28 +1590,28 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="B37" s="0">
-        <x:v>134249</x:v>
+        <x:v>238725</x:v>
       </x:c>
       <x:c r="C37" s="0">
-        <x:v>65.109</x:v>
+        <x:v>65.579</x:v>
       </x:c>
       <x:c r="D37" s="0">
-        <x:v>175709</x:v>
+        <x:v>293563</x:v>
       </x:c>
       <x:c r="E37" s="0">
-        <x:v>65</x:v>
+        <x:v>65.535</x:v>
       </x:c>
       <x:c r="F37" s="0">
-        <x:v>309958</x:v>
+        <x:v>532288</x:v>
       </x:c>
       <x:c r="G37" s="0">
-        <x:v>1.00257755567712</x:v>
+        <x:v>1.31896524979728</x:v>
       </x:c>
       <x:c r="H37" s="0">
-        <x:v>-41460</x:v>
+        <x:v>-54838</x:v>
       </x:c>
       <x:c r="I37" s="0">
-        <x:v>64.647</x:v>
+        <x:v>65.341</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:9">
@@ -1613,28 +1619,28 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="B38" s="0">
-        <x:v>190971</x:v>
+        <x:v>259423</x:v>
       </x:c>
       <x:c r="C38" s="0">
-        <x:v>65.015</x:v>
+        <x:v>64.947</x:v>
       </x:c>
       <x:c r="D38" s="0">
-        <x:v>238505</x:v>
+        <x:v>319102</x:v>
       </x:c>
       <x:c r="E38" s="0">
-        <x:v>65.052</x:v>
+        <x:v>65.318</x:v>
       </x:c>
       <x:c r="F38" s="0">
-        <x:v>429476</x:v>
+        <x:v>578525</x:v>
       </x:c>
       <x:c r="G38" s="0">
-        <x:v>1.38916562341345</x:v>
+        <x:v>1.43353667777401</x:v>
       </x:c>
       <x:c r="H38" s="0">
-        <x:v>-47534</x:v>
+        <x:v>-59679</x:v>
       </x:c>
       <x:c r="I38" s="0">
-        <x:v>65.203</x:v>
+        <x:v>66.929</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:9">
@@ -1642,28 +1648,28 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="B39" s="0">
-        <x:v>212563</x:v>
+        <x:v>466428</x:v>
       </x:c>
       <x:c r="C39" s="0">
-        <x:v>64.431</x:v>
+        <x:v>65.495</x:v>
       </x:c>
       <x:c r="D39" s="0">
-        <x:v>273883</x:v>
+        <x:v>534269</x:v>
       </x:c>
       <x:c r="E39" s="0">
-        <x:v>64.951</x:v>
+        <x:v>65.812</x:v>
       </x:c>
       <x:c r="F39" s="0">
-        <x:v>486446</x:v>
+        <x:v>1000697</x:v>
       </x:c>
       <x:c r="G39" s="0">
-        <x:v>1.57343847117645</x:v>
+        <x:v>2.47964366766936</x:v>
       </x:c>
       <x:c r="H39" s="0">
-        <x:v>-61320</x:v>
+        <x:v>-67841</x:v>
       </x:c>
       <x:c r="I39" s="0">
-        <x:v>66.756</x:v>
+        <x:v>67.991</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:9">
@@ -1671,28 +1677,28 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="B40" s="0">
-        <x:v>78779</x:v>
+        <x:v>1011590</x:v>
       </x:c>
       <x:c r="C40" s="0">
-        <x:v>64.673</x:v>
+        <x:v>65.382</x:v>
       </x:c>
       <x:c r="D40" s="0">
-        <x:v>140100</x:v>
+        <x:v>1086729</x:v>
       </x:c>
       <x:c r="E40" s="0">
-        <x:v>64.66</x:v>
+        <x:v>65.616</x:v>
       </x:c>
       <x:c r="F40" s="0">
-        <x:v>218879</x:v>
+        <x:v>2098319</x:v>
       </x:c>
       <x:c r="G40" s="0">
-        <x:v>0.707977122090902</x:v>
+        <x:v>5.19945939789998</x:v>
       </x:c>
       <x:c r="H40" s="0">
-        <x:v>-61321</x:v>
+        <x:v>-75139</x:v>
       </x:c>
       <x:c r="I40" s="0">
-        <x:v>64.643</x:v>
+        <x:v>68.767</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:9">
@@ -1700,28 +1706,28 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="B41" s="0">
-        <x:v>159672</x:v>
+        <x:v>1733631</x:v>
       </x:c>
       <x:c r="C41" s="0">
-        <x:v>65.018</x:v>
+        <x:v>65.213</x:v>
       </x:c>
       <x:c r="D41" s="0">
-        <x:v>221670</x:v>
+        <x:v>1814625</x:v>
       </x:c>
       <x:c r="E41" s="0">
-        <x:v>64.784</x:v>
+        <x:v>65.541</x:v>
       </x:c>
       <x:c r="F41" s="0">
-        <x:v>381342</x:v>
+        <x:v>3548256</x:v>
       </x:c>
       <x:c r="G41" s="0">
-        <x:v>1.2334733423142</x:v>
+        <x:v>8.79228230090609</x:v>
       </x:c>
       <x:c r="H41" s="0">
-        <x:v>-61998</x:v>
+        <x:v>-80994</x:v>
       </x:c>
       <x:c r="I41" s="0">
-        <x:v>64.179</x:v>
+        <x:v>72.55</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:9">
@@ -1729,28 +1735,28 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="B42" s="0">
-        <x:v>539021</x:v>
+        <x:v>94298</x:v>
       </x:c>
       <x:c r="C42" s="0">
-        <x:v>65.186</x:v>
+        <x:v>65.155</x:v>
       </x:c>
       <x:c r="D42" s="0">
-        <x:v>610215</x:v>
+        <x:v>177302</x:v>
       </x:c>
       <x:c r="E42" s="0">
-        <x:v>65.537</x:v>
+        <x:v>65.139</x:v>
       </x:c>
       <x:c r="F42" s="0">
-        <x:v>1149236</x:v>
+        <x:v>271600</x:v>
       </x:c>
       <x:c r="G42" s="0">
-        <x:v>3.71727208130181</x:v>
+        <x:v>0.673002137649058</x:v>
       </x:c>
       <x:c r="H42" s="0">
-        <x:v>-71194</x:v>
+        <x:v>-83004</x:v>
       </x:c>
       <x:c r="I42" s="0">
-        <x:v>68.193</x:v>
+        <x:v>65.12</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:9">
@@ -1758,28 +1764,28 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="B43" s="0">
-        <x:v>2465796</x:v>
+        <x:v>193674</x:v>
       </x:c>
       <x:c r="C43" s="0">
-        <x:v>64.897</x:v>
+        <x:v>64.778</x:v>
       </x:c>
       <x:c r="D43" s="0">
-        <x:v>2562900</x:v>
+        <x:v>285139</x:v>
       </x:c>
       <x:c r="E43" s="0">
-        <x:v>64.968</x:v>
+        <x:v>65.012</x:v>
       </x:c>
       <x:c r="F43" s="0">
-        <x:v>5028696</x:v>
+        <x:v>478813</x:v>
       </x:c>
       <x:c r="G43" s="0">
-        <x:v>16.265615805765</x:v>
+        <x:v>1.18645866176052</x:v>
       </x:c>
       <x:c r="H43" s="0">
-        <x:v>-97104</x:v>
+        <x:v>-91465</x:v>
       </x:c>
       <x:c r="I43" s="0">
-        <x:v>66.785</x:v>
+        <x:v>65.506</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:9">
@@ -1787,28 +1793,28 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="B44" s="0">
-        <x:v>168376</x:v>
+        <x:v>205793</x:v>
       </x:c>
       <x:c r="C44" s="0">
-        <x:v>64.395</x:v>
+        <x:v>65.551</x:v>
       </x:c>
       <x:c r="D44" s="0">
-        <x:v>270449</x:v>
+        <x:v>306837</x:v>
       </x:c>
       <x:c r="E44" s="0">
-        <x:v>64.893</x:v>
+        <x:v>65.487</x:v>
       </x:c>
       <x:c r="F44" s="0">
-        <x:v>438825</x:v>
+        <x:v>512630</x:v>
       </x:c>
       <x:c r="G44" s="0">
-        <x:v>1.4194055190381</x:v>
+        <x:v>1.2702543660642</x:v>
       </x:c>
       <x:c r="H44" s="0">
-        <x:v>-102073</x:v>
+        <x:v>-101044</x:v>
       </x:c>
       <x:c r="I44" s="0">
-        <x:v>65.715</x:v>
+        <x:v>65.355</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:9">
@@ -1816,28 +1822,28 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="B45" s="0">
-        <x:v>34834</x:v>
+        <x:v>653788</x:v>
       </x:c>
       <x:c r="C45" s="0">
-        <x:v>65.062</x:v>
+        <x:v>65.575</x:v>
       </x:c>
       <x:c r="D45" s="0">
-        <x:v>150489</x:v>
+        <x:v>764072</x:v>
       </x:c>
       <x:c r="E45" s="0">
-        <x:v>65.936</x:v>
+        <x:v>65.949</x:v>
       </x:c>
       <x:c r="F45" s="0">
-        <x:v>185323</x:v>
+        <x:v>1417860</x:v>
       </x:c>
       <x:c r="G45" s="0">
-        <x:v>0.599438247603709</x:v>
+        <x:v>3.51333877351654</x:v>
       </x:c>
       <x:c r="H45" s="0">
-        <x:v>-115655</x:v>
+        <x:v>-110284</x:v>
       </x:c>
       <x:c r="I45" s="0">
-        <x:v>66.199</x:v>
+        <x:v>68.167</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:9">
@@ -1845,28 +1851,28 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="B46" s="0">
-        <x:v>332897</x:v>
+        <x:v>36615</x:v>
       </x:c>
       <x:c r="C46" s="0">
-        <x:v>64.799</x:v>
+        <x:v>65.177</x:v>
       </x:c>
       <x:c r="D46" s="0">
-        <x:v>499516</x:v>
+        <x:v>166103</x:v>
       </x:c>
       <x:c r="E46" s="0">
-        <x:v>65.083</x:v>
+        <x:v>66.087</x:v>
       </x:c>
       <x:c r="F46" s="0">
-        <x:v>832413</x:v>
+        <x:v>202718</x:v>
       </x:c>
       <x:c r="G46" s="0">
-        <x:v>2.69248927549493</x:v>
+        <x:v>0.502318289175043</x:v>
       </x:c>
       <x:c r="H46" s="0">
-        <x:v>-166619</x:v>
+        <x:v>-129488</x:v>
       </x:c>
       <x:c r="I46" s="0">
-        <x:v>65.65</x:v>
+        <x:v>66.345</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:9">
@@ -1874,28 +1880,28 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="B47" s="0">
-        <x:v>734989</x:v>
+        <x:v>3261158</x:v>
       </x:c>
       <x:c r="C47" s="0">
-        <x:v>65.056</x:v>
+        <x:v>65.514</x:v>
       </x:c>
       <x:c r="D47" s="0">
-        <x:v>1011127</x:v>
+        <x:v>3442295</x:v>
       </x:c>
       <x:c r="E47" s="0">
-        <x:v>65.243</x:v>
+        <x:v>65.574</x:v>
       </x:c>
       <x:c r="F47" s="0">
-        <x:v>1746116</x:v>
+        <x:v>6703453</x:v>
       </x:c>
       <x:c r="G47" s="0">
-        <x:v>5.64791588282511</x:v>
+        <x:v>16.6105971967231</x:v>
       </x:c>
       <x:c r="H47" s="0">
-        <x:v>-276138</x:v>
+        <x:v>-181137</x:v>
       </x:c>
       <x:c r="I47" s="0">
-        <x:v>65.74</x:v>
+        <x:v>66.666</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:9">
@@ -1903,28 +1909,28 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="B48" s="0">
-        <x:v>400181</x:v>
+        <x:v>400999</x:v>
       </x:c>
       <x:c r="C48" s="0">
-        <x:v>65.485</x:v>
+        <x:v>65.248</x:v>
       </x:c>
       <x:c r="D48" s="0">
-        <x:v>697650</x:v>
+        <x:v>644880</x:v>
       </x:c>
       <x:c r="E48" s="0">
-        <x:v>64.829</x:v>
+        <x:v>65.637</x:v>
       </x:c>
       <x:c r="F48" s="0">
-        <x:v>1097831</x:v>
+        <x:v>1045879</x:v>
       </x:c>
       <x:c r="G48" s="0">
-        <x:v>3.55099955647722</x:v>
+        <x:v>2.59160089367548</x:v>
       </x:c>
       <x:c r="H48" s="0">
-        <x:v>-297469</x:v>
+        <x:v>-243881</x:v>
       </x:c>
       <x:c r="I48" s="0">
-        <x:v>63.945</x:v>
+        <x:v>66.277</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:9">
@@ -1932,28 +1938,86 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="B49" s="0">
-        <x:v>64773</x:v>
+        <x:v>457031</x:v>
       </x:c>
       <x:c r="C49" s="0">
-        <x:v>65.424</x:v>
+        <x:v>65.746</x:v>
       </x:c>
       <x:c r="D49" s="0">
-        <x:v>431553</x:v>
+        <x:v>767142</x:v>
       </x:c>
       <x:c r="E49" s="0">
-        <x:v>65.295</x:v>
+        <x:v>65.06</x:v>
       </x:c>
       <x:c r="F49" s="0">
-        <x:v>496326</x:v>
+        <x:v>1224173</x:v>
       </x:c>
       <x:c r="G49" s="0">
-        <x:v>1.60539591783081</x:v>
+        <x:v>3.0333985487933</x:v>
       </x:c>
       <x:c r="H49" s="0">
-        <x:v>-366780</x:v>
+        <x:v>-310111</x:v>
       </x:c>
       <x:c r="I49" s="0">
-        <x:v>65.272</x:v>
+        <x:v>64.05</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50" spans="1:9">
+      <x:c r="A50" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="B50" s="0">
+        <x:v>904087</x:v>
+      </x:c>
+      <x:c r="C50" s="0">
+        <x:v>65.515</x:v>
+      </x:c>
+      <x:c r="D50" s="0">
+        <x:v>1224888</x:v>
+      </x:c>
+      <x:c r="E50" s="0">
+        <x:v>65.601</x:v>
+      </x:c>
+      <x:c r="F50" s="0">
+        <x:v>2128975</x:v>
+      </x:c>
+      <x:c r="G50" s="0">
+        <x:v>5.27542240795804</x:v>
+      </x:c>
+      <x:c r="H50" s="0">
+        <x:v>-320801</x:v>
+      </x:c>
+      <x:c r="I50" s="0">
+        <x:v>65.845</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="51" spans="1:9">
+      <x:c r="A51" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="B51" s="0">
+        <x:v>68087</x:v>
+      </x:c>
+      <x:c r="C51" s="0">
+        <x:v>65.528</x:v>
+      </x:c>
+      <x:c r="D51" s="0">
+        <x:v>458668</x:v>
+      </x:c>
+      <x:c r="E51" s="0">
+        <x:v>65.433</x:v>
+      </x:c>
+      <x:c r="F51" s="0">
+        <x:v>526755</x:v>
+      </x:c>
+      <x:c r="G51" s="0">
+        <x:v>1.30525493747176</x:v>
+      </x:c>
+      <x:c r="H51" s="0">
+        <x:v>-390581</x:v>
+      </x:c>
+      <x:c r="I51" s="0">
+        <x:v>65.416</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
